--- a/data/DATA.xlsx
+++ b/data/DATA.xlsx
@@ -33,14 +33,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId24" roundtripDataChecksum="s0K4lRMRAblYP6LqK4oPqbxIN2s93dkLApUSPKAZce0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId24" roundtripDataChecksum="OaOXRb8xyBh6uiN/GekqOiXxRTx5ItTRps98N5o7A1o="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="846">
   <si>
     <t>id</t>
   </si>
@@ -1672,214 +1672,220 @@
     <t>./images/2022/DUONG_THI_THANH_TAM.jpg</t>
   </si>
   <si>
+    <t>Hồ Thị Thảo Tiên</t>
+  </si>
+  <si>
+    <t>./images/2022/HO_THI_THAO_TIEN.jpg</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Tuyến</t>
+  </si>
+  <si>
+    <t>Tuyến</t>
+  </si>
+  <si>
+    <t>Quảng Phương</t>
+  </si>
+  <si>
+    <t>Đào Thị Bích Thảo</t>
+  </si>
+  <si>
+    <t>./images/2022/DAO_THI_BICH_THAO.jpg</t>
+  </si>
+  <si>
+    <t>Hồ Thị Thanh Hiền</t>
+  </si>
+  <si>
+    <t>Nhuận Đức</t>
+  </si>
+  <si>
+    <t>./images/2022/HO_THI_THANH_HIEN.jpg</t>
+  </si>
+  <si>
+    <t>Lê Thị Xuân Nhàn (Nhàn Lee)</t>
+  </si>
+  <si>
+    <t>./images/2022/LE_THI_XUAN_NHAN.jpg</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Diệp Linh (Nhỏ)</t>
+  </si>
+  <si>
+    <t>smile</t>
+  </si>
+  <si>
+    <t>./images/2022/NGUYEN_THI_DIEP_LINH.jpg</t>
+  </si>
+  <si>
+    <t>Lê Thị Kim Ngân</t>
+  </si>
+  <si>
+    <t>Photo girl</t>
+  </si>
+  <si>
+    <t>./images/2021/LE_THI_KIM_NGAN.jpg</t>
+  </si>
+  <si>
+    <t>Bạch Thị Thu Thảo (Tabi)</t>
+  </si>
+  <si>
+    <t>Ban chấp hành 2022-2024</t>
+  </si>
+  <si>
+    <t>Thảo Tabi</t>
+  </si>
+  <si>
+    <t>./images/2021/BACH_THI_THU_THAO.jpg</t>
+  </si>
+  <si>
+    <t>Nguyễn Khánh Hà</t>
+  </si>
+  <si>
+    <t>oyoui</t>
+  </si>
+  <si>
+    <t>./images/2021/NGUYEN_KHANH_HA.jpg</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Nhật Trâm (Na)</t>
+  </si>
+  <si>
+    <t>Nhat Tram</t>
+  </si>
+  <si>
+    <t>./images/2021/NGUYEN_THI_NHAT_TRAM.jpg</t>
+  </si>
+  <si>
+    <t>Trần Thị Quỳnh Phương</t>
+  </si>
+  <si>
+    <t>Ban chấp hành 2022-2023</t>
+  </si>
+  <si>
+    <t>Mãi yêu Chánh Tâm</t>
+  </si>
+  <si>
+    <t>./images/2021/TRAN_THI_QUYNH_PHUONG.jpg</t>
+  </si>
+  <si>
+    <t>Phan Thị Cẩm Nhi (Nhem cute)</t>
+  </si>
+  <si>
+    <t>Ban chấp hành 2021-2024</t>
+  </si>
+  <si>
+    <t>Nhuận Hỷ</t>
+  </si>
+  <si>
+    <t>./images/2021/PHAN_THI_CAM_NHI.jpg</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Hồng Ngọc (Right)</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Diễm Ái (Nu)</t>
+  </si>
+  <si>
+    <t>Quảng Ân</t>
+  </si>
+  <si>
+    <t>Lê Thị Ngọc (Ngọtle)</t>
+  </si>
+  <si>
+    <t>Nguyễn Nhật Uyên</t>
+  </si>
+  <si>
+    <t>Lớp trưởng</t>
+  </si>
+  <si>
+    <t>Thích Yêu Thương, Nắng Yêu Thương, Tương Sinh</t>
+  </si>
+  <si>
+    <t>Nhật Uyên xinh đẹp</t>
+  </si>
+  <si>
+    <t>./images/2020/NGUYEN_NHAT_UYEN.jpg</t>
+  </si>
+  <si>
+    <t>Nguyễn Nhật Linh</t>
+  </si>
+  <si>
+    <t>Bớt nghe, bớt nói, bớt nhìn. Giữ tâm thanh tịnh mới là thảnh thơi.</t>
+  </si>
+  <si>
+    <t>./images/2020/NGUYEN_NHAT_LINH.jpg</t>
+  </si>
+  <si>
+    <t>Trần Xuân Trung</t>
+  </si>
+  <si>
+    <t>Trung</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Mỹ Nhàn</t>
+  </si>
+  <si>
+    <t>Nhuận Niệm</t>
+  </si>
+  <si>
+    <t>./images/2020/NGUYEN_THI_MY_NHAN.jpg</t>
+  </si>
+  <si>
+    <t>Nguyễn Đăng Huy</t>
+  </si>
+  <si>
+    <t>Chú Huy</t>
+  </si>
+  <si>
+    <t>./images/2020/NGUYEN_DANG_HUY.jpg</t>
+  </si>
+  <si>
+    <t>Hoàng Giang (Long Ka)</t>
+  </si>
+  <si>
+    <t>Kết nối - Nhiệt tình - Vui vẻ - Hoà đồng</t>
+  </si>
+  <si>
+    <t>./images/2020/HOANG_GIANG.jpg</t>
+  </si>
+  <si>
+    <t>Nguyễn Bá Quốc</t>
+  </si>
+  <si>
+    <t>Quốc</t>
+  </si>
+  <si>
+    <t>Phan Văn Hưng</t>
+  </si>
+  <si>
+    <t>Nguyễn Phúc Hưng (Ki)</t>
+  </si>
+  <si>
+    <t>Đinh Thị Ngọc Anh</t>
+  </si>
+  <si>
+    <t>Banh</t>
+  </si>
+  <si>
+    <t>./images/2020/DINH_THI_NGOC_ANH.jpg</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Kiều Anh</t>
+  </si>
+  <si>
+    <t>Quang Tú</t>
+  </si>
+  <si>
+    <t>./images/2020/NGUYEN_HOANG_KIEU_ANH.jpg</t>
+  </si>
+  <si>
     <t>Đoàn Thị Thu Hà</t>
   </si>
   <si>
-    <t>Hồ Thị Thảo Tiên</t>
-  </si>
-  <si>
-    <t>./images/2022/HO_THI_THAO_TIEN.jpg</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Kim Tuyến</t>
-  </si>
-  <si>
-    <t>Tuyến</t>
-  </si>
-  <si>
-    <t>Quảng Phương</t>
-  </si>
-  <si>
-    <t>Đào Thị Bích Thảo</t>
-  </si>
-  <si>
-    <t>./images/2022/DAO_THI_BICH_THAO.jpg</t>
-  </si>
-  <si>
-    <t>Hồ Thị Thanh Hiền</t>
-  </si>
-  <si>
-    <t>Nhuận Đức</t>
-  </si>
-  <si>
-    <t>./images/2022/HO_THI_THANH_HIEN.jpg</t>
-  </si>
-  <si>
-    <t>Lê Thị Xuân Nhàn (Nhàn Lee)</t>
-  </si>
-  <si>
-    <t>./images/2022/LE_THI_XUAN_NHAN.jpg</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Diệp Linh (Nhỏ)</t>
-  </si>
-  <si>
-    <t>smile</t>
-  </si>
-  <si>
-    <t>./images/2022/NGUYEN_THI_DIEP_LINH.jpg</t>
-  </si>
-  <si>
-    <t>Lê Thị Kim Ngân</t>
-  </si>
-  <si>
-    <t>Photo girl</t>
-  </si>
-  <si>
-    <t>./images/2021/LE_THI_KIM_NGAN.jpg</t>
-  </si>
-  <si>
-    <t>Bạch Thị Thu Thảo (Tabi)</t>
-  </si>
-  <si>
-    <t>Ban chấp hành 2022-2024</t>
-  </si>
-  <si>
-    <t>Thảo Tabi</t>
-  </si>
-  <si>
-    <t>./images/2021/BACH_THI_THU_THAO.jpg</t>
-  </si>
-  <si>
-    <t>Nguyễn Khánh Hà</t>
-  </si>
-  <si>
-    <t>oyoui</t>
-  </si>
-  <si>
-    <t>./images/2021/NGUYEN_KHANH_HA.jpg</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Nhật Trâm (Na)</t>
-  </si>
-  <si>
-    <t>Nhat Tram</t>
-  </si>
-  <si>
-    <t>./images/2021/NGUYEN_THI_NHAT_TRAM.jpg</t>
-  </si>
-  <si>
-    <t>Trần Thị Quỳnh Phương</t>
-  </si>
-  <si>
-    <t>Ban chấp hành 2022-2023</t>
-  </si>
-  <si>
-    <t>Mãi yêu Chánh Tâm</t>
-  </si>
-  <si>
-    <t>./images/2021/TRAN_THI_QUYNH_PHUONG.jpg</t>
-  </si>
-  <si>
-    <t>Phan Thị Cẩm Nhi (Nhem cute)</t>
-  </si>
-  <si>
-    <t>Ban chấp hành 2021-2024</t>
-  </si>
-  <si>
-    <t>Nhuận Hỷ</t>
-  </si>
-  <si>
-    <t>./images/2021/PHAN_THI_CAM_NHI.jpg</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Hồng Ngọc (Right)</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Diễm Ái (Nu)</t>
-  </si>
-  <si>
-    <t>Quảng Ân</t>
-  </si>
-  <si>
-    <t>Lê Thị Ngọc (Ngọtle)</t>
-  </si>
-  <si>
-    <t>Nguyễn Nhật Uyên</t>
-  </si>
-  <si>
-    <t>Lớp trưởng</t>
-  </si>
-  <si>
-    <t>Thích Yêu Thương, Nắng Yêu Thương, Tương Sinh</t>
-  </si>
-  <si>
-    <t>Nhật Uyên xinh đẹp</t>
-  </si>
-  <si>
-    <t>./images/2020/NGUYEN_NHAT_UYEN.jpg</t>
-  </si>
-  <si>
-    <t>Nguyễn Nhật Linh</t>
-  </si>
-  <si>
-    <t>Bớt nghe, bớt nói, bớt nhìn. Giữ tâm thanh tịnh mới là thảnh thơi.</t>
-  </si>
-  <si>
-    <t>./images/2020/NGUYEN_NHAT_LINH.jpg</t>
-  </si>
-  <si>
-    <t>Trần Xuân Trung</t>
-  </si>
-  <si>
-    <t>Trung</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Mỹ Nhàn</t>
-  </si>
-  <si>
-    <t>Nhuận Niệm</t>
-  </si>
-  <si>
-    <t>./images/2020/NGUYEN_THI_MY_NHAN.jpg</t>
-  </si>
-  <si>
-    <t>Nguyễn Đăng Huy</t>
-  </si>
-  <si>
-    <t>Chú Huy</t>
-  </si>
-  <si>
-    <t>./images/2020/NGUYEN_DANG_HUY.jpg</t>
-  </si>
-  <si>
-    <t>Hoàng Giang (Long Ka)</t>
-  </si>
-  <si>
-    <t>Kết nối - Nhiệt tình - Vui vẻ - Hoà đồng</t>
-  </si>
-  <si>
-    <t>./images/2020/HOANG_GIANG.jpg</t>
-  </si>
-  <si>
-    <t>Nguyễn Bá Quốc</t>
-  </si>
-  <si>
-    <t>Quốc</t>
-  </si>
-  <si>
-    <t>Phan Văn Hưng</t>
-  </si>
-  <si>
-    <t>Nguyễn Phúc Hưng (Ki)</t>
-  </si>
-  <si>
-    <t>Đinh Thị Ngọc Anh</t>
-  </si>
-  <si>
-    <t>Banh</t>
-  </si>
-  <si>
-    <t>./images/2020/DINH_THI_NGOC_ANH.jpg</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Kiều Anh</t>
-  </si>
-  <si>
-    <t>Quang Tú</t>
-  </si>
-  <si>
-    <t>./images/2020/NGUYEN_HOANG_KIEU_ANH.jpg</t>
+    <t>Cô gái Huế hay cười</t>
+  </si>
+  <si>
+    <t>./images/2020/DOAN_THI_THU_HA.jpg</t>
   </si>
   <si>
     <t>Lê Thị Thuận Hóa</t>
@@ -4016,10 +4022,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -4028,10 +4034,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -4042,22 +4048,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="H3" s="1">
         <v>3.0</v>
@@ -4068,7 +4074,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>359</v>
@@ -4080,10 +4086,10 @@
         <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -4094,22 +4100,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4120,22 +4126,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="H6" s="1">
         <v>6.0</v>
@@ -4146,10 +4152,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -4158,10 +4164,10 @@
         <v>52</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4172,22 +4178,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>138</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -4198,22 +4204,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>39</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -5263,22 +5269,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6333,22 +6339,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>531</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6359,10 +6365,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -6371,10 +6377,10 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7428,22 +7434,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>376</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H2" s="5">
         <v>5.0</v>
@@ -8498,10 +8504,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -8510,7 +8516,7 @@
         <v>500</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H2" s="2">
         <v>7.0</v>
@@ -8521,10 +8527,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
@@ -9590,7 +9596,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>145</v>
@@ -9599,13 +9605,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -9616,22 +9622,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>266</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -9642,7 +9648,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -9654,10 +9660,10 @@
         <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -9668,22 +9674,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>174</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -10737,22 +10743,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -10763,22 +10769,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -10789,22 +10795,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>440</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -10815,7 +10821,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>71</v>
@@ -10827,10 +10833,10 @@
         <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -10841,7 +10847,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>221</v>
@@ -10853,10 +10859,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -11879,7 +11885,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -16408,22 +16414,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>128</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="H2" s="2">
         <v>7.0</v>
@@ -16434,16 +16440,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>122</v>
@@ -16457,22 +16463,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>207</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>122</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -16483,16 +16489,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>122</v>
@@ -16506,16 +16512,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>122</v>
@@ -16529,19 +16535,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="H7" s="2">
         <v>7.0</v>
@@ -16552,13 +16558,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>387</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>26</v>
@@ -16567,7 +16573,7 @@
         <v>122</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -16578,13 +16584,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>26</v>
@@ -16593,7 +16599,7 @@
         <v>122</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="H9" s="2">
         <v>8.0</v>
@@ -16604,13 +16610,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>39</v>
@@ -16627,7 +16633,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>158</v>
@@ -16650,7 +16656,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>207</v>
@@ -16673,10 +16679,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -16696,10 +16702,10 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -16719,10 +16725,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -16731,7 +16737,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H15" s="2">
         <v>8.0</v>
@@ -16742,10 +16748,10 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -16765,7 +16771,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>521</v>
@@ -16788,7 +16794,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>75</v>
@@ -16811,7 +16817,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>320</v>
@@ -16834,7 +16840,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>143</v>
@@ -16857,7 +16863,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>124</v>
@@ -16880,7 +16886,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>262</v>
@@ -16903,7 +16909,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>166</v>
@@ -16926,7 +16932,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>94</v>
@@ -16949,10 +16955,10 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -16972,7 +16978,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>79</v>
@@ -16995,7 +17001,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>20</v>
@@ -17018,7 +17024,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>266</v>
@@ -17041,7 +17047,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>51</v>
@@ -17064,7 +17070,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>179</v>
@@ -17087,10 +17093,10 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -17110,7 +17116,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>90</v>
@@ -17133,7 +17139,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>174</v>
@@ -17156,7 +17162,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>176</v>
@@ -17179,7 +17185,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>515</v>
@@ -17202,10 +17208,10 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -17225,7 +17231,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>164</v>
@@ -17248,10 +17254,10 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
@@ -17271,7 +17277,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>20</v>
@@ -17317,7 +17323,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
@@ -17340,10 +17346,10 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
@@ -17363,10 +17369,10 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
@@ -17386,7 +17392,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>147</v>
@@ -17409,10 +17415,10 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
@@ -17432,10 +17438,10 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
@@ -17455,7 +17461,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>476</v>
@@ -17478,10 +17484,10 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
@@ -17501,7 +17507,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>299</v>
@@ -17524,7 +17530,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>277</v>
@@ -17547,10 +17553,10 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>10</v>
@@ -17570,7 +17576,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>270</v>
@@ -17593,10 +17599,10 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
@@ -17616,10 +17622,10 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
@@ -17639,10 +17645,10 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
@@ -17662,7 +17668,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>90</v>
@@ -17685,10 +17691,10 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
@@ -17708,7 +17714,7 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>191</v>
@@ -17731,7 +17737,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>15</v>
@@ -17754,10 +17760,10 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>10</v>
@@ -17778,10 +17784,10 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
@@ -17801,7 +17807,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>402</v>
@@ -17824,7 +17830,7 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>376</v>
@@ -17847,7 +17853,7 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>531</v>
@@ -17870,10 +17876,10 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
@@ -17893,7 +17899,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>143</v>
@@ -17916,7 +17922,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>15</v>
@@ -17939,7 +17945,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>128</v>
@@ -17962,7 +17968,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>75</v>
@@ -17974,7 +17980,7 @@
         <v>26</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="H69" s="2">
         <v>8.0</v>
@@ -17985,7 +17991,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>387</v>
@@ -18008,7 +18014,7 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>495</v>
@@ -18031,10 +18037,10 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
@@ -18054,7 +18060,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>432</v>
@@ -18077,7 +18083,7 @@
         <v>73.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>207</v>
@@ -18100,7 +18106,7 @@
         <v>74.0</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>476</v>
@@ -24157,7 +24163,7 @@
         <v>542</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>476</v>
+        <v>174</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -24167,6 +24173,9 @@
       </c>
       <c r="F22" s="2" t="s">
         <v>122</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>543</v>
       </c>
       <c r="H22" s="2">
         <v>6.0</v>
@@ -24177,25 +24186,22 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>174</v>
+        <v>545</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H23" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -24203,22 +24209,25 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>546</v>
+        <v>71</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>547</v>
+        <v>122</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="H24" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -24226,25 +24235,25 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>122</v>
+        <v>550</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H25" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -24252,10 +24261,10 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>262</v>
+        <v>521</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -24264,67 +24273,42 @@
         <v>26</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>551</v>
+        <v>122</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H26" s="2">
         <v>7.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>521</v>
+        <v>166</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>122</v>
+        <v>555</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H27" s="2">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="1">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H28" s="2">
         <v>6.0</v>
       </c>
     </row>
+    <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -25296,7 +25280,6 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$G$1">
     <sortState ref="A1:G1">
@@ -25358,7 +25341,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>387</v>
@@ -25370,10 +25353,10 @@
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>560</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25384,22 +25367,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>564</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -25410,7 +25393,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>476</v>
@@ -25422,10 +25405,10 @@
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>566</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>567</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -25436,7 +25419,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>184</v>
@@ -25448,10 +25431,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -25462,22 +25445,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>128</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>573</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>574</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -25488,22 +25471,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>578</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -25514,7 +25497,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>79</v>
@@ -25537,7 +25520,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>338</v>
@@ -25549,7 +25532,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -25560,7 +25543,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>79</v>
@@ -26624,22 +26607,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>587</v>
       </c>
       <c r="H2" s="1">
         <v>3.0</v>
@@ -26650,22 +26633,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>166</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>590</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -26676,19 +26659,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -26699,22 +26682,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>521</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>594</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>595</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -26725,7 +26708,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>143</v>
@@ -26737,10 +26720,10 @@
         <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>597</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>598</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -26751,7 +26734,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>391</v>
@@ -26763,10 +26746,10 @@
         <v>16</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -26777,10 +26760,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>603</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
@@ -26800,7 +26783,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>266</v>
@@ -26823,7 +26806,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>266</v>
@@ -26846,7 +26829,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>62</v>
@@ -26858,10 +26841,10 @@
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>608</v>
       </c>
       <c r="H11" s="1">
         <v>7.0</v>
@@ -26872,7 +26855,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>62</v>
@@ -26884,16 +26867,41 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="H12" s="2">
         <v>7.0</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1"/>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="H13" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
     <row r="14" ht="15.75" customHeight="1"/>
     <row r="15" ht="15.75" customHeight="1"/>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -27936,22 +27944,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="H2" s="1">
         <v>4.0</v>
@@ -27962,22 +27970,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -27988,19 +27996,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28011,10 +28019,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -28034,7 +28042,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>262</v>
@@ -28046,10 +28054,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H6" s="1">
         <v>7.0</v>
@@ -28060,7 +28068,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>436</v>
@@ -28072,10 +28080,10 @@
         <v>39</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28086,19 +28094,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1"/>
@@ -29149,10 +29157,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -29161,10 +29169,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H2" s="1">
         <v>6.0</v>
@@ -29175,10 +29183,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
@@ -29187,10 +29195,10 @@
         <v>500</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H3" s="1">
         <v>6.0</v>
@@ -29201,7 +29209,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>182</v>
@@ -29213,7 +29221,7 @@
         <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -29224,22 +29232,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H5" s="2">
         <v>6.0</v>
@@ -29250,22 +29258,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>128</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29276,7 +29284,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>58</v>
@@ -29288,10 +29296,10 @@
         <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="H7" s="2">
         <v>7.0</v>

--- a/data/DATA.xlsx
+++ b/data/DATA.xlsx
@@ -638,10 +638,10 @@
     <t>./images/2024/NGUYEN_MAI_LAN.jpg</t>
   </si>
   <si>
-    <t>Ngô Vũ Vân Châu</t>
-  </si>
-  <si>
-    <t>Quảng Ngọc</t>
+    <t>Ngô Vũ Vân Châu (mani - mina)</t>
+  </si>
+  <si>
+    <t>thích chị Nhật Uyên - thích BTT 📷</t>
   </si>
   <si>
     <t>./images/2024/NGO_VU_VAN_CHAU.jpg</t>
@@ -19380,7 +19380,7 @@
       <c r="A51" s="1">
         <v>49.0</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>198</v>
       </c>
       <c r="C51" s="1" t="s">

--- a/data/DATA.xlsx
+++ b/data/DATA.xlsx
@@ -1705,6 +1705,9 @@
     <t>Lê Thị Xuân Nhàn (Nhàn Lee)</t>
   </si>
   <si>
+    <t>Mình đây tuy chẳng cao sang. Chỉ mong cố gắng, vững vàng mai sau</t>
+  </si>
+  <si>
     <t>./images/2022/LE_THI_XUAN_NHAN.jpg</t>
   </si>
   <si>
@@ -2038,7 +2041,7 @@
     <t>Chánh Tâm Nhỏ, Hít Thở Mỉm Cười, Tâm An</t>
   </si>
   <si>
-    <t>🎨🌧️🎧</t>
+    <t>&lt;a href="https://lythanhtung-github.github.io/chanhtamwtbh/" target="_blank"&gt;🎨🌧️🎧&lt;/a&gt;</t>
   </si>
   <si>
     <t>./images/2017/LY_THANH_TUNG.jpg</t>
@@ -2099,9 +2102,6 @@
   </si>
   <si>
     <t>Đặng Thanh Hương (Na)</t>
-  </si>
-  <si>
-    <t>Hươ</t>
   </si>
   <si>
     <t>Ban cố vấn</t>
@@ -4022,10 +4022,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -4034,10 +4034,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -4048,22 +4048,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="F3" s="1" t="s">
         <v>664</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>665</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H3" s="1">
         <v>3.0</v>
@@ -4074,7 +4074,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>359</v>
@@ -4086,10 +4086,10 @@
         <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -4100,22 +4100,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4126,22 +4126,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H6" s="1">
         <v>6.0</v>
@@ -4152,10 +4152,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -4164,10 +4164,10 @@
         <v>52</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4178,22 +4178,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>138</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -4204,10 +4204,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>685</v>
+        <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>686</v>
@@ -5275,7 +5275,7 @@
         <v>690</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
@@ -10746,7 +10746,7 @@
         <v>724</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>686</v>
@@ -23726,8 +23726,8 @@
       <c r="C5" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>67</v>
+      <c r="D5" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -24273,10 +24273,10 @@
         <v>26</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>122</v>
+        <v>553</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H26" s="2">
         <v>7.0</v>
@@ -24287,7 +24287,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>166</v>
@@ -24299,10 +24299,10 @@
         <v>26</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H27" s="2">
         <v>6.0</v>
@@ -25341,7 +25341,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>387</v>
@@ -25353,10 +25353,10 @@
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25367,22 +25367,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -25393,7 +25393,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>476</v>
@@ -25405,10 +25405,10 @@
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -25419,7 +25419,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>184</v>
@@ -25431,10 +25431,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -25445,22 +25445,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>128</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -25471,22 +25471,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -25497,7 +25497,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>79</v>
@@ -25520,7 +25520,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>338</v>
@@ -25532,7 +25532,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -25543,7 +25543,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>79</v>
@@ -26607,22 +26607,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H2" s="1">
         <v>3.0</v>
@@ -26633,22 +26633,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>166</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -26659,13 +26659,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -26682,22 +26682,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>521</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -26708,7 +26708,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>143</v>
@@ -26720,10 +26720,10 @@
         <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -26734,7 +26734,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>391</v>
@@ -26746,10 +26746,10 @@
         <v>16</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -26760,10 +26760,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
@@ -26783,7 +26783,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>266</v>
@@ -26806,7 +26806,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>266</v>
@@ -26829,7 +26829,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>62</v>
@@ -26841,10 +26841,10 @@
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H11" s="1">
         <v>7.0</v>
@@ -26855,7 +26855,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>62</v>
@@ -26867,10 +26867,10 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H12" s="2">
         <v>7.0</v>
@@ -26881,7 +26881,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>476</v>
@@ -26893,10 +26893,10 @@
         <v>26</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -27944,22 +27944,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2" s="1">
         <v>4.0</v>
@@ -27970,22 +27970,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -27996,19 +27996,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28019,10 +28019,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -28042,7 +28042,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>262</v>
@@ -28054,10 +28054,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H6" s="1">
         <v>7.0</v>
@@ -28068,7 +28068,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>436</v>
@@ -28080,10 +28080,10 @@
         <v>39</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28094,19 +28094,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1"/>
@@ -29157,10 +29157,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -29169,10 +29169,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2" s="1">
         <v>6.0</v>
@@ -29183,10 +29183,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
@@ -29195,10 +29195,10 @@
         <v>500</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H3" s="1">
         <v>6.0</v>
@@ -29209,7 +29209,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>182</v>
@@ -29221,7 +29221,7 @@
         <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -29232,22 +29232,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H5" s="2">
         <v>6.0</v>
@@ -29258,22 +29258,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>128</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29284,7 +29284,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>58</v>
@@ -29296,10 +29296,10 @@
         <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H7" s="2">
         <v>7.0</v>

--- a/data/DATA.xlsx
+++ b/data/DATA.xlsx
@@ -2186,7 +2186,7 @@
     <t>Mặt hơi nhiều râu</t>
   </si>
   <si>
-    <t>./images/2012/TRUONG_MINH_Y.jpg</t>
+    <t>./images/2012/TRUONG_MINH_Y.webp</t>
   </si>
   <si>
     <t>Định Hưng (Toni)</t>
@@ -2198,7 +2198,7 @@
     <t>Toni Định</t>
   </si>
   <si>
-    <t>./images/2012/DINH_HUNG.jpg</t>
+    <t>./images/2012/DINH_HUNG.webp</t>
   </si>
   <si>
     <t>Trương Thị Phương Anh (Bơ Cena)</t>
@@ -2207,7 +2207,7 @@
     <t>Chị Bơ</t>
   </si>
   <si>
-    <t>./images/2012/TRUONG_THI_PHUONG_ANH.jpg</t>
+    <t>./images/2012/TRUONG_THI_PHUONG_ANH.webp</t>
   </si>
   <si>
     <t>Lê Thị Bích Tiên</t>
@@ -2216,7 +2216,7 @@
     <t>Giọng to nhất Chánh Tâm</t>
   </si>
   <si>
-    <t>./images/2012/LE_THI_BICH_TIEN.jpg</t>
+    <t>./images/2012/LE_THI_BICH_TIEN.webp</t>
   </si>
   <si>
     <t>Tống Văn Hùng</t>
@@ -2225,7 +2225,7 @@
     <t>Hùng hóm hỉnh</t>
   </si>
   <si>
-    <t>./images/2011/TONG_VAN_HUNG.jpg</t>
+    <t>./images/2011/TONG_VAN_HUNG.webp</t>
   </si>
   <si>
     <t>Trương Thị Kim Chi (Xuxuchichi)</t>
@@ -2237,7 +2237,7 @@
     <t>Cô dâu Chi</t>
   </si>
   <si>
-    <t>./images/2011/TRUONG_THI_KIM_CHI.jpg</t>
+    <t>./images/2011/TRUONG_THI_KIM_CHI.webp</t>
   </si>
   <si>
     <t>Trương Thị Kim Cương</t>
@@ -2246,7 +2246,7 @@
     <t>Mẹ Khoai, Đậu, Dâu Tây</t>
   </si>
   <si>
-    <t>./images/2011/TRUONG_THI_KIM_CUONG.jpg</t>
+    <t>./images/2011/TRUONG_THI_KIM_CUONG.webp</t>
   </si>
   <si>
     <t>Hồ Thị Diệu Thảo (Bông)</t>
@@ -2255,7 +2255,7 @@
     <t>Tâm Thuận</t>
   </si>
   <si>
-    <t>./images/2011/HO_THI_DIEU_THAO.jpg</t>
+    <t>./images/2011/HO_THI_DIEU_THAO.webp</t>
   </si>
   <si>
     <t>Phan Thị Thanh Hồng</t>
@@ -2264,7 +2264,7 @@
     <t>Quảng Tuyết</t>
   </si>
   <si>
-    <t>./images/2011/PHAN_THI_THANH_HONG.jpg</t>
+    <t>./images/2011/PHAN_THI_THANH_HONG.webp</t>
   </si>
   <si>
     <t>full_name 2010</t>
@@ -9601,8 +9601,8 @@
       <c r="C2" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
+      <c r="D2" s="2" t="s">
+        <v>686</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>711</v>
@@ -9610,7 +9610,7 @@
       <c r="F2" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>713</v>
       </c>
       <c r="H2" s="2">
@@ -9636,7 +9636,7 @@
       <c r="F3" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>717</v>
       </c>
       <c r="H3" s="2">
@@ -9688,7 +9688,7 @@
       <c r="F5" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>723</v>
       </c>
       <c r="H5" s="2">
@@ -10757,7 +10757,7 @@
       <c r="F2" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>726</v>
       </c>
       <c r="H2" s="2">
@@ -10783,7 +10783,7 @@
       <c r="F3" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>730</v>
       </c>
       <c r="H3" s="2">
@@ -10809,7 +10809,7 @@
       <c r="F4" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>733</v>
       </c>
       <c r="H4" s="2">
@@ -10835,7 +10835,7 @@
       <c r="F5" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>736</v>
       </c>
       <c r="H5" s="1">
@@ -10861,7 +10861,7 @@
       <c r="F6" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>739</v>
       </c>
       <c r="H6" s="2">

--- a/data/DATA.xlsx
+++ b/data/DATA.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Vui vẻ, thích cười </t>
   </si>
   <si>
-    <t>./images/2025/LE_THI_THUY_TRANG.jpg</t>
+    <t>./data/images/2025/LE_THI_THUY_TRANG.jpg</t>
   </si>
   <si>
     <t>Trần Văn Quang</t>
@@ -96,7 +96,7 @@
     <t>Trầm tính</t>
   </si>
   <si>
-    <t>./images/2025/TRAN_VAN_QUANG.jpg</t>
+    <t>./data/images/2025/TRAN_VAN_QUANG.jpg</t>
   </si>
   <si>
     <t>Hoàng Ngọc Hoài An</t>
@@ -111,7 +111,7 @@
     <t>Mình là một người low pin nhưng high mood, nhạc là chân ái, deadline là động lực, chưa giỏi lắm nhưng vui là chính</t>
   </si>
   <si>
-    <t>./images/2025/HOANG_NGOC_HOAI_AN.jpg</t>
+    <t>./data/images/2025/HOANG_NGOC_HOAI_AN.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Đặng Thị Thu Thanh </t>
@@ -126,7 +126,7 @@
     <t>Khi tâm an, đời sẽ nhẹ</t>
   </si>
   <si>
-    <t>./images/2025/DANG_THI_THU_THANH.jpg</t>
+    <t>./data/images/2025/DANG_THI_THU_THANH.jpg</t>
   </si>
   <si>
     <t>Lê Nguyễn Phương My (Mắm)</t>
@@ -138,7 +138,7 @@
     <t>Mập nhất gia đình Chánh Tâm</t>
   </si>
   <si>
-    <t>./images/2025/LE_NGUYEN_PHUONG_MY.png</t>
+    <t>./data/images/2025/LE_NGUYEN_PHUONG_MY.png</t>
   </si>
   <si>
     <t>Nguyễn Nhật Ánh (Tia)</t>
@@ -150,7 +150,7 @@
     <t>Tia Nắng</t>
   </si>
   <si>
-    <t>./images/2025/NGUYEN_NHAT_ANH.jpg</t>
+    <t>./data/images/2025/NGUYEN_NHAT_ANH.jpg</t>
   </si>
   <si>
     <t>Phạm Thị Mỹ Nga (Sư sư)</t>
@@ -165,7 +165,7 @@
     <t>📸</t>
   </si>
   <si>
-    <t>./images/2025/PHAM_THI_MY_NGA.jpg</t>
+    <t>./data/images/2025/PHAM_THI_MY_NGA.jpg</t>
   </si>
   <si>
     <t>Lê Bảo Trân (Su Zin)</t>
@@ -177,7 +177,7 @@
     <t>Thành viên mới👼🏻</t>
   </si>
   <si>
-    <t>./images/2025/LE_BAO_TRAN.jpg</t>
+    <t>./data/images/2025/LE_BAO_TRAN.jpg</t>
   </si>
   <si>
     <t>Trần Thị Anh Thư</t>
@@ -189,7 +189,7 @@
     <t>Niệm vô thất</t>
   </si>
   <si>
-    <t>./images/2025/TRAN_THI_ANH_THU.jpg</t>
+    <t>./data/images/2025/TRAN_THI_ANH_THU.jpg</t>
   </si>
   <si>
     <t>Châu Thị Mỹ Lệ</t>
@@ -204,7 +204,7 @@
     <t>Chân thật trong suy nghĩ tử tế trong hành động🥰</t>
   </si>
   <si>
-    <t>./images/2025/CHAU_THI_MY_LE.jpg</t>
+    <t>./data/images/2025/CHAU_THI_MY_LE.jpg</t>
   </si>
   <si>
     <t>Lê Thị Trà My</t>
@@ -222,7 +222,7 @@
     <t>hối nượng</t>
   </si>
   <si>
-    <t>./images/2025/HO_THI_MINH_CHAU.jpg</t>
+    <t>./data/images/2025/HO_THI_MINH_CHAU.jpg</t>
   </si>
   <si>
     <t>Nguyễn Minh Trâm Anh (Nai)</t>
@@ -234,7 +234,7 @@
     <t>Hướng nội fulltime</t>
   </si>
   <si>
-    <t>./images/2025/NGUYEN_MINH_TRAM_ANH.jpg</t>
+    <t>./data/images/2025/NGUYEN_MINH_TRAM_ANH.jpg</t>
   </si>
   <si>
     <t>Trần Thị Xuân Diệu</t>
@@ -249,7 +249,7 @@
     <t>Nhà Thơ</t>
   </si>
   <si>
-    <t>./images/2024/TRAN_THI_XUAN_DIEU.jpg</t>
+    <t>./data/images/2024/TRAN_THI_XUAN_DIEU.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Dạ Thảo (Nai)</t>
@@ -261,7 +261,7 @@
     <t>Con Nai vàng ngơ ngác</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_THI_DA_THAO.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_DA_THAO.jpg</t>
   </si>
   <si>
     <t>Nguyễn Phan Bảo Uyên</t>
@@ -273,7 +273,7 @@
     <t>🧶</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_PHAN_BAO_UYEN.jpg</t>
+    <t>./data/images/2024/NGUYEN_PHAN_BAO_UYEN.jpg</t>
   </si>
   <si>
     <t>Tôn Nữ Yến Ngọc</t>
@@ -285,7 +285,7 @@
     <t>Sống cùng cảm xúc</t>
   </si>
   <si>
-    <t>./images/2024/TON_NU_YEN_NGOC.jpg</t>
+    <t>./data/images/2024/TON_NU_YEN_NGOC.jpg</t>
   </si>
   <si>
     <t>Nguyễn Luýt (Nhất Tam)</t>
@@ -297,7 +297,7 @@
     <t>Nguyện người thường An 🍀</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_LUYT.jpg</t>
+    <t>./data/images/2024/NGUYEN_LUYT.jpg</t>
   </si>
   <si>
     <t>Phạm Đức Định</t>
@@ -318,7 +318,7 @@
     <t>Em Ánh Nguyệt</t>
   </si>
   <si>
-    <t xml:space="preserve">./images/2024/TRAN_NGUYEN_ANH_NHI.jpg
+    <t xml:space="preserve">./data/images/2024/TRAN_NGUYEN_ANH_NHI.jpg
 </t>
   </si>
   <si>
@@ -331,7 +331,7 @@
     <t>Hương Queen</t>
   </si>
   <si>
-    <t>./images/2024/TRAN_THI_THU_HUONG.jpg</t>
+    <t>./data/images/2024/TRAN_THI_THU_HUONG.jpg</t>
   </si>
   <si>
     <t>Trần Nguyễn Ánh Nguyệt</t>
@@ -343,7 +343,7 @@
     <t>Chị Ánh Nhi</t>
   </si>
   <si>
-    <t xml:space="preserve">./images/2024/TRAN_NGUYEN_ANH_NGUYET.jpg
+    <t xml:space="preserve">./data/images/2024/TRAN_NGUYEN_ANH_NGUYET.jpg
 </t>
   </si>
   <si>
@@ -356,7 +356,7 @@
     <t>bạn thân Minh Anh</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_THI_NHAT_ANH.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_NHAT_ANH.jpg</t>
   </si>
   <si>
     <t>Phan Lê Xuân Hiếu (Híu)</t>
@@ -368,7 +368,7 @@
     <t>hihi</t>
   </si>
   <si>
-    <t>./images/2024/PHAN_LE_XUAN_HIEU.jpg</t>
+    <t>./data/images/2024/PHAN_LE_XUAN_HIEU.jpg</t>
   </si>
   <si>
     <t>Lê Thị Huyền Trang (Suu)</t>
@@ -377,7 +377,7 @@
     <t>Người hay cười 😊</t>
   </si>
   <si>
-    <t>./images/2024/LE_THI_HUYEN_TRANG.jpg</t>
+    <t>./data/images/2024/LE_THI_HUYEN_TRANG.jpg</t>
   </si>
   <si>
     <t>Nguyễn Ngọc Thanh Thảo (naaaa)</t>
@@ -386,7 +386,7 @@
     <t>na xinh vứi đôi má hồnggg</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_NGOC_THANH_THAO.jpg</t>
+    <t>./data/images/2024/NGUYEN_NGOC_THANH_THAO.jpg</t>
   </si>
   <si>
     <t>Nguyễn Hoàng Minh Anh (Ma)</t>
@@ -395,7 +395,7 @@
     <t>bạn thân Nhật Anh</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_HOANG_MINH_ANH.jpg</t>
+    <t>./data/images/2024/NGUYEN_HOANG_MINH_ANH.jpg</t>
   </si>
   <si>
     <t>Trương Văn Quý</t>
@@ -407,7 +407,7 @@
     <t>Nhuận Thiền Dũng</t>
   </si>
   <si>
-    <t>./images/2024/TRUONG_VAN_QUY.jpg</t>
+    <t>./data/images/2024/TRUONG_VAN_QUY.jpg</t>
   </si>
   <si>
     <t>Nguyễn Hồ Minh Anh (Manh)</t>
@@ -425,7 +425,7 @@
     <t>Quỳnh Như hihi</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_HOANG_QUYNH_NHU.jpg</t>
+    <t>./data/images/2024/NGUYEN_HOANG_QUYNH_NHU.jpg</t>
   </si>
   <si>
     <t>Nguyễn Văn Phương</t>
@@ -455,7 +455,7 @@
     <t>Cái gì không làm được thì mình vừa khóc vừa làm!</t>
   </si>
   <si>
-    <t>./images/2024/DUONG_THI_NGOC_BICH.jpg</t>
+    <t>./data/images/2024/DUONG_THI_NGOC_BICH.jpg</t>
   </si>
   <si>
     <t>Nguyễn Phúc (Phúc Phúc)</t>
@@ -467,7 +467,7 @@
     <t>Người lái tàu</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_PHUC.jpg</t>
+    <t>./data/images/2024/NGUYEN_PHUC.jpg</t>
   </si>
   <si>
     <t>Đào Gia Hiếu</t>
@@ -500,7 +500,7 @@
     <t>Nhuận Bảo Lộc</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_VAN_LOC.jpg</t>
+    <t>./data/images/2024/NGUYEN_VAN_LOC.jpg</t>
   </si>
   <si>
     <t>Trương Thị Phương Loan</t>
@@ -530,7 +530,7 @@
     <t>dưa hấu không hạt</t>
   </si>
   <si>
-    <t>./images/2024/MAI_THI_THANH_THAO.jpg</t>
+    <t>./data/images/2024/MAI_THI_THANH_THAO.jpg</t>
   </si>
   <si>
     <t>Lê Thị Bích Ngọc</t>
@@ -548,7 +548,7 @@
     <t>Linh</t>
   </si>
   <si>
-    <t>./images/2024/DANG_THI_KHANH_LINH.jpg</t>
+    <t>./data/images/2024/DANG_THI_KHANH_LINH.jpg</t>
   </si>
   <si>
     <t>Lê Thị Băng Nhi</t>
@@ -605,7 +605,7 @@
     <t>Yêu múa ca</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_MAI_THUY_TRAM.jpg</t>
+    <t>./data/images/2024/NGUYEN_MAI_THUY_TRAM.jpg</t>
   </si>
   <si>
     <t>Lê Thị Minh Ngọc</t>
@@ -614,7 +614,7 @@
     <t>Cá nọc</t>
   </si>
   <si>
-    <t>./images/2024/LE_THI_MINH_NGOC.jpg</t>
+    <t>./data/images/2024/LE_THI_MINH_NGOC.jpg</t>
   </si>
   <si>
     <t>Nguyễn Anh Tài (Tài Cris)</t>
@@ -626,7 +626,7 @@
     <t>Siêu đầu bếp Chánh Tâm</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_ANH_TAI.jpg</t>
+    <t>./data/images/2024/NGUYEN_ANH_TAI.jpg</t>
   </si>
   <si>
     <t>Nguyễn Mai Lan</t>
@@ -638,7 +638,7 @@
     <t>hướng nội ít nói</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_MAI_LAN.jpg</t>
+    <t>./data/images/2024/NGUYEN_MAI_LAN.jpg</t>
   </si>
   <si>
     <t>Ngô Vũ Vân Châu (mani - mina)</t>
@@ -647,7 +647,7 @@
     <t>thích chị Nhật Uyên - thích BTT 📷</t>
   </si>
   <si>
-    <t>./images/2024/NGO_VU_VAN_CHAU.jpg</t>
+    <t>./data/images/2024/NGO_VU_VAN_CHAU.jpg</t>
   </si>
   <si>
     <t>Lê Thị Kim Anh (Ka)</t>
@@ -656,7 +656,7 @@
     <t>Chị Ka</t>
   </si>
   <si>
-    <t>./images/2024/LE_THI_KIM_ANH.jpg</t>
+    <t>./data/images/2024/LE_THI_KIM_ANH.jpg</t>
   </si>
   <si>
     <t>Nguyễn Trần Quang Khánh</t>
@@ -680,7 +680,7 @@
     <t>Nhuận Minh</t>
   </si>
   <si>
-    <t>./images/2024/DO_ANH_KIET.jpg</t>
+    <t>./data/images/2024/DO_ANH_KIET.jpg</t>
   </si>
   <si>
     <t>Lê Thị Hồng Hạnh</t>
@@ -695,7 +695,7 @@
     <t>Nhuận Bảoo ✌️</t>
   </si>
   <si>
-    <t>./images/2024/TRAN_NGOC_MINH_CHAU.jpg</t>
+    <t>./data/images/2024/TRAN_NGOC_MINH_CHAU.jpg</t>
   </si>
   <si>
     <t>Phan Uyên Phương (Bơ)</t>
@@ -704,7 +704,7 @@
     <t>hướng nội part time</t>
   </si>
   <si>
-    <t>./images/2024/PHAN_UYEN_PHUONG.jpg</t>
+    <t>./data/images/2024/PHAN_UYEN_PHUONG.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Thu Hồng</t>
@@ -713,13 +713,13 @@
     <t>Hồng</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_THI_THU_HONG.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_THU_HONG.jpg</t>
   </si>
   <si>
     <t>Huỳnh Thị Thu Phương (Pủm)</t>
   </si>
   <si>
-    <t>./images/2024/HUYNH_THI_THU_PHUONG.jpg</t>
+    <t>./data/images/2024/HUYNH_THI_THU_PHUONG.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Uyên Thi</t>
@@ -728,7 +728,7 @@
     <t>Đang học ở Đài Loan</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_THI_UYEN_THI.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_UYEN_THI.jpg</t>
   </si>
   <si>
     <t>Trần Phước Thanh Thanh</t>
@@ -737,13 +737,13 @@
     <t>Nhuận Phước</t>
   </si>
   <si>
-    <t>./images/2024/TRAN_PHUOC_THANH_THANH.jpg</t>
+    <t>./data/images/2024/TRAN_PHUOC_THANH_THANH.jpg</t>
   </si>
   <si>
     <t>Võ Thị Hồng My</t>
   </si>
   <si>
-    <t>./images/2024/VO_THI_HONG_MY.jpg</t>
+    <t>./data/images/2024/VO_THI_HONG_MY.jpg</t>
   </si>
   <si>
     <t>Huỳnh Thị Huê</t>
@@ -755,7 +755,7 @@
     <t>Hay cười 🌱</t>
   </si>
   <si>
-    <t xml:space="preserve">./images/2024/HUYNH_THI_HUE.jpg
+    <t xml:space="preserve">./data/images/2024/HUYNH_THI_HUE.jpg
 </t>
   </si>
   <si>
@@ -765,7 +765,7 @@
     <t>Doanh</t>
   </si>
   <si>
-    <t>./images/2024/TRAN_THIEN_DOANH.jpg</t>
+    <t>./data/images/2024/TRAN_THIEN_DOANH.jpg</t>
   </si>
   <si>
     <t>Nguyễn Tấn Nhật Huy</t>
@@ -774,7 +774,7 @@
     <t>Quảng Đức</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_TAN_NHAT_HUY.jpg</t>
+    <t>./data/images/2024/NGUYEN_TAN_NHAT_HUY.jpg</t>
   </si>
   <si>
     <t>Châu Bảo Anh (May)</t>
@@ -783,7 +783,7 @@
     <t>Vạn Thông</t>
   </si>
   <si>
-    <t xml:space="preserve">./images/2024/CHAU_BAO_ANH.jpg
+    <t xml:space="preserve">./data/images/2024/CHAU_BAO_ANH.jpg
 </t>
   </si>
   <si>
@@ -796,7 +796,7 @@
     <t>Biển Trần</t>
   </si>
   <si>
-    <t>./images/2024/TRAN_HOANG_THANH_HAI.jpg</t>
+    <t>./data/images/2024/TRAN_HOANG_THANH_HAI.jpg</t>
   </si>
   <si>
     <t>Trương Ngọc Hiếu An (Đậu)</t>
@@ -805,7 +805,7 @@
     <t>Đậu Hũ</t>
   </si>
   <si>
-    <t>./images/2024/TRUONG_NGOC_HIEU_AN.jpg</t>
+    <t>./data/images/2024/TRUONG_NGOC_HIEU_AN.jpg</t>
   </si>
   <si>
     <t>Trần Nguyễn Xuân Nghi</t>
@@ -817,7 +817,7 @@
     <t>ngại ngùng</t>
   </si>
   <si>
-    <t>./images/2024/TRAN_NGUYEN_XUAN_NGHI.jpg</t>
+    <t>./data/images/2024/TRAN_NGUYEN_XUAN_NGHI.jpg</t>
   </si>
   <si>
     <t>Nguyễn Đình Nam</t>
@@ -829,7 +829,7 @@
     <t>Ồn nhất Tương Sinh</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_DINH_NAM.jpg</t>
+    <t>./data/images/2024/NGUYEN_DINH_NAM.jpg</t>
   </si>
   <si>
     <t>Hồ Thị Thanh Hiền (Sam)</t>
@@ -841,7 +841,7 @@
     <t>Thanh Hiền</t>
   </si>
   <si>
-    <t>./images/2024/HO_THI_THANH_HIEN.jpg</t>
+    <t>./data/images/2024/HO_THI_THANH_HIEN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Bảo Hưng</t>
@@ -865,7 +865,7 @@
     <t>Nhuận Thường</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_HOANG_DUC.jpg</t>
+    <t>./data/images/2024/NGUYEN_HOANG_DUC.jpg</t>
   </si>
   <si>
     <t>Nguyễn Quốc Việt</t>
@@ -892,7 +892,7 @@
     <t>Bông 🌸</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_THI_QUYNH_NHAN.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_QUYNH_NHAN.jpg</t>
   </si>
   <si>
     <t>Phạm Văn Quốc Tấn</t>
@@ -904,7 +904,7 @@
     <t>Quảng Đạt</t>
   </si>
   <si>
-    <t>./images/2024/PHAM_VAN_QUOC_TAN.jpg</t>
+    <t>./data/images/2024/PHAM_VAN_QUOC_TAN.jpg</t>
   </si>
   <si>
     <t>Phan Văn Đạt</t>
@@ -913,13 +913,13 @@
     <t>Đạt</t>
   </si>
   <si>
-    <t>./images/2024/PHAN_VAN_DAT.jpg</t>
+    <t>./data/images/2024/PHAN_VAN_DAT.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Thu Thảo</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_THI_THU_THAO.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_THU_THAO.jpg</t>
   </si>
   <si>
     <t>Đặng Hoàng Hoài Thư</t>
@@ -928,7 +928,7 @@
     <t>Thực tập Ban chấp hành</t>
   </si>
   <si>
-    <t>./images/2024/DANG_HOANG_HOAI_THU.jpg</t>
+    <t>./data/images/2024/DANG_HOANG_HOAI_THU.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Ánh Tuyết (Út)</t>
@@ -940,7 +940,7 @@
     <t>Nguyên Lan</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_THI_ANH_TUYET.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_ANH_TUYET.jpg</t>
   </si>
   <si>
     <t>Võ Thị Kiều Yến</t>
@@ -952,7 +952,7 @@
     <t>Quãng Ngọc</t>
   </si>
   <si>
-    <t>./images/2024/VO_THI_KIEU_YEN.jpg</t>
+    <t>./data/images/2024/VO_THI_KIEU_YEN.jpg</t>
   </si>
   <si>
     <t>Lê Thị Thu Thuỷ</t>
@@ -964,7 +964,7 @@
     <t>Như Tiên</t>
   </si>
   <si>
-    <t>./images/2024/LE_THI_THU_THUY.jpg</t>
+    <t>./data/images/2024/LE_THI_THU_THUY.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Đăng Nhi</t>
@@ -973,7 +973,7 @@
     <t>Thể Tường</t>
   </si>
   <si>
-    <t>./images/2024/NGUYEN_THI_DANG_NHI.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_DANG_NHI.jpg</t>
   </si>
   <si>
     <t>Đinh Thị Hiếu Thảo (Mắm)</t>
@@ -982,13 +982,13 @@
     <t>Thánh Nhiên</t>
   </si>
   <si>
-    <t>./images/2024/DINH_THI_HIEU_THAO.jpg</t>
+    <t>./data/images/2024/DINH_THI_HIEU_THAO.jpg</t>
   </si>
   <si>
     <t>Huỳnh Thị Kim Ánh</t>
   </si>
   <si>
-    <t>./images/2024/HUYNH_THI_KIM_ANH.jpg</t>
+    <t>./data/images/2024/HUYNH_THI_KIM_ANH.jpg</t>
   </si>
   <si>
     <t>Nguyễn Phan Phước Hải Anh</t>
@@ -1003,7 +1003,7 @@
     <t>Chân Thiện Mỹ</t>
   </si>
   <si>
-    <t>./images/2023/DANG_HOANG_MY_CHAN.jpg</t>
+    <t>./data/images/2023/DANG_HOANG_MY_CHAN.jpg</t>
   </si>
   <si>
     <t>Thân Trọng Quang Dũng</t>
@@ -1015,7 +1015,7 @@
     <t>hoho</t>
   </si>
   <si>
-    <t>./images/2023/THAN_TRONG_QUANG_DUNG.jpg</t>
+    <t>./data/images/2023/THAN_TRONG_QUANG_DUNG.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Duyên (Xô)</t>
@@ -1027,7 +1027,7 @@
     <t>Xô Nguyễn</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_THI_DUYEN.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_DUYEN.jpg</t>
   </si>
   <si>
     <t>Huỳnh Nguyễn Tâm Nhã</t>
@@ -1039,7 +1039,7 @@
     <t>Bộ trưởng bộ ngoại giao</t>
   </si>
   <si>
-    <t>./images/2023/HUYNH_NGUYEN_TAM_NHA.jpg</t>
+    <t>./data/images/2023/HUYNH_NGUYEN_TAM_NHA.jpg</t>
   </si>
   <si>
     <t>Phan Việt Thi (Nhật Diệp)</t>
@@ -1048,7 +1048,7 @@
     <t>Lá được ánh nắng chiếu vào 🌿</t>
   </si>
   <si>
-    <t>./images/2023/PHAN_VIET_THI.jpg</t>
+    <t>./data/images/2023/PHAN_VIET_THI.jpg</t>
   </si>
   <si>
     <t>Lê Huyền Trang</t>
@@ -1057,7 +1057,7 @@
     <t>Hướng nội</t>
   </si>
   <si>
-    <t>./images/2023/LE_HUYEN_TRANG.jpg</t>
+    <t>./data/images/2023/LE_HUYEN_TRANG.jpg</t>
   </si>
   <si>
     <t>Hoàng Thị Diệu Ái</t>
@@ -1072,7 +1072,7 @@
     <t>Hậu cần khó - có chị Ái</t>
   </si>
   <si>
-    <t>./images/2023/HOANG_THI_DIEU_AI.jpg</t>
+    <t>./data/images/2023/HOANG_THI_DIEU_AI.jpg</t>
   </si>
   <si>
     <t>Phạm Hoàng Anh</t>
@@ -1081,7 +1081,7 @@
     <t>Hoàng Anh</t>
   </si>
   <si>
-    <t>./images/2023/PHAM_HOANG_ANH.jpg</t>
+    <t>./data/images/2023/PHAM_HOANG_ANH.jpg</t>
   </si>
   <si>
     <t>Nguyễn Ngọc Kỳ Duyên</t>
@@ -1090,7 +1090,7 @@
     <t>🍓</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_NGOC_KY_DUYEN.jpg</t>
+    <t>./data/images/2023/NGUYEN_NGOC_KY_DUYEN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Xuân Quỳnh Anh (Cuộn Len)</t>
@@ -1099,7 +1099,7 @@
     <t>giao diện 1 đằng, hệ điều hành 1 nẻo</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_XUAN_QUYNH_ANH.jpg</t>
+    <t>./data/images/2023/NGUYEN_XUAN_QUYNH_ANH.jpg</t>
   </si>
   <si>
     <t>Võ Nguyễn Minh Châu</t>
@@ -1108,7 +1108,7 @@
     <t>Introvert 🥹</t>
   </si>
   <si>
-    <t>./images/2023/VO_NGUYEN_MINH_CHAU.jpg</t>
+    <t>./data/images/2023/VO_NGUYEN_MINH_CHAU.jpg</t>
   </si>
   <si>
     <t>Lê Ngọc Giản Đơn</t>
@@ -1120,7 +1120,7 @@
     <t>cô bé phức tạp</t>
   </si>
   <si>
-    <t>./images/2023/LE_NGOC_GIAN_DON.jpg</t>
+    <t>./data/images/2023/LE_NGOC_GIAN_DON.jpg</t>
   </si>
   <si>
     <t>Trần Nhật Lai</t>
@@ -1132,7 +1132,7 @@
     <t>Muốn được iu thưn🫶</t>
   </si>
   <si>
-    <t>./images/2023/TRAN_NHAT_LAI.jpg</t>
+    <t>./data/images/2023/TRAN_NHAT_LAI.jpg</t>
   </si>
   <si>
     <t>Phan Thị Quỳnh Trâm</t>
@@ -1141,7 +1141,7 @@
     <t>Quỳnh Trâm</t>
   </si>
   <si>
-    <t>./images/2023/PHAN_THI_QUYNH_TRAM.jpg</t>
+    <t>./data/images/2023/PHAN_THI_QUYNH_TRAM.jpg</t>
   </si>
   <si>
     <t>Lê Thị Diệu Trinh</t>
@@ -1150,7 +1150,7 @@
     <t>Lặng lẽ học tập, rèn luyện thân tâm</t>
   </si>
   <si>
-    <t>./images/2023/LE_THI_DIEU_TRINH.jpg</t>
+    <t>./data/images/2023/LE_THI_DIEU_TRINH.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Tống Hồ Trần Tuyền </t>
@@ -1162,7 +1162,7 @@
     <t>bún đậu muối tiêu</t>
   </si>
   <si>
-    <t>./images/2023/TONG_HO_TRAN_TUYEN.jpg</t>
+    <t>./data/images/2023/TONG_HO_TRAN_TUYEN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Như Ý (Nhã Đan)</t>
@@ -1171,7 +1171,7 @@
     <t>Tẻn tẻn</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_THI_NHU_Y.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_NHU_Y.jpg</t>
   </si>
   <si>
     <t>Đoàn Đại Trung Nguyên (Đức Phúc)</t>
@@ -1183,7 +1183,7 @@
     <t>Nhuận Bình</t>
   </si>
   <si>
-    <t>./images/2023/DAI_DOAN_TRUNG_NGUYEN.jpg</t>
+    <t>./data/images/2023/DAI_DOAN_TRUNG_NGUYEN.jpg</t>
   </si>
   <si>
     <t>Hồ Văn Quốc Huy</t>
@@ -1198,13 +1198,13 @@
     <t>Quỳnh</t>
   </si>
   <si>
-    <t>./images/2023/LE_NGUYEN_DIEM_QUYNH.jpg</t>
+    <t>./data/images/2023/LE_NGUYEN_DIEM_QUYNH.jpg</t>
   </si>
   <si>
     <t>Lê Thảo Nguyên (Ốc iu)</t>
   </si>
   <si>
-    <t>./images/2023/LE_THAO_NGUYEN.jpg</t>
+    <t>./data/images/2023/LE_THAO_NGUYEN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Thu Ngân</t>
@@ -1216,7 +1216,7 @@
     <t>Quảng Diệu</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_THI_THU_NGAN.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_THU_NGAN.jpg</t>
   </si>
   <si>
     <t>Phan Thị Hương Giang</t>
@@ -1228,7 +1228,7 @@
     <t>Nà Ná</t>
   </si>
   <si>
-    <t>./images/2023/PHAN_THI_HUONG_GIANG.jpg</t>
+    <t>./data/images/2023/PHAN_THI_HUONG_GIANG.jpg</t>
   </si>
   <si>
     <t>Phùng Uyển Cát Tiên</t>
@@ -1237,7 +1237,7 @@
     <t>Nhuận Hoàng</t>
   </si>
   <si>
-    <t>./images/2023/PHUNG_UYEN_CAT_TIEN.jpg</t>
+    <t>./data/images/2023/PHUNG_UYEN_CAT_TIEN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Huỳnh Thanh</t>
@@ -1249,7 +1249,7 @@
     <t>Má hồng 😳</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_THI_HUYNH_THANH.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_HUYNH_THANH.jpg</t>
   </si>
   <si>
     <t>Nguyễn Anh Quân</t>
@@ -1261,7 +1261,7 @@
     <t>Quảng Nam</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_ANH_QUAN.jpg</t>
+    <t>./data/images/2023/NGUYEN_ANH_QUAN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Thuỳ</t>
@@ -1270,7 +1270,7 @@
     <t>Thuỳ</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_THI_THUY.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_THUY.jpg</t>
   </si>
   <si>
     <t>Lê Văn Nhất Vạn (Mười)</t>
@@ -1282,13 +1282,13 @@
     <t>Nhuận Từ</t>
   </si>
   <si>
-    <t>./images/2023/LE_VAN_NHAT_VAN.jpg</t>
+    <t>./data/images/2023/LE_VAN_NHAT_VAN.jpg</t>
   </si>
   <si>
     <t>Đỗ Thị Thu Thảo</t>
   </si>
   <si>
-    <t>./images/2023/DO_THI_THU_THAO.jpg</t>
+    <t>./data/images/2023/DO_THI_THU_THAO.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thành Tâm</t>
@@ -1297,7 +1297,7 @@
     <t>Tâm</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_THANH_TAM.jpg</t>
+    <t>./data/images/2023/NGUYEN_THANH_TAM.jpg</t>
   </si>
   <si>
     <t>Đặng Thị Lượm (Dalu)</t>
@@ -1309,7 +1309,7 @@
     <t>Quảng Tích</t>
   </si>
   <si>
-    <t>./images/2023/DANG_THI_LUOM.jpg</t>
+    <t>./data/images/2023/DANG_THI_LUOM.jpg</t>
   </si>
   <si>
     <t>Hà Văn Triều</t>
@@ -1321,7 +1321,7 @@
     <t>Mất tích</t>
   </si>
   <si>
-    <t>./images/2023/HA_VAN_TRIEU.jpg</t>
+    <t>./data/images/2023/HA_VAN_TRIEU.jpg</t>
   </si>
   <si>
     <t>Lê Châu Tường Minh</t>
@@ -1330,7 +1330,7 @@
     <t>Quảng Chuyên</t>
   </si>
   <si>
-    <t>./images/2023/LE_CHAU_TUONG_MINH.jpg</t>
+    <t>./data/images/2023/LE_CHAU_TUONG_MINH.jpg</t>
   </si>
   <si>
     <t>Lê Thảo Vân</t>
@@ -1339,7 +1339,7 @@
     <t>Nguyên Tâm</t>
   </si>
   <si>
-    <t>./images/2023/LE_THAO_VAN.jpg</t>
+    <t>./data/images/2023/LE_THAO_VAN.jpg</t>
   </si>
   <si>
     <t>Ngô Trần Thị Thu Đông</t>
@@ -1351,7 +1351,7 @@
     <t>⛄</t>
   </si>
   <si>
-    <t>./images/2023/NGO_TRAN_THU_DONG.jpg</t>
+    <t>./data/images/2023/NGO_TRAN_THU_DONG.jpg</t>
   </si>
   <si>
     <t>Nguyễn Đức Nghĩa</t>
@@ -1363,7 +1363,7 @@
     <t>Nguyên Nhân</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_DUC_NGHIA.jpg</t>
+    <t>./data/images/2023/NGUYEN_DUC_NGHIA.jpg</t>
   </si>
   <si>
     <t>Nguyễn Hải Cương</t>
@@ -1384,7 +1384,7 @@
     <t>Quảng Liên Kiều</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_THI_THANH_PHUONG.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_THANH_PHUONG.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Thanh Thảo</t>
@@ -1393,7 +1393,7 @@
     <t>Tâm Phương</t>
   </si>
   <si>
-    <t>./images/2023/NGUYEN_THI_THANH_THAO.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_THANH_THAO.jpg</t>
   </si>
   <si>
     <t>Phạm Khánh Quỳnh</t>
@@ -1402,13 +1402,13 @@
     <t>Nguyên An</t>
   </si>
   <si>
-    <t>./images/2023/PHAM_KHANH_QUYNH.jpg</t>
+    <t>./data/images/2023/PHAM_KHANH_QUYNH.jpg</t>
   </si>
   <si>
     <t>Trần Hoàng Phương Linh</t>
   </si>
   <si>
-    <t>./images/2023/TRAN_HOANG_PHUONG_LINH.jpg</t>
+    <t>./data/images/2023/TRAN_HOANG_PHUONG_LINH.jpg</t>
   </si>
   <si>
     <t>Trần Thị Ly (lixinh)</t>
@@ -1417,7 +1417,7 @@
     <t>Ly</t>
   </si>
   <si>
-    <t>./images/2023/TRAN_THI_LY.jpg</t>
+    <t>./data/images/2023/TRAN_THI_LY.jpg</t>
   </si>
   <si>
     <t>Trương Nguyễn Bảo Trân</t>
@@ -1441,7 +1441,7 @@
     <t>Tống Thị Mỹ Nhi</t>
   </si>
   <si>
-    <t>./images/2023/TONG_MY_NHI.jpg</t>
+    <t>./data/images/2023/TONG_MY_NHI.jpg</t>
   </si>
   <si>
     <t>Trương Huyên Chương</t>
@@ -1453,13 +1453,13 @@
     <t>Nhuận Pháp</t>
   </si>
   <si>
-    <t>./images/2023/TRUONG_HUYEN_CHUONG.jpg</t>
+    <t>./data/images/2023/TRUONG_HUYEN_CHUONG.jpg</t>
   </si>
   <si>
     <t>Phạm Trương Bảo Hoàng (Kem)</t>
   </si>
   <si>
-    <t>./images/2023/PHAM_TRUONG_BAO_HOANG.jpg</t>
+    <t>./data/images/2023/PHAM_TRUONG_BAO_HOANG.jpg</t>
   </si>
   <si>
     <t>Phan Thị Phương Anh (Sô)</t>
@@ -1471,7 +1471,7 @@
     <t>Sony Phan</t>
   </si>
   <si>
-    <t>./images/2022/PHAN_THI_PHUONG_ANH.jpg</t>
+    <t>./data/images/2022/PHAN_THI_PHUONG_ANH.jpg</t>
   </si>
   <si>
     <t>Trần Thị Hà (Trần Hà)</t>
@@ -1483,7 +1483,7 @@
     <t>Quảng Hồng</t>
   </si>
   <si>
-    <t>./images/2022/TRAN_THI_HA.jpg</t>
+    <t>./data/images/2022/TRAN_THI_HA.jpg</t>
   </si>
   <si>
     <t>Nguyễn Hồ Thảo Nhi (Pho)</t>
@@ -1492,7 +1492,7 @@
     <t>trong veo</t>
   </si>
   <si>
-    <t>./images/2022/NGUYEN_HO_THAO_NHI.jpg</t>
+    <t>./data/images/2022/NGUYEN_HO_THAO_NHI.jpg</t>
   </si>
   <si>
     <t>Trần  Thị Như Giao</t>
@@ -1504,7 +1504,7 @@
     <t>Tử tế</t>
   </si>
   <si>
-    <t>./images/2022/TRAN_THI_NHU_GIAO.jpg</t>
+    <t>./data/images/2022/TRAN_THI_NHU_GIAO.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Ngọc Ánh (Énn énnnnn)</t>
@@ -1516,7 +1516,7 @@
     <t>Mặt trời nhỏo</t>
   </si>
   <si>
-    <t>./images/2022/NGUYEN_THI_NGOC_ANH.jpg</t>
+    <t>./data/images/2022/NGUYEN_THI_NGOC_ANH.jpg</t>
   </si>
   <si>
     <t>Hồ Thị Châu Linh</t>
@@ -1528,7 +1528,7 @@
     <t>Cá thích chơi</t>
   </si>
   <si>
-    <t>./images/2022/HO_THI_CHAU_LINH.jpg</t>
+    <t>./data/images/2022/HO_THI_CHAU_LINH.jpg</t>
   </si>
   <si>
     <t>Dương Thị Thu Huyền</t>
@@ -1540,7 +1540,7 @@
     <t>&lt;b&gt;𝘽𝙚 𝙮𝙤𝙪𝙧𝙨𝙚𝙡𝙛, 𝙙𝙤𝙣'𝙩 𝙗𝙚 𝙖𝙣𝙮𝙤𝙣𝙚 𝙚𝙡𝙨𝙚&lt;/b&gt;</t>
   </si>
   <si>
-    <t>./images/2022/DUONG_THI_THU_HUYEN.jpg</t>
+    <t>./data/images/2022/DUONG_THI_THU_HUYEN.jpg</t>
   </si>
   <si>
     <t>Hoàng Hữu Tuấn Vũ (TVũ 4S)</t>
@@ -1555,7 +1555,7 @@
     <t>Sống chỉ đơn giản - lấy nụ cười làm căn bản</t>
   </si>
   <si>
-    <t>./images/2022/HOANG_HUU_TUAN_VU.jpg</t>
+    <t>./data/images/2022/HOANG_HUU_TUAN_VU.jpg</t>
   </si>
   <si>
     <t>Trần Phương Nam (Nhuận Tường)</t>
@@ -1564,7 +1564,7 @@
     <t>Hiện tại mình đang sống ẩn</t>
   </si>
   <si>
-    <t>./images/2022/TRAN_PHUONG_NAM.jpg</t>
+    <t>./data/images/2022/TRAN_PHUONG_NAM.jpg</t>
   </si>
   <si>
     <t>Võ Hồng Đức (Mai Cồ Phước Duyên)</t>
@@ -1573,7 +1573,7 @@
     <t>Hậu cần, Diễn kịch và Nước mía</t>
   </si>
   <si>
-    <t>./images/2022/VO_HONG_DUC.jpg</t>
+    <t>./data/images/2022/VO_HONG_DUC.jpg</t>
   </si>
   <si>
     <t>Nguyễn Đức Nguyên Thông (Thúng)</t>
@@ -1588,7 +1588,7 @@
     <t>Thở là ra thơ</t>
   </si>
   <si>
-    <t>./images/2022/NGUYEN_DUC_NGUYEN_THONG.jpg</t>
+    <t>./data/images/2022/NGUYEN_DUC_NGUYEN_THONG.jpg</t>
   </si>
   <si>
     <t>Đậu Đoàn Hoàn Mỹ (Mỵ Mỵ)</t>
@@ -1603,7 +1603,7 @@
     <t>Nhỏ mà có võ</t>
   </si>
   <si>
-    <t>./images/2022/DAU_DOAN_HOAN_MY.jpg</t>
+    <t>./data/images/2022/DAU_DOAN_HOAN_MY.jpg</t>
   </si>
   <si>
     <t>Lê  Thị Ngọc</t>
@@ -1618,7 +1618,7 @@
     <t>Quảng Thuần</t>
   </si>
   <si>
-    <t>./images/2022/LE_THI_THANH_NHAN.jpg</t>
+    <t>./data/images/2022/LE_THI_THANH_NHAN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Văn Rin</t>
@@ -1630,13 +1630,13 @@
     <t>Nguyện Thành</t>
   </si>
   <si>
-    <t>./images/2022/NGUYEN_VAN_RIN.jpg</t>
+    <t>./data/images/2022/NGUYEN_VAN_RIN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Mỹ Duyên</t>
   </si>
   <si>
-    <t>./images/2022/NGUYEN_THI_MY_DUYEN.jpg</t>
+    <t>./data/images/2022/NGUYEN_THI_MY_DUYEN.jpg</t>
   </si>
   <si>
     <t>Châu Phước Nhật</t>
@@ -1648,7 +1648,7 @@
     <t>Nhuận Tuệ</t>
   </si>
   <si>
-    <t>./images/2022/CHAU_PHUOC_NHAT.jpg</t>
+    <t>./data/images/2022/CHAU_PHUOC_NHAT.jpg</t>
   </si>
   <si>
     <t>Trần Như Nhã Kỳ</t>
@@ -1657,7 +1657,7 @@
     <t>Kỳ</t>
   </si>
   <si>
-    <t>./images/2022/TRAN_NHU_NHA_KY.jpg</t>
+    <t>./data/images/2022/TRAN_NHU_NHA_KY.jpg</t>
   </si>
   <si>
     <t>Lê Thị Diễm My (Mymyno)</t>
@@ -1666,19 +1666,19 @@
     <t>Nhuận Hiền</t>
   </si>
   <si>
-    <t>./images/2022/LE_THI_DIEM_MY.jpg</t>
+    <t>./data/images/2022/LE_THI_DIEM_MY.jpg</t>
   </si>
   <si>
     <t>Dương Thị Thanh Tâm</t>
   </si>
   <si>
-    <t>./images/2022/DUONG_THI_THANH_TAM.jpg</t>
+    <t>./data/images/2022/DUONG_THI_THANH_TAM.jpg</t>
   </si>
   <si>
     <t>Hồ Thị Thảo Tiên</t>
   </si>
   <si>
-    <t>./images/2022/HO_THI_THAO_TIEN.jpg</t>
+    <t>./data/images/2022/HO_THI_THAO_TIEN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Kim Tuyến</t>
@@ -1693,7 +1693,7 @@
     <t>Đào Thị Bích Thảo</t>
   </si>
   <si>
-    <t>./images/2022/DAO_THI_BICH_THAO.jpg</t>
+    <t>./data/images/2022/DAO_THI_BICH_THAO.jpg</t>
   </si>
   <si>
     <t>Hồ Thị Thanh Hiền</t>
@@ -1702,7 +1702,7 @@
     <t>Nhuận Đức</t>
   </si>
   <si>
-    <t>./images/2022/HO_THI_THANH_HIEN.jpg</t>
+    <t>./data/images/2022/HO_THI_THANH_HIEN.jpg</t>
   </si>
   <si>
     <t>Lê Thị Xuân Nhàn (Nhàn Lee)</t>
@@ -1711,7 +1711,7 @@
     <t>Mình đây tuy chẳng cao sang. Chỉ mong cố gắng, vững vàng mai sau</t>
   </si>
   <si>
-    <t>./images/2022/LE_THI_XUAN_NHAN.jpg</t>
+    <t>./data/images/2022/LE_THI_XUAN_NHAN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Diệp Linh (Nhỏ)</t>
@@ -1720,7 +1720,7 @@
     <t>smile</t>
   </si>
   <si>
-    <t>./images/2022/NGUYEN_THI_DIEP_LINH.jpg</t>
+    <t>./data/images/2022/NGUYEN_THI_DIEP_LINH.jpg</t>
   </si>
   <si>
     <t>Lê Thị Kim Ngân</t>
@@ -1729,7 +1729,7 @@
     <t>Photo girl</t>
   </si>
   <si>
-    <t>./images/2021/LE_THI_KIM_NGAN.jpg</t>
+    <t>./data/images/2021/LE_THI_KIM_NGAN.jpg</t>
   </si>
   <si>
     <t>Bạch Thị Thu Thảo (Tabi)</t>
@@ -1741,7 +1741,7 @@
     <t>Thảo Tabi</t>
   </si>
   <si>
-    <t>./images/2021/BACH_THI_THU_THAO.jpg</t>
+    <t>./data/images/2021/BACH_THI_THU_THAO.jpg</t>
   </si>
   <si>
     <t>Nguyễn Khánh Hà</t>
@@ -1750,7 +1750,7 @@
     <t>oyoui</t>
   </si>
   <si>
-    <t>./images/2021/NGUYEN_KHANH_HA.jpg</t>
+    <t>./data/images/2021/NGUYEN_KHANH_HA.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Nhật Trâm (Na)</t>
@@ -1759,7 +1759,7 @@
     <t>Nhat Tram</t>
   </si>
   <si>
-    <t>./images/2021/NGUYEN_THI_NHAT_TRAM.jpg</t>
+    <t>./data/images/2021/NGUYEN_THI_NHAT_TRAM.jpg</t>
   </si>
   <si>
     <t>Trần Thị Quỳnh Phương</t>
@@ -1771,7 +1771,7 @@
     <t>Mãi yêu Chánh Tâm</t>
   </si>
   <si>
-    <t>./images/2021/TRAN_THI_QUYNH_PHUONG.jpg</t>
+    <t>./data/images/2021/TRAN_THI_QUYNH_PHUONG.jpg</t>
   </si>
   <si>
     <t>Phan Thị Cẩm Nhi (Nhem cute)</t>
@@ -1783,7 +1783,7 @@
     <t>Nhuận Hỷ</t>
   </si>
   <si>
-    <t>./images/2021/PHAN_THI_CAM_NHI.jpg</t>
+    <t>./data/images/2021/PHAN_THI_CAM_NHI.jpg</t>
   </si>
   <si>
     <t>Nguyễn Văn Hồng Ngọc (Right)</t>
@@ -1810,7 +1810,7 @@
     <t>Nhật Uyên xinh đẹp</t>
   </si>
   <si>
-    <t>./images/2020/NGUYEN_NHAT_UYEN.jpg</t>
+    <t>./data/images/2020/NGUYEN_NHAT_UYEN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Nhật Linh</t>
@@ -1819,7 +1819,7 @@
     <t>Bớt nghe, bớt nói, bớt nhìn. Giữ tâm thanh tịnh mới là thảnh thơi.</t>
   </si>
   <si>
-    <t>./images/2020/NGUYEN_NHAT_LINH.jpg</t>
+    <t>./data/images/2020/NGUYEN_NHAT_LINH.jpg</t>
   </si>
   <si>
     <t>Trần Xuân Trung</t>
@@ -1834,7 +1834,7 @@
     <t>Nhuận Niệm</t>
   </si>
   <si>
-    <t>./images/2020/NGUYEN_THI_MY_NHAN.jpg</t>
+    <t>./data/images/2020/NGUYEN_THI_MY_NHAN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Đăng Huy</t>
@@ -1843,7 +1843,7 @@
     <t>Chú Huy</t>
   </si>
   <si>
-    <t>./images/2020/NGUYEN_DANG_HUY.jpg</t>
+    <t>./data/images/2020/NGUYEN_DANG_HUY.jpg</t>
   </si>
   <si>
     <t>Hoàng Giang (Long Ka)</t>
@@ -1852,7 +1852,7 @@
     <t>Kết nối - Nhiệt tình - Vui vẻ - Hoà đồng</t>
   </si>
   <si>
-    <t>./images/2020/HOANG_GIANG.jpg</t>
+    <t>./data/images/2020/HOANG_GIANG.jpg</t>
   </si>
   <si>
     <t>Nguyễn Bá Quốc</t>
@@ -1873,7 +1873,7 @@
     <t>Banh</t>
   </si>
   <si>
-    <t>./images/2020/DINH_THI_NGOC_ANH.jpg</t>
+    <t>./data/images/2020/DINH_THI_NGOC_ANH.jpg</t>
   </si>
   <si>
     <t>Nguyễn Hoàng Kiều Anh</t>
@@ -1882,7 +1882,7 @@
     <t>Quang Tú</t>
   </si>
   <si>
-    <t>./images/2020/NGUYEN_HOANG_KIEU_ANH.jpg</t>
+    <t>./data/images/2020/NGUYEN_HOANG_KIEU_ANH.jpg</t>
   </si>
   <si>
     <t>Đoàn Thị Thu Hà</t>
@@ -1891,7 +1891,7 @@
     <t>Cô gái Huế hay cười</t>
   </si>
   <si>
-    <t>./images/2020/DOAN_THI_THU_HA.jpg</t>
+    <t>./data/images/2020/DOAN_THI_THU_HA.jpg</t>
   </si>
   <si>
     <t>Lê Thị Thuận Hóa</t>
@@ -1906,7 +1906,7 @@
     <t>Nàng thơ cây cỏ</t>
   </si>
   <si>
-    <t>./images/2019/LE_THI_THUAN_HOA.jpg</t>
+    <t>./data/images/2019/LE_THI_THUAN_HOA.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Như Ngọc</t>
@@ -1918,7 +1918,7 @@
     <t>Quảng Lan</t>
   </si>
   <si>
-    <t>./images/2019/NGUYEN_THI_NHU_NGOC.jpg</t>
+    <t>./data/images/2019/NGUYEN_THI_NHU_NGOC.jpg</t>
   </si>
   <si>
     <t>Ngô Thị Bảo Trân</t>
@@ -1942,7 +1942,7 @@
     <t>Quảng Tịnh</t>
   </si>
   <si>
-    <t>./images/2019/NGUYEN_THI_THANH_HIEN.jpg</t>
+    <t>./data/images/2019/NGUYEN_THI_THANH_HIEN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Kính Nghĩa (Bin)</t>
@@ -1951,7 +1951,7 @@
     <t>Quảng Trung</t>
   </si>
   <si>
-    <t>./images/2019/NGUYEN_KINH_NGHIA.jpg</t>
+    <t>./data/images/2019/NGUYEN_KINH_NGHIA.jpg</t>
   </si>
   <si>
     <t>Lê Đình Hùng</t>
@@ -1975,7 +1975,7 @@
     <t>vuýp</t>
   </si>
   <si>
-    <t>./images/2018/PHAN_VU_PHUC_DUONG.jpg</t>
+    <t>./data/images/2018/PHAN_VU_PHUC_DUONG.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Xuân Mai</t>
@@ -1987,7 +1987,7 @@
     <t>Quảng Trang</t>
   </si>
   <si>
-    <t>./images/2018/NGUYEN_THI_XUAN_MAI.jpg</t>
+    <t>./data/images/2018/NGUYEN_THI_XUAN_MAI.jpg</t>
   </si>
   <si>
     <t>Lê Văn Anh Hào</t>
@@ -2002,7 +2002,7 @@
     <t>Quảng Châu</t>
   </si>
   <si>
-    <t>./images/2018/NGUYEN_LE_HONG_NGOC.jpg</t>
+    <t>./data/images/2018/NGUYEN_LE_HONG_NGOC.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Thanh Phương (Bơ nhỏ)</t>
@@ -2011,7 +2011,7 @@
     <t>Quảng Mỹ</t>
   </si>
   <si>
-    <t>./images/2018/NGUYEN_THI_THANH_PHUONG.jpg</t>
+    <t>./data/images/2018/NGUYEN_THI_THANH_PHUONG.jpg</t>
   </si>
   <si>
     <t>Ngô Thị Băng Châu (Bắp)</t>
@@ -2020,7 +2020,7 @@
     <t>Nhuận Thảo</t>
   </si>
   <si>
-    <t>./images/2018/NGO_THI_BANG_CHAU.jpg</t>
+    <t>./data/images/2018/NGO_THI_BANG_CHAU.jpg</t>
   </si>
   <si>
     <t>Lê Đức Duy</t>
@@ -2032,7 +2032,7 @@
     <t>Duyy BUỒN NGẨU</t>
   </si>
   <si>
-    <t>./images/2017/LE_DUC_DUY.jpg</t>
+    <t>./data/images/2017/LE_DUC_DUY.jpg</t>
   </si>
   <si>
     <t>Lý Thanh Tùng (Tbh)</t>
@@ -2047,7 +2047,7 @@
     <t>&lt;a href="https://lythanhtung-github.github.io/chanhtamwtbh/" target="_blank"&gt;🎨🌧️🎧&lt;/a&gt;</t>
   </si>
   <si>
-    <t>./images/2017/LY_THANH_TUNG.jpg</t>
+    <t>./data/images/2017/LY_THANH_TUNG.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Lai (Lai Lụt)</t>
@@ -2056,7 +2056,7 @@
     <t>Lai Thị Lụtt</t>
   </si>
   <si>
-    <t>./images/2017/NGUYEN_THI_LAI.jpg</t>
+    <t>./data/images/2017/NGUYEN_THI_LAI.jpg</t>
   </si>
   <si>
     <t>Lê Văn Huy (Huy Lê)</t>
@@ -2068,7 +2068,7 @@
     <t>&lt;s&gt;yesterday&lt;/s&gt; NOW &lt;del&gt;tomorrow&lt;/del&gt;</t>
   </si>
   <si>
-    <t>./images/2017/LE_VAN_HUY.jpg</t>
+    <t>./data/images/2017/LE_VAN_HUY.jpg</t>
   </si>
   <si>
     <t>Phan Đình Thành Nhân</t>
@@ -2080,7 +2080,7 @@
     <t>Cu em</t>
   </si>
   <si>
-    <t>./images/2017/PHAN_DINH_THANH_NHAN.jpg</t>
+    <t>./data/images/2017/PHAN_DINH_THANH_NHAN.jpg</t>
   </si>
   <si>
     <t>Trần Văn Quốc (Bi)</t>
@@ -2089,7 +2089,7 @@
     <t>Quảng Bảo</t>
   </si>
   <si>
-    <t>./images/2017/TRAN_QUOC.jpg</t>
+    <t>./data/images/2017/TRAN_QUOC.jpg</t>
   </si>
   <si>
     <t>Nguyễn Đăng Hoàng Phúc (Bun)</t>
@@ -2101,7 +2101,7 @@
     <t>Nhuận Hạnh</t>
   </si>
   <si>
-    <t>./images/2017/NGUYEN_DANG_HOANG_PHUC.jpg</t>
+    <t>./data/images/2017/NGUYEN_DANG_HOANG_PHUC.jpg</t>
   </si>
   <si>
     <t>Đặng Thanh Hương (Na)</t>
@@ -2113,7 +2113,7 @@
     <t>🍈</t>
   </si>
   <si>
-    <t>./images/2017/DANG_THANH_HUONG.jpg</t>
+    <t>./data/images/2017/DANG_THANH_HUONG.jpg</t>
   </si>
   <si>
     <t>Trần Thị Lành (Xíu)</t>
@@ -2125,7 +2125,7 @@
     <t>Nhuận Hải Tâm</t>
   </si>
   <si>
-    <t>./images/2016/TRAN_THI_LANH.jpg</t>
+    <t>./data/images/2016/TRAN_THI_LANH.jpg</t>
   </si>
   <si>
     <t>Lê Thị Nhật (Nước Lọc)</t>
@@ -2137,7 +2137,7 @@
     <t>Biết ơn - Tĩnh lặng</t>
   </si>
   <si>
-    <t>./images/2015/LE_THI_NHAT.jpg</t>
+    <t>./data/images/2015/LE_THI_NHAT.jpg</t>
   </si>
   <si>
     <t>Đỗ Văn Tuấn</t>
@@ -2149,7 +2149,7 @@
     <t>Nhuận Tú Minh</t>
   </si>
   <si>
-    <t>./images/2015/DO_VAN_TUAN.jpg</t>
+    <t>./data/images/2015/DO_VAN_TUAN.jpg</t>
   </si>
   <si>
     <t>Hồ Tâm Nguyên (Nguyên Hồ)</t>
@@ -2162,7 +2162,7 @@
     <t>Người anh sâu sắc</t>
   </si>
   <si>
-    <t>./images/2014/HO_TAM_NGUYEN.jpg</t>
+    <t>./data/images/2014/HO_TAM_NGUYEN.jpg</t>
   </si>
   <si>
     <t>Lê Linh Đài</t>
@@ -2189,7 +2189,7 @@
     <t>Mặt hơi nhiều râu</t>
   </si>
   <si>
-    <t>./images/2012/TRUONG_MINH_Y.webp</t>
+    <t>./data/images/2012/TRUONG_MINH_Y.webp</t>
   </si>
   <si>
     <t>Định Hưng (Toni)</t>
@@ -2201,7 +2201,7 @@
     <t>Toni Định</t>
   </si>
   <si>
-    <t>./images/2012/DINH_HUNG.webp</t>
+    <t>./data/images/2012/DINH_HUNG.webp</t>
   </si>
   <si>
     <t>Trương Thị Phương Anh (Bơ Cena)</t>
@@ -2210,7 +2210,7 @@
     <t>Chị Bơ</t>
   </si>
   <si>
-    <t>./images/2012/TRUONG_THI_PHUONG_ANH.webp</t>
+    <t>./data/images/2012/TRUONG_THI_PHUONG_ANH.webp</t>
   </si>
   <si>
     <t>Lê Thị Bích Tiên</t>
@@ -2219,7 +2219,7 @@
     <t>Giọng to nhất Chánh Tâm</t>
   </si>
   <si>
-    <t>./images/2012/LE_THI_BICH_TIEN.webp</t>
+    <t>./data/images/2012/LE_THI_BICH_TIEN.webp</t>
   </si>
   <si>
     <t>Tống Văn Hùng</t>
@@ -2228,7 +2228,7 @@
     <t>Hùng hóm hỉnh</t>
   </si>
   <si>
-    <t>./images/2011/TONG_VAN_HUNG.webp</t>
+    <t>./data/images/2011/TONG_VAN_HUNG.webp</t>
   </si>
   <si>
     <t>Trương Thị Kim Chi (Xuxuchichi)</t>
@@ -2240,7 +2240,7 @@
     <t>Cô dâu Chi</t>
   </si>
   <si>
-    <t>./images/2011/TRUONG_THI_KIM_CHI.webp</t>
+    <t>./data/images/2011/TRUONG_THI_KIM_CHI.webp</t>
   </si>
   <si>
     <t>Trương Thị Kim Cương</t>
@@ -2249,7 +2249,7 @@
     <t>Mẹ Khoai, Đậu, Dâu Tây</t>
   </si>
   <si>
-    <t>./images/2011/TRUONG_THI_KIM_CUONG.webp</t>
+    <t>./data/images/2011/TRUONG_THI_KIM_CUONG.webp</t>
   </si>
   <si>
     <t>Hồ Thị Diệu Thảo (Bông)</t>
@@ -2258,7 +2258,7 @@
     <t>Tâm Thuận</t>
   </si>
   <si>
-    <t>./images/2011/HO_THI_DIEU_THAO.webp</t>
+    <t>./data/images/2011/HO_THI_DIEU_THAO.webp</t>
   </si>
   <si>
     <t>Phan Thị Thanh Hồng</t>
@@ -2267,7 +2267,7 @@
     <t>Quảng Tuyết</t>
   </si>
   <si>
-    <t>./images/2011/PHAN_THI_THANH_HONG.webp</t>
+    <t>./data/images/2011/PHAN_THI_THANH_HONG.webp</t>
   </si>
   <si>
     <t>full_name 2010</t>
@@ -2285,7 +2285,7 @@
     <t>Mẹ Chánh Tâm</t>
   </si>
   <si>
-    <t>./images/NO/CHAU_LIEN_PHUONG.jpg</t>
+    <t>./data/images/NO/CHAU_LIEN_PHUONG.jpg</t>
   </si>
   <si>
     <t>Hà Thị Thu</t>
@@ -2297,7 +2297,7 @@
     <t>Hoàng Thị Xuân Vân</t>
   </si>
   <si>
-    <t>./images/NO/HOANG_THI_XUAN_VAN.jpg</t>
+    <t>./data/images/NO/HOANG_THI_XUAN_VAN.jpg</t>
   </si>
   <si>
     <t>Huỳnh Thị Kim Anh</t>
@@ -2315,7 +2315,7 @@
     <t>Lê Thị Huyền Ngân (Mắm)</t>
   </si>
   <si>
-    <t>./images/NO/LE_THI_HUYEN_NGAN.jpg</t>
+    <t>./data/images/NO/LE_THI_HUYEN_NGAN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Hữu Khánh Toàn</t>
@@ -2324,7 +2324,7 @@
     <t>Toàn</t>
   </si>
   <si>
-    <t>./images/NO/NGUYEN_HUU_KHANH_TOAN.jpg</t>
+    <t>./data/images/NO/NGUYEN_HUU_KHANH_TOAN.jpg</t>
   </si>
   <si>
     <t>Nguyễn Thị Lan Anh</t>
@@ -2624,7 +2624,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2636,8 +2636,17 @@
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -4039,7 +4048,7 @@
       <c r="F2" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>662</v>
       </c>
       <c r="H2" s="1">
@@ -4065,7 +4074,7 @@
       <c r="F3" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>667</v>
       </c>
       <c r="H3" s="1">
@@ -4091,7 +4100,7 @@
       <c r="F4" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>670</v>
       </c>
       <c r="H4" s="1">
@@ -4117,7 +4126,7 @@
       <c r="F5" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>674</v>
       </c>
       <c r="H5" s="1">
@@ -4169,7 +4178,7 @@
       <c r="F7" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>681</v>
       </c>
       <c r="H7" s="1">
@@ -5286,7 +5295,7 @@
       <c r="F2" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>693</v>
       </c>
       <c r="H2" s="1">
@@ -6356,7 +6365,7 @@
       <c r="F2" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>697</v>
       </c>
       <c r="H2" s="1">
@@ -7433,32 +7442,32 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="7">
         <v>1.0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>702</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>703</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>704</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="8" t="s">
         <v>705</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="7">
         <v>5.0</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
     <row r="4" ht="15.75" customHeight="1"/>
@@ -15065,7 +15074,7 @@
       <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="2">
@@ -15091,7 +15100,7 @@
       <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="2">
@@ -15117,7 +15126,7 @@
       <c r="F4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="2">
@@ -15143,7 +15152,7 @@
       <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H5" s="2">
@@ -15169,7 +15178,7 @@
       <c r="F6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H6" s="2">
@@ -15195,7 +15204,7 @@
       <c r="F7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H7" s="2">
@@ -15221,7 +15230,7 @@
       <c r="F8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H8" s="2">
@@ -15247,7 +15256,7 @@
       <c r="F9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="H9" s="2">
@@ -15273,7 +15282,7 @@
       <c r="F10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="2" t="s">
         <v>49</v>
       </c>
       <c r="H10" s="2">
@@ -15299,7 +15308,7 @@
       <c r="F11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>54</v>
       </c>
       <c r="H11" s="2">
@@ -15348,7 +15357,7 @@
       <c r="F13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="2" t="s">
         <v>60</v>
       </c>
       <c r="H13" s="2">
@@ -15374,7 +15383,7 @@
       <c r="F14" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="2" t="s">
         <v>64</v>
       </c>
       <c r="H14" s="2">
@@ -17768,17 +17777,17 @@
       <c r="C60" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="F60" s="6" t="s">
+      <c r="F60" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="G60" s="6"/>
-      <c r="H60" s="7">
+      <c r="G60" s="9"/>
+      <c r="H60" s="10">
         <v>8.0</v>
       </c>
     </row>
@@ -18199,7 +18208,7 @@
       <c r="F2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="H2" s="1">
@@ -18225,7 +18234,7 @@
       <c r="F3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="H3" s="1">
@@ -18251,7 +18260,7 @@
       <c r="F4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>77</v>
       </c>
       <c r="H4" s="1">
@@ -18277,7 +18286,7 @@
       <c r="F5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>81</v>
       </c>
       <c r="H5" s="1">
@@ -18303,7 +18312,7 @@
       <c r="F6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>85</v>
       </c>
       <c r="H6" s="1">
@@ -18352,7 +18361,7 @@
       <c r="F8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="2" t="s">
         <v>92</v>
       </c>
       <c r="H8" s="1">
@@ -18378,7 +18387,7 @@
       <c r="F9" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="2" t="s">
         <v>96</v>
       </c>
       <c r="H9" s="1">
@@ -18404,7 +18413,7 @@
       <c r="F10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H10" s="1">
@@ -18430,7 +18439,7 @@
       <c r="F11" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>104</v>
       </c>
       <c r="H11" s="1">
@@ -18456,7 +18465,7 @@
       <c r="F12" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>108</v>
       </c>
       <c r="H12" s="2">
@@ -18482,7 +18491,7 @@
       <c r="F13" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="2" t="s">
         <v>111</v>
       </c>
       <c r="H13" s="2">
@@ -18508,7 +18517,7 @@
       <c r="F14" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="2" t="s">
         <v>114</v>
       </c>
       <c r="H14" s="2">
@@ -18534,7 +18543,7 @@
       <c r="F15" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="2" t="s">
         <v>117</v>
       </c>
       <c r="H15" s="2">
@@ -18560,7 +18569,7 @@
       <c r="F16" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H16" s="2">
@@ -18609,7 +18618,7 @@
       <c r="F18" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="2" t="s">
         <v>127</v>
       </c>
       <c r="H18" s="2">
@@ -18704,7 +18713,7 @@
       <c r="F22" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="2" t="s">
         <v>137</v>
       </c>
       <c r="H22" s="2">
@@ -18730,7 +18739,7 @@
       <c r="F23" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="2" t="s">
         <v>141</v>
       </c>
       <c r="H23" s="2">
@@ -18848,7 +18857,7 @@
       <c r="F28" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="2" t="s">
         <v>152</v>
       </c>
       <c r="H28" s="2">
@@ -18966,7 +18975,7 @@
       <c r="F33" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="2" t="s">
         <v>162</v>
       </c>
       <c r="H33" s="2">
@@ -19294,7 +19303,7 @@
       <c r="F47" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="2" t="s">
         <v>187</v>
       </c>
       <c r="H47" s="2">
@@ -19320,7 +19329,7 @@
       <c r="F48" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="2" t="s">
         <v>190</v>
       </c>
       <c r="H48" s="2">
@@ -19346,7 +19355,7 @@
       <c r="F49" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="2" t="s">
         <v>194</v>
       </c>
       <c r="H49" s="2">
@@ -19372,7 +19381,7 @@
       <c r="F50" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="2" t="s">
         <v>198</v>
       </c>
       <c r="H50" s="2">
@@ -19424,7 +19433,7 @@
       <c r="F52" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="2" t="s">
         <v>204</v>
       </c>
       <c r="H52" s="2">
@@ -19568,7 +19577,7 @@
       <c r="F58" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="2" t="s">
         <v>217</v>
       </c>
       <c r="H58" s="2">
@@ -19594,7 +19603,7 @@
       <c r="F59" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" s="2" t="s">
         <v>220</v>
       </c>
       <c r="H59" s="2">
@@ -19620,7 +19629,7 @@
       <c r="F60" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="G60" s="2" t="s">
         <v>223</v>
       </c>
       <c r="H60" s="2">
@@ -19750,7 +19759,7 @@
       <c r="F65" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G65" s="2" t="s">
         <v>237</v>
       </c>
       <c r="H65" s="2">
@@ -19828,7 +19837,7 @@
       <c r="F68" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="G68" s="2" t="s">
         <v>246</v>
       </c>
       <c r="H68" s="2">
@@ -19880,7 +19889,7 @@
       <c r="F70" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="G70" s="2" t="s">
         <v>253</v>
       </c>
       <c r="H70" s="2">
@@ -19906,7 +19915,7 @@
       <c r="F71" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="G71" s="2" t="s">
         <v>257</v>
       </c>
       <c r="H71" s="2">
@@ -19932,7 +19941,7 @@
       <c r="F72" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="G72" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H72" s="2">
@@ -19958,7 +19967,7 @@
       <c r="F73" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="G73" s="2" t="s">
         <v>265</v>
       </c>
       <c r="H73" s="2">
@@ -20125,7 +20134,7 @@
       <c r="F80" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="G80" s="2" t="s">
         <v>282</v>
       </c>
       <c r="H80" s="2">
@@ -20151,7 +20160,7 @@
       <c r="F81" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="G81" s="2" t="s">
         <v>286</v>
       </c>
       <c r="H81" s="2">
@@ -20177,7 +20186,7 @@
       <c r="F82" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="G82" s="2" t="s">
         <v>289</v>
       </c>
       <c r="H82" s="2">
@@ -20203,7 +20212,7 @@
       <c r="F83" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G83" s="1" t="s">
+      <c r="G83" s="2" t="s">
         <v>291</v>
       </c>
       <c r="H83" s="2">
@@ -20229,7 +20238,7 @@
       <c r="F84" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G84" s="1" t="s">
+      <c r="G84" s="2" t="s">
         <v>294</v>
       </c>
       <c r="H84" s="2">
@@ -20255,7 +20264,7 @@
       <c r="F85" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="G85" s="1" t="s">
+      <c r="G85" s="2" t="s">
         <v>298</v>
       </c>
       <c r="H85" s="2">
@@ -20281,7 +20290,7 @@
       <c r="F86" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="G86" s="1" t="s">
+      <c r="G86" s="2" t="s">
         <v>302</v>
       </c>
       <c r="H86" s="2">
@@ -20307,7 +20316,7 @@
       <c r="F87" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="G87" s="1" t="s">
+      <c r="G87" s="2" t="s">
         <v>306</v>
       </c>
       <c r="H87" s="2">
@@ -20333,7 +20342,7 @@
       <c r="F88" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="G88" s="1" t="s">
+      <c r="G88" s="2" t="s">
         <v>309</v>
       </c>
       <c r="H88" s="2">
@@ -21399,7 +21408,7 @@
       <c r="F2" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H2" s="1">
@@ -21425,7 +21434,7 @@
       <c r="F3" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>323</v>
       </c>
       <c r="H3" s="1">
@@ -21477,7 +21486,7 @@
       <c r="F5" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>331</v>
       </c>
       <c r="H5" s="1">
@@ -21503,7 +21512,7 @@
       <c r="F6" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>334</v>
       </c>
       <c r="H6" s="1">
@@ -21529,7 +21538,7 @@
       <c r="F7" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>337</v>
       </c>
       <c r="H7" s="2">
@@ -21607,7 +21616,7 @@
       <c r="F10" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="2" t="s">
         <v>348</v>
       </c>
       <c r="H10" s="1">
@@ -21633,7 +21642,7 @@
       <c r="F11" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>351</v>
       </c>
       <c r="H11" s="2">
@@ -21659,7 +21668,7 @@
       <c r="F12" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>354</v>
       </c>
       <c r="H12" s="2">
@@ -21685,7 +21694,7 @@
       <c r="F13" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="2" t="s">
         <v>358</v>
       </c>
       <c r="H13" s="2">
@@ -21711,7 +21720,7 @@
       <c r="F14" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="2" t="s">
         <v>362</v>
       </c>
       <c r="H14" s="2">
@@ -21763,7 +21772,7 @@
       <c r="F16" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="2" t="s">
         <v>368</v>
       </c>
       <c r="H16" s="2">
@@ -21789,7 +21798,7 @@
       <c r="F17" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="2" t="s">
         <v>372</v>
       </c>
       <c r="H17" s="2">
@@ -21815,7 +21824,7 @@
       <c r="F18" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="2" t="s">
         <v>375</v>
       </c>
       <c r="H18" s="2">
@@ -21841,7 +21850,7 @@
       <c r="F19" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="2" t="s">
         <v>379</v>
       </c>
       <c r="H19" s="1">
@@ -21890,7 +21899,7 @@
       <c r="F21" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="2" t="s">
         <v>384</v>
       </c>
       <c r="H21" s="1">
@@ -21916,7 +21925,7 @@
       <c r="F22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="2" t="s">
         <v>386</v>
       </c>
       <c r="H22" s="1">
@@ -21942,7 +21951,7 @@
       <c r="F23" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="2" t="s">
         <v>390</v>
       </c>
       <c r="H23" s="1">
@@ -21968,7 +21977,7 @@
       <c r="F24" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="2" t="s">
         <v>394</v>
       </c>
       <c r="H24" s="1">
@@ -21994,7 +22003,7 @@
       <c r="F25" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="2" t="s">
         <v>397</v>
       </c>
       <c r="H25" s="1">
@@ -22020,7 +22029,7 @@
       <c r="F26" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="2" t="s">
         <v>401</v>
       </c>
       <c r="H26" s="1">
@@ -22046,7 +22055,7 @@
       <c r="F27" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="2" t="s">
         <v>405</v>
       </c>
       <c r="H27" s="1">
@@ -22072,7 +22081,7 @@
       <c r="F28" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="2" t="s">
         <v>408</v>
       </c>
       <c r="H28" s="1">
@@ -23660,7 +23669,7 @@
       <c r="F2" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>475</v>
       </c>
       <c r="H2" s="2">
@@ -23686,7 +23695,7 @@
       <c r="F3" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>479</v>
       </c>
       <c r="H3" s="1">
@@ -23712,7 +23721,7 @@
       <c r="F4" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>482</v>
       </c>
       <c r="H4" s="1">
@@ -23738,7 +23747,7 @@
       <c r="F5" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>486</v>
       </c>
       <c r="H5" s="1">
@@ -23764,7 +23773,7 @@
       <c r="F6" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>490</v>
       </c>
       <c r="H6" s="2">
@@ -23790,7 +23799,7 @@
       <c r="F7" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>494</v>
       </c>
       <c r="H7" s="1">
@@ -23816,7 +23825,7 @@
       <c r="F8" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="2" t="s">
         <v>498</v>
       </c>
       <c r="H8" s="2">
@@ -23842,7 +23851,7 @@
       <c r="F9" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="2" t="s">
         <v>503</v>
       </c>
       <c r="H9" s="2">
@@ -23868,7 +23877,7 @@
       <c r="F10" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="2" t="s">
         <v>506</v>
       </c>
       <c r="H10" s="2">
@@ -23894,7 +23903,7 @@
       <c r="F11" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>509</v>
       </c>
       <c r="H11" s="2">
@@ -23920,7 +23929,7 @@
       <c r="F12" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>514</v>
       </c>
       <c r="H12" s="2">
@@ -23946,7 +23955,7 @@
       <c r="F13" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="2" t="s">
         <v>519</v>
       </c>
       <c r="H13" s="1">
@@ -23995,7 +24004,7 @@
       <c r="F15" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="2" t="s">
         <v>524</v>
       </c>
       <c r="H15" s="1">
@@ -24021,7 +24030,7 @@
       <c r="F16" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="2" t="s">
         <v>528</v>
       </c>
       <c r="H16" s="1">
@@ -24047,7 +24056,7 @@
       <c r="F17" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="2" t="s">
         <v>530</v>
       </c>
       <c r="H17" s="1">
@@ -25358,7 +25367,7 @@
       <c r="F2" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>561</v>
       </c>
       <c r="H2" s="2">
@@ -25384,7 +25393,7 @@
       <c r="F3" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>565</v>
       </c>
       <c r="H3" s="1">
@@ -25410,7 +25419,7 @@
       <c r="F4" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>568</v>
       </c>
       <c r="H4" s="1">
@@ -25436,7 +25445,7 @@
       <c r="F5" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>571</v>
       </c>
       <c r="H5" s="1">
@@ -25462,7 +25471,7 @@
       <c r="F6" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>575</v>
       </c>
       <c r="H6" s="1">
@@ -25488,7 +25497,7 @@
       <c r="F7" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>579</v>
       </c>
       <c r="H7" s="1">
@@ -26650,7 +26659,7 @@
       <c r="F3" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>591</v>
       </c>
       <c r="H3" s="1">
@@ -26699,7 +26708,7 @@
       <c r="F5" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>596</v>
       </c>
       <c r="H5" s="1">
@@ -26725,7 +26734,7 @@
       <c r="F6" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="6" t="s">
         <v>599</v>
       </c>
       <c r="H6" s="1">
@@ -26751,7 +26760,7 @@
       <c r="F7" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>602</v>
       </c>
       <c r="H7" s="2">
@@ -26846,7 +26855,7 @@
       <c r="F11" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>609</v>
       </c>
       <c r="H11" s="1">
@@ -27961,7 +27970,7 @@
       <c r="F2" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>620</v>
       </c>
       <c r="H2" s="1">
@@ -27987,7 +27996,7 @@
       <c r="F3" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>624</v>
       </c>
       <c r="H3" s="1">
@@ -28059,7 +28068,7 @@
       <c r="F6" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>632</v>
       </c>
       <c r="H6" s="1">
@@ -29174,7 +29183,7 @@
       <c r="F2" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>643</v>
       </c>
       <c r="H2" s="1">
@@ -29200,7 +29209,7 @@
       <c r="F3" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>647</v>
       </c>
       <c r="H3" s="1">

--- a/data/DATA.xlsx
+++ b/data/DATA.xlsx
@@ -2032,7 +2032,7 @@
     <t>Duyy BUỒN NGẨU</t>
   </si>
   <si>
-    <t>./data/images/2017/LE_DUC_DUY.jpg</t>
+    <t>./data/images/2017/LE_DUC_DUY.webp</t>
   </si>
   <si>
     <t>Lý Thanh Tùng (Tbh)</t>
@@ -2047,7 +2047,7 @@
     <t>&lt;a href="https://lythanhtung-github.github.io/chanhtamwtbh/" target="_blank"&gt;🎨🌧️🎧&lt;/a&gt;</t>
   </si>
   <si>
-    <t>./data/images/2017/LY_THANH_TUNG.jpg</t>
+    <t>./data/images/2017/LY_THANH_TUNG.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Lai (Lai Lụt)</t>
@@ -2056,7 +2056,7 @@
     <t>Lai Thị Lụtt</t>
   </si>
   <si>
-    <t>./data/images/2017/NGUYEN_THI_LAI.jpg</t>
+    <t>./data/images/2017/NGUYEN_THI_LAI.webp</t>
   </si>
   <si>
     <t>Lê Văn Huy (Huy Lê)</t>
@@ -2068,7 +2068,7 @@
     <t>&lt;s&gt;yesterday&lt;/s&gt; NOW &lt;del&gt;tomorrow&lt;/del&gt;</t>
   </si>
   <si>
-    <t>./data/images/2017/LE_VAN_HUY.jpg</t>
+    <t>./data/images/2017/LE_VAN_HUY.webp</t>
   </si>
   <si>
     <t>Phan Đình Thành Nhân</t>
@@ -2080,7 +2080,7 @@
     <t>Cu em</t>
   </si>
   <si>
-    <t>./data/images/2017/PHAN_DINH_THANH_NHAN.jpg</t>
+    <t>./data/images/2017/PHAN_DINH_THANH_NHAN.webp</t>
   </si>
   <si>
     <t>Trần Văn Quốc (Bi)</t>
@@ -2089,7 +2089,7 @@
     <t>Quảng Bảo</t>
   </si>
   <si>
-    <t>./data/images/2017/TRAN_QUOC.jpg</t>
+    <t>./data/images/2017/TRAN_QUOC.webp</t>
   </si>
   <si>
     <t>Nguyễn Đăng Hoàng Phúc (Bun)</t>
@@ -2101,7 +2101,7 @@
     <t>Nhuận Hạnh</t>
   </si>
   <si>
-    <t>./data/images/2017/NGUYEN_DANG_HOANG_PHUC.jpg</t>
+    <t>./data/images/2017/NGUYEN_DANG_HOANG_PHUC.webp</t>
   </si>
   <si>
     <t>Đặng Thanh Hương (Na)</t>
@@ -2113,7 +2113,7 @@
     <t>🍈</t>
   </si>
   <si>
-    <t>./data/images/2017/DANG_THANH_HUONG.jpg</t>
+    <t>./data/images/2017/DANG_THANH_HUONG.webp</t>
   </si>
   <si>
     <t>Trần Thị Lành (Xíu)</t>
@@ -2125,7 +2125,7 @@
     <t>Nhuận Hải Tâm</t>
   </si>
   <si>
-    <t>./data/images/2016/TRAN_THI_LANH.jpg</t>
+    <t>./data/images/2016/TRAN_THI_LANH.webp</t>
   </si>
   <si>
     <t>Lê Thị Nhật (Nước Lọc)</t>
@@ -2137,7 +2137,7 @@
     <t>Biết ơn - Tĩnh lặng</t>
   </si>
   <si>
-    <t>./data/images/2015/LE_THI_NHAT.jpg</t>
+    <t>./data/images/2015/LE_THI_NHAT.webp</t>
   </si>
   <si>
     <t>Đỗ Văn Tuấn</t>
@@ -2149,7 +2149,7 @@
     <t>Nhuận Tú Minh</t>
   </si>
   <si>
-    <t>./data/images/2015/DO_VAN_TUAN.jpg</t>
+    <t>./data/images/2015/DO_VAN_TUAN.webp</t>
   </si>
   <si>
     <t>Hồ Tâm Nguyên (Nguyên Hồ)</t>
@@ -2162,7 +2162,7 @@
     <t>Người anh sâu sắc</t>
   </si>
   <si>
-    <t>./data/images/2014/HO_TAM_NGUYEN.jpg</t>
+    <t>./data/images/2014/HO_TAM_NGUYEN.webp</t>
   </si>
   <si>
     <t>Lê Linh Đài</t>
@@ -6316,7 +6316,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="6" width="8.56"/>
-    <col customWidth="1" min="7" max="7" width="27.78"/>
+    <col customWidth="1" min="7" max="7" width="36.0"/>
     <col customWidth="1" min="8" max="26" width="8.56"/>
   </cols>
   <sheetData>

--- a/data/DATA.xlsx
+++ b/data/DATA.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="851">
   <si>
     <t>id</t>
   </si>
@@ -1810,7 +1810,7 @@
     <t>Nhật Uyên xinh đẹp</t>
   </si>
   <si>
-    <t>./data/images/2020/NGUYEN_NHAT_UYEN.jpg</t>
+    <t>./data/images/2020/NGUYEN_NHAT_UYEN.webp</t>
   </si>
   <si>
     <t>Nguyễn Nhật Linh</t>
@@ -1819,7 +1819,7 @@
     <t>Bớt nghe, bớt nói, bớt nhìn. Giữ tâm thanh tịnh mới là thảnh thơi.</t>
   </si>
   <si>
-    <t>./data/images/2020/NGUYEN_NHAT_LINH.jpg</t>
+    <t>./data/images/2020/NGUYEN_NHAT_LINH.webp</t>
   </si>
   <si>
     <t>Trần Xuân Trung</t>
@@ -1828,13 +1828,16 @@
     <t>Trung</t>
   </si>
   <si>
+    <t>./data/images/2020/TRAN_XUAN_TRUNG.webp</t>
+  </si>
+  <si>
     <t>Nguyễn Thị Mỹ Nhàn</t>
   </si>
   <si>
     <t>Nhuận Niệm</t>
   </si>
   <si>
-    <t>./data/images/2020/NGUYEN_THI_MY_NHAN.jpg</t>
+    <t>./data/images/2020/NGUYEN_THI_MY_NHAN.webp</t>
   </si>
   <si>
     <t>Nguyễn Đăng Huy</t>
@@ -1843,7 +1846,7 @@
     <t>Chú Huy</t>
   </si>
   <si>
-    <t>./data/images/2020/NGUYEN_DANG_HUY.jpg</t>
+    <t>./data/images/2020/NGUYEN_DANG_HUY.webp</t>
   </si>
   <si>
     <t>Hoàng Giang (Long Ka)</t>
@@ -1852,7 +1855,7 @@
     <t>Kết nối - Nhiệt tình - Vui vẻ - Hoà đồng</t>
   </si>
   <si>
-    <t>./data/images/2020/HOANG_GIANG.jpg</t>
+    <t>./data/images/2020/HOANG_GIANG.webp</t>
   </si>
   <si>
     <t>Nguyễn Bá Quốc</t>
@@ -1864,6 +1867,9 @@
     <t>Phan Văn Hưng</t>
   </si>
   <si>
+    <t>./data/images/2020/PHAN_VAN_HUNG.webp</t>
+  </si>
+  <si>
     <t>Nguyễn Phúc Hưng (Ki)</t>
   </si>
   <si>
@@ -1873,7 +1879,7 @@
     <t>Banh</t>
   </si>
   <si>
-    <t>./data/images/2020/DINH_THI_NGOC_ANH.jpg</t>
+    <t>./data/images/2020/DINH_THI_NGOC_ANH.webp</t>
   </si>
   <si>
     <t>Nguyễn Hoàng Kiều Anh</t>
@@ -1882,7 +1888,7 @@
     <t>Quang Tú</t>
   </si>
   <si>
-    <t>./data/images/2020/NGUYEN_HOANG_KIEU_ANH.jpg</t>
+    <t>./data/images/2020/NGUYEN_HOANG_KIEU_ANH.webp</t>
   </si>
   <si>
     <t>Đoàn Thị Thu Hà</t>
@@ -1891,7 +1897,7 @@
     <t>Cô gái Huế hay cười</t>
   </si>
   <si>
-    <t>./data/images/2020/DOAN_THI_THU_HA.jpg</t>
+    <t>./data/images/2020/DOAN_THI_THU_HA.webp</t>
   </si>
   <si>
     <t>Lê Thị Thuận Hóa</t>
@@ -1906,7 +1912,7 @@
     <t>Nàng thơ cây cỏ</t>
   </si>
   <si>
-    <t>./data/images/2019/LE_THI_THUAN_HOA.jpg</t>
+    <t>./data/images/2019/LE_THI_THUAN_HOA.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Như Ngọc</t>
@@ -1918,7 +1924,7 @@
     <t>Quảng Lan</t>
   </si>
   <si>
-    <t>./data/images/2019/NGUYEN_THI_NHU_NGOC.jpg</t>
+    <t>./data/images/2019/NGUYEN_THI_NHU_NGOC.webp</t>
   </si>
   <si>
     <t>Ngô Thị Bảo Trân</t>
@@ -1930,6 +1936,9 @@
     <t>Cô gái lúm đồng tiền 🪙</t>
   </si>
   <si>
+    <t>./data/images/2019/NGO_THI_BAO_TRAN.webp</t>
+  </si>
+  <si>
     <t>Ngô Đức Minh Tuệ</t>
   </si>
   <si>
@@ -1942,7 +1951,7 @@
     <t>Quảng Tịnh</t>
   </si>
   <si>
-    <t>./data/images/2019/NGUYEN_THI_THANH_HIEN.jpg</t>
+    <t>./data/images/2019/NGUYEN_THI_THANH_HIEN.webp</t>
   </si>
   <si>
     <t>Nguyễn Kính Nghĩa (Bin)</t>
@@ -1951,7 +1960,7 @@
     <t>Quảng Trung</t>
   </si>
   <si>
-    <t>./data/images/2019/NGUYEN_KINH_NGHIA.jpg</t>
+    <t>./data/images/2019/NGUYEN_KINH_NGHIA.webp</t>
   </si>
   <si>
     <t>Lê Đình Hùng</t>
@@ -1966,6 +1975,9 @@
     <t>Nhuận Tâm</t>
   </si>
   <si>
+    <t>./data/images/2019/LE_DINH_HUNG.webp</t>
+  </si>
+  <si>
     <t>Phan Vũ Phúc Dương (Hím em)</t>
   </si>
   <si>
@@ -1975,7 +1987,7 @@
     <t>vuýp</t>
   </si>
   <si>
-    <t>./data/images/2018/PHAN_VU_PHUC_DUONG.jpg</t>
+    <t>./data/images/2018/PHAN_VU_PHUC_DUONG.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Xuân Mai</t>
@@ -1987,7 +1999,7 @@
     <t>Quảng Trang</t>
   </si>
   <si>
-    <t>./data/images/2018/NGUYEN_THI_XUAN_MAI.jpg</t>
+    <t>./data/images/2018/NGUYEN_THI_XUAN_MAI.webp</t>
   </si>
   <si>
     <t>Lê Văn Anh Hào</t>
@@ -2002,7 +2014,7 @@
     <t>Quảng Châu</t>
   </si>
   <si>
-    <t>./data/images/2018/NGUYEN_LE_HONG_NGOC.jpg</t>
+    <t>./data/images/2018/NGUYEN_LE_HONG_NGOC.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Thanh Phương (Bơ nhỏ)</t>
@@ -2011,7 +2023,7 @@
     <t>Quảng Mỹ</t>
   </si>
   <si>
-    <t>./data/images/2018/NGUYEN_THI_THANH_PHUONG.jpg</t>
+    <t>./data/images/2018/NGUYEN_THI_THANH_PHUONG.webp</t>
   </si>
   <si>
     <t>Ngô Thị Băng Châu (Bắp)</t>
@@ -2020,7 +2032,7 @@
     <t>Nhuận Thảo</t>
   </si>
   <si>
-    <t>./data/images/2018/NGO_THI_BANG_CHAU.jpg</t>
+    <t>./data/images/2018/NGO_THI_BANG_CHAU.webp</t>
   </si>
   <si>
     <t>Lê Đức Duy</t>
@@ -4034,10 +4046,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -4046,10 +4058,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -4060,22 +4072,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>585</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="H3" s="1">
         <v>3.0</v>
@@ -4086,7 +4098,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>360</v>
@@ -4098,10 +4110,10 @@
         <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -4112,22 +4124,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>144</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4138,22 +4150,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>280</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="H6" s="1">
         <v>6.0</v>
@@ -4164,10 +4176,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -4176,10 +4188,10 @@
         <v>52</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4190,22 +4202,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>139</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -4216,22 +4228,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>39</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -5281,22 +5293,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6351,22 +6363,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>532</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6377,10 +6389,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -6389,10 +6401,10 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7446,22 +7458,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>377</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>52</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="H2" s="7">
         <v>5.0</v>
@@ -8516,10 +8528,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -8528,7 +8540,7 @@
         <v>501</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="H2" s="2">
         <v>7.0</v>
@@ -8539,10 +8551,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
@@ -9608,22 +9620,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>146</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -9634,22 +9646,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>267</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -9660,7 +9672,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -9672,10 +9684,10 @@
         <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -9686,22 +9698,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>175</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -10755,22 +10767,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -10781,22 +10793,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -10807,22 +10819,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -10833,7 +10845,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>71</v>
@@ -10845,10 +10857,10 @@
         <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -10859,7 +10871,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>222</v>
@@ -10871,10 +10883,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -11897,7 +11909,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -16426,22 +16438,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="H2" s="2">
         <v>7.0</v>
@@ -16452,16 +16464,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>744</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>123</v>
@@ -16475,22 +16487,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>208</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -16501,16 +16513,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>123</v>
@@ -16524,16 +16536,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>123</v>
@@ -16547,19 +16559,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>192</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="H7" s="2">
         <v>7.0</v>
@@ -16570,13 +16582,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>388</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>26</v>
@@ -16585,7 +16597,7 @@
         <v>123</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -16596,13 +16608,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>26</v>
@@ -16611,7 +16623,7 @@
         <v>123</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="H9" s="2">
         <v>8.0</v>
@@ -16622,13 +16634,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>39</v>
@@ -16645,7 +16657,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>159</v>
@@ -16668,7 +16680,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>208</v>
@@ -16691,10 +16703,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -16714,10 +16726,10 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -16737,10 +16749,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -16749,7 +16761,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="H15" s="2">
         <v>8.0</v>
@@ -16760,10 +16772,10 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -16783,7 +16795,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>522</v>
@@ -16806,7 +16818,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>75</v>
@@ -16829,7 +16841,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>321</v>
@@ -16852,7 +16864,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>144</v>
@@ -16875,7 +16887,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -16898,7 +16910,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>263</v>
@@ -16921,7 +16933,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>167</v>
@@ -16944,7 +16956,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>94</v>
@@ -16967,10 +16979,10 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -16990,7 +17002,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>79</v>
@@ -17013,7 +17025,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>20</v>
@@ -17036,7 +17048,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>267</v>
@@ -17059,7 +17071,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>51</v>
@@ -17082,7 +17094,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>180</v>
@@ -17105,10 +17117,10 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -17128,7 +17140,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>90</v>
@@ -17151,7 +17163,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>175</v>
@@ -17174,7 +17186,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>177</v>
@@ -17197,7 +17209,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>516</v>
@@ -17220,10 +17232,10 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -17243,7 +17255,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>165</v>
@@ -17266,10 +17278,10 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
@@ -17289,7 +17301,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>20</v>
@@ -17335,7 +17347,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
@@ -17358,10 +17370,10 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
@@ -17381,10 +17393,10 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
@@ -17404,7 +17416,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>148</v>
@@ -17427,10 +17439,10 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
@@ -17450,10 +17462,10 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
@@ -17473,7 +17485,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>477</v>
@@ -17496,10 +17508,10 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
@@ -17519,7 +17531,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>300</v>
@@ -17542,7 +17554,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>278</v>
@@ -17565,10 +17577,10 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>10</v>
@@ -17588,7 +17600,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>271</v>
@@ -17611,10 +17623,10 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
@@ -17634,10 +17646,10 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
@@ -17657,10 +17669,10 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
@@ -17680,7 +17692,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>90</v>
@@ -17703,10 +17715,10 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
@@ -17726,7 +17738,7 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>192</v>
@@ -17749,7 +17761,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>15</v>
@@ -17772,10 +17784,10 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>10</v>
@@ -17796,10 +17808,10 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
@@ -17819,7 +17831,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>403</v>
@@ -17842,7 +17854,7 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>377</v>
@@ -17865,7 +17877,7 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>532</v>
@@ -17888,10 +17900,10 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
@@ -17911,7 +17923,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>144</v>
@@ -17934,7 +17946,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>15</v>
@@ -17957,7 +17969,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>129</v>
@@ -17980,7 +17992,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>75</v>
@@ -17992,7 +18004,7 @@
         <v>26</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="H69" s="2">
         <v>8.0</v>
@@ -18003,7 +18015,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>388</v>
@@ -18026,7 +18038,7 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>496</v>
@@ -18049,10 +18061,10 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
@@ -18072,7 +18084,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>433</v>
@@ -18095,7 +18107,7 @@
         <v>73.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>208</v>
@@ -18118,7 +18130,7 @@
         <v>74.0</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>477</v>
@@ -26685,6 +26697,9 @@
       <c r="F4" s="1" t="s">
         <v>551</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>594</v>
+      </c>
       <c r="H4" s="1">
         <v>5.0</v>
       </c>
@@ -26694,7 +26709,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>522</v>
@@ -26706,10 +26721,10 @@
         <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -26720,7 +26735,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>144</v>
@@ -26732,10 +26747,10 @@
         <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -26746,7 +26761,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>392</v>
@@ -26758,10 +26773,10 @@
         <v>16</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -26772,10 +26787,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
@@ -26795,7 +26810,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>267</v>
@@ -26808,6 +26823,9 @@
       </c>
       <c r="F9" s="1" t="s">
         <v>411</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>607</v>
       </c>
       <c r="H9" s="1">
         <v>7.0</v>
@@ -26818,7 +26836,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>267</v>
@@ -26841,7 +26859,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>62</v>
@@ -26853,10 +26871,10 @@
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H11" s="1">
         <v>7.0</v>
@@ -26867,7 +26885,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>62</v>
@@ -26879,10 +26897,10 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H12" s="2">
         <v>7.0</v>
@@ -26893,7 +26911,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>477</v>
@@ -26905,10 +26923,10 @@
         <v>26</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -27956,22 +27974,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="H2" s="1">
         <v>4.0</v>
@@ -27982,22 +28000,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -28008,19 +28026,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>630</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28031,10 +28052,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -28054,7 +28075,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>263</v>
@@ -28066,10 +28087,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="H6" s="1">
         <v>7.0</v>
@@ -28080,7 +28101,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>437</v>
@@ -28092,10 +28113,10 @@
         <v>39</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28106,19 +28127,25 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="H8" s="2">
+        <v>6.0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1"/>
@@ -29169,10 +29196,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -29181,10 +29208,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="H2" s="1">
         <v>6.0</v>
@@ -29195,10 +29222,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
@@ -29207,10 +29234,10 @@
         <v>501</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="H3" s="1">
         <v>6.0</v>
@@ -29221,7 +29248,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>183</v>
@@ -29233,7 +29260,7 @@
         <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -29244,22 +29271,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="H5" s="2">
         <v>6.0</v>
@@ -29270,22 +29297,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29296,7 +29323,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>58</v>
@@ -29308,10 +29335,10 @@
         <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="H7" s="2">
         <v>7.0</v>

--- a/data/DATA.xlsx
+++ b/data/DATA.xlsx
@@ -33,14 +33,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId24" roundtripDataChecksum="OaOXRb8xyBh6uiN/GekqOiXxRTx5ItTRps98N5o7A1o="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId24" roundtripDataChecksum="qKk1rX9TLJ94QDhcpdXnnQiQsX/XnBAdbTUNtIInMt8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="853">
   <si>
     <t>id</t>
   </si>
@@ -1000,10 +1000,13 @@
     <t>Chân</t>
   </si>
   <si>
+    <t>Trưởng ban hoạt náo</t>
+  </si>
+  <si>
     <t>Chân Thiện Mỹ</t>
   </si>
   <si>
-    <t>./data/images/2023/DANG_HOANG_MY_CHAN.jpg</t>
+    <t>./data/images/2023/DANG_HOANG_MY_CHAN.webp</t>
   </si>
   <si>
     <t>Thân Trọng Quang Dũng</t>
@@ -1015,7 +1018,7 @@
     <t>hoho</t>
   </si>
   <si>
-    <t>./data/images/2023/THAN_TRONG_QUANG_DUNG.jpg</t>
+    <t>./data/images/2023/THAN_TRONG_QUANG_DUNG.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Duyên (Xô)</t>
@@ -1027,7 +1030,7 @@
     <t>Xô Nguyễn</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_THI_DUYEN.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_DUYEN.webp</t>
   </si>
   <si>
     <t>Huỳnh Nguyễn Tâm Nhã</t>
@@ -1039,7 +1042,7 @@
     <t>Bộ trưởng bộ ngoại giao</t>
   </si>
   <si>
-    <t>./data/images/2023/HUYNH_NGUYEN_TAM_NHA.jpg</t>
+    <t>./data/images/2023/HUYNH_NGUYEN_TAM_NHA.webp</t>
   </si>
   <si>
     <t>Phan Việt Thi (Nhật Diệp)</t>
@@ -1048,7 +1051,7 @@
     <t>Lá được ánh nắng chiếu vào 🌿</t>
   </si>
   <si>
-    <t>./data/images/2023/PHAN_VIET_THI.jpg</t>
+    <t>./data/images/2023/PHAN_VIET_THI.webp</t>
   </si>
   <si>
     <t>Lê Huyền Trang</t>
@@ -1057,7 +1060,7 @@
     <t>Hướng nội</t>
   </si>
   <si>
-    <t>./data/images/2023/LE_HUYEN_TRANG.jpg</t>
+    <t>./data/images/2023/LE_HUYEN_TRANG.webp</t>
   </si>
   <si>
     <t>Hoàng Thị Diệu Ái</t>
@@ -1072,7 +1075,7 @@
     <t>Hậu cần khó - có chị Ái</t>
   </si>
   <si>
-    <t>./data/images/2023/HOANG_THI_DIEU_AI.jpg</t>
+    <t>./data/images/2023/HOANG_THI_DIEU_AI.webp</t>
   </si>
   <si>
     <t>Phạm Hoàng Anh</t>
@@ -1081,7 +1084,7 @@
     <t>Hoàng Anh</t>
   </si>
   <si>
-    <t>./data/images/2023/PHAM_HOANG_ANH.jpg</t>
+    <t>./data/images/2023/PHAM_HOANG_ANH.webp</t>
   </si>
   <si>
     <t>Nguyễn Ngọc Kỳ Duyên</t>
@@ -1090,7 +1093,7 @@
     <t>🍓</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_NGOC_KY_DUYEN.jpg</t>
+    <t>./data/images/2023/NGUYEN_NGOC_KY_DUYEN.webp</t>
   </si>
   <si>
     <t>Nguyễn Xuân Quỳnh Anh (Cuộn Len)</t>
@@ -1099,7 +1102,7 @@
     <t>giao diện 1 đằng, hệ điều hành 1 nẻo</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_XUAN_QUYNH_ANH.jpg</t>
+    <t>./data/images/2023/NGUYEN_XUAN_QUYNH_ANH.webp</t>
   </si>
   <si>
     <t>Võ Nguyễn Minh Châu</t>
@@ -1108,7 +1111,7 @@
     <t>Introvert 🥹</t>
   </si>
   <si>
-    <t>./data/images/2023/VO_NGUYEN_MINH_CHAU.jpg</t>
+    <t>./data/images/2023/VO_NGUYEN_MINH_CHAU.webp</t>
   </si>
   <si>
     <t>Lê Ngọc Giản Đơn</t>
@@ -1120,7 +1123,7 @@
     <t>cô bé phức tạp</t>
   </si>
   <si>
-    <t>./data/images/2023/LE_NGOC_GIAN_DON.jpg</t>
+    <t>./data/images/2023/LE_NGOC_GIAN_DON.webp</t>
   </si>
   <si>
     <t>Trần Nhật Lai</t>
@@ -1132,7 +1135,7 @@
     <t>Muốn được iu thưn🫶</t>
   </si>
   <si>
-    <t>./data/images/2023/TRAN_NHAT_LAI.jpg</t>
+    <t>./data/images/2023/TRAN_NHAT_LAI.webp</t>
   </si>
   <si>
     <t>Phan Thị Quỳnh Trâm</t>
@@ -1141,7 +1144,7 @@
     <t>Quỳnh Trâm</t>
   </si>
   <si>
-    <t>./data/images/2023/PHAN_THI_QUYNH_TRAM.jpg</t>
+    <t>./data/images/2023/PHAN_THI_QUYNH_TRAM.webp</t>
   </si>
   <si>
     <t>Lê Thị Diệu Trinh</t>
@@ -1150,7 +1153,7 @@
     <t>Lặng lẽ học tập, rèn luyện thân tâm</t>
   </si>
   <si>
-    <t>./data/images/2023/LE_THI_DIEU_TRINH.jpg</t>
+    <t>./data/images/2023/LE_THI_DIEU_TRINH.webp</t>
   </si>
   <si>
     <t xml:space="preserve">Tống Hồ Trần Tuyền </t>
@@ -1162,7 +1165,7 @@
     <t>bún đậu muối tiêu</t>
   </si>
   <si>
-    <t>./data/images/2023/TONG_HO_TRAN_TUYEN.jpg</t>
+    <t>./data/images/2023/TONG_HO_TRAN_TUYEN.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Như Ý (Nhã Đan)</t>
@@ -1171,7 +1174,7 @@
     <t>Tẻn tẻn</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_THI_NHU_Y.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_NHU_Y.webp</t>
   </si>
   <si>
     <t>Đoàn Đại Trung Nguyên (Đức Phúc)</t>
@@ -1183,7 +1186,7 @@
     <t>Nhuận Bình</t>
   </si>
   <si>
-    <t>./data/images/2023/DAI_DOAN_TRUNG_NGUYEN.jpg</t>
+    <t>./data/images/2023/DAI_DOAN_TRUNG_NGUYEN.webp</t>
   </si>
   <si>
     <t>Hồ Văn Quốc Huy</t>
@@ -1198,13 +1201,13 @@
     <t>Quỳnh</t>
   </si>
   <si>
-    <t>./data/images/2023/LE_NGUYEN_DIEM_QUYNH.jpg</t>
+    <t>./data/images/2023/LE_NGUYEN_DIEM_QUYNH.webp</t>
   </si>
   <si>
     <t>Lê Thảo Nguyên (Ốc iu)</t>
   </si>
   <si>
-    <t>./data/images/2023/LE_THAO_NGUYEN.jpg</t>
+    <t>./data/images/2023/LE_THAO_NGUYEN.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Thu Ngân</t>
@@ -1216,7 +1219,7 @@
     <t>Quảng Diệu</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_THI_THU_NGAN.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_THU_NGAN.webp</t>
   </si>
   <si>
     <t>Phan Thị Hương Giang</t>
@@ -1228,7 +1231,7 @@
     <t>Nà Ná</t>
   </si>
   <si>
-    <t>./data/images/2023/PHAN_THI_HUONG_GIANG.jpg</t>
+    <t>./data/images/2023/PHAN_THI_HUONG_GIANG.webp</t>
   </si>
   <si>
     <t>Phùng Uyển Cát Tiên</t>
@@ -1237,7 +1240,7 @@
     <t>Nhuận Hoàng</t>
   </si>
   <si>
-    <t>./data/images/2023/PHUNG_UYEN_CAT_TIEN.jpg</t>
+    <t>./data/images/2023/PHUNG_UYEN_CAT_TIEN.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Huỳnh Thanh</t>
@@ -1249,7 +1252,7 @@
     <t>Má hồng 😳</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_THI_HUYNH_THANH.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_HUYNH_THANH.webp</t>
   </si>
   <si>
     <t>Nguyễn Anh Quân</t>
@@ -1261,7 +1264,7 @@
     <t>Quảng Nam</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_ANH_QUAN.jpg</t>
+    <t>./data/images/2023/NGUYEN_ANH_QUAN.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Thuỳ</t>
@@ -1270,7 +1273,7 @@
     <t>Thuỳ</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_THI_THUY.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_THUY.webp</t>
   </si>
   <si>
     <t>Lê Văn Nhất Vạn (Mười)</t>
@@ -1282,13 +1285,13 @@
     <t>Nhuận Từ</t>
   </si>
   <si>
-    <t>./data/images/2023/LE_VAN_NHAT_VAN.jpg</t>
+    <t>./data/images/2023/LE_VAN_NHAT_VAN.webp</t>
   </si>
   <si>
     <t>Đỗ Thị Thu Thảo</t>
   </si>
   <si>
-    <t>./data/images/2023/DO_THI_THU_THAO.jpg</t>
+    <t>./data/images/2023/DO_THI_THU_THAO.webp</t>
   </si>
   <si>
     <t>Nguyễn Thành Tâm</t>
@@ -1297,7 +1300,7 @@
     <t>Tâm</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_THANH_TAM.jpg</t>
+    <t>./data/images/2023/NGUYEN_THANH_TAM.webp</t>
   </si>
   <si>
     <t>Đặng Thị Lượm (Dalu)</t>
@@ -1309,7 +1312,7 @@
     <t>Quảng Tích</t>
   </si>
   <si>
-    <t>./data/images/2023/DANG_THI_LUOM.jpg</t>
+    <t>./data/images/2023/DANG_THI_LUOM.webp</t>
   </si>
   <si>
     <t>Hà Văn Triều</t>
@@ -1321,7 +1324,7 @@
     <t>Mất tích</t>
   </si>
   <si>
-    <t>./data/images/2023/HA_VAN_TRIEU.jpg</t>
+    <t>./data/images/2023/HA_VAN_TRIEU.webp</t>
   </si>
   <si>
     <t>Lê Châu Tường Minh</t>
@@ -1330,7 +1333,7 @@
     <t>Quảng Chuyên</t>
   </si>
   <si>
-    <t>./data/images/2023/LE_CHAU_TUONG_MINH.jpg</t>
+    <t>./data/images/2023/LE_CHAU_TUONG_MINH.webp</t>
   </si>
   <si>
     <t>Lê Thảo Vân</t>
@@ -1339,7 +1342,7 @@
     <t>Nguyên Tâm</t>
   </si>
   <si>
-    <t>./data/images/2023/LE_THAO_VAN.jpg</t>
+    <t>./data/images/2023/LE_THAO_VAN.webp</t>
   </si>
   <si>
     <t>Ngô Trần Thị Thu Đông</t>
@@ -1351,7 +1354,7 @@
     <t>⛄</t>
   </si>
   <si>
-    <t>./data/images/2023/NGO_TRAN_THU_DONG.jpg</t>
+    <t>./data/images/2023/NGO_TRAN_THU_DONG.webp</t>
   </si>
   <si>
     <t>Nguyễn Đức Nghĩa</t>
@@ -1363,7 +1366,7 @@
     <t>Nguyên Nhân</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_DUC_NGHIA.jpg</t>
+    <t>./data/images/2023/NGUYEN_DUC_NGHIA.webp</t>
   </si>
   <si>
     <t>Nguyễn Hải Cương</t>
@@ -1384,7 +1387,7 @@
     <t>Quảng Liên Kiều</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_THI_THANH_PHUONG.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_THANH_PHUONG.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Thanh Thảo</t>
@@ -1393,7 +1396,7 @@
     <t>Tâm Phương</t>
   </si>
   <si>
-    <t>./data/images/2023/NGUYEN_THI_THANH_THAO.jpg</t>
+    <t>./data/images/2023/NGUYEN_THI_THANH_THAO.webp</t>
   </si>
   <si>
     <t>Phạm Khánh Quỳnh</t>
@@ -1402,13 +1405,13 @@
     <t>Nguyên An</t>
   </si>
   <si>
-    <t>./data/images/2023/PHAM_KHANH_QUYNH.jpg</t>
+    <t>./data/images/2023/PHAM_KHANH_QUYNH.webp</t>
   </si>
   <si>
     <t>Trần Hoàng Phương Linh</t>
   </si>
   <si>
-    <t>./data/images/2023/TRAN_HOANG_PHUONG_LINH.jpg</t>
+    <t>./data/images/2023/TRAN_HOANG_PHUONG_LINH.webp</t>
   </si>
   <si>
     <t>Trần Thị Ly (lixinh)</t>
@@ -1417,7 +1420,7 @@
     <t>Ly</t>
   </si>
   <si>
-    <t>./data/images/2023/TRAN_THI_LY.jpg</t>
+    <t>./data/images/2023/TRAN_THI_LY.webp</t>
   </si>
   <si>
     <t>Trương Nguyễn Bảo Trân</t>
@@ -1441,7 +1444,7 @@
     <t>Tống Thị Mỹ Nhi</t>
   </si>
   <si>
-    <t>./data/images/2023/TONG_MY_NHI.jpg</t>
+    <t>./data/images/2023/TONG_MY_NHI.webp</t>
   </si>
   <si>
     <t>Trương Huyên Chương</t>
@@ -1453,13 +1456,13 @@
     <t>Nhuận Pháp</t>
   </si>
   <si>
-    <t>./data/images/2023/TRUONG_HUYEN_CHUONG.jpg</t>
+    <t>./data/images/2023/TRUONG_HUYEN_CHUONG.webp</t>
   </si>
   <si>
     <t>Phạm Trương Bảo Hoàng (Kem)</t>
   </si>
   <si>
-    <t>./data/images/2023/PHAM_TRUONG_BAO_HOANG.jpg</t>
+    <t>./data/images/2023/PHAM_TRUONG_BAO_HOANG.webp</t>
   </si>
   <si>
     <t>Phan Thị Phương Anh (Sô)</t>
@@ -1471,7 +1474,7 @@
     <t>Sony Phan</t>
   </si>
   <si>
-    <t>./data/images/2022/PHAN_THI_PHUONG_ANH.jpg</t>
+    <t>./data/images/2022/PHAN_THI_PHUONG_ANH.webp</t>
   </si>
   <si>
     <t>Trần Thị Hà (Trần Hà)</t>
@@ -1483,7 +1486,7 @@
     <t>Quảng Hồng</t>
   </si>
   <si>
-    <t>./data/images/2022/TRAN_THI_HA.jpg</t>
+    <t>./data/images/2022/TRAN_THI_HA.webp</t>
   </si>
   <si>
     <t>Nguyễn Hồ Thảo Nhi (Pho)</t>
@@ -1492,7 +1495,7 @@
     <t>trong veo</t>
   </si>
   <si>
-    <t>./data/images/2022/NGUYEN_HO_THAO_NHI.jpg</t>
+    <t>./data/images/2022/NGUYEN_HO_THAO_NHI.webp</t>
   </si>
   <si>
     <t>Trần  Thị Như Giao</t>
@@ -1504,7 +1507,7 @@
     <t>Tử tế</t>
   </si>
   <si>
-    <t>./data/images/2022/TRAN_THI_NHU_GIAO.jpg</t>
+    <t>./data/images/2022/TRAN_THI_NHU_GIAO.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Ngọc Ánh (Énn énnnnn)</t>
@@ -1516,7 +1519,7 @@
     <t>Mặt trời nhỏo</t>
   </si>
   <si>
-    <t>./data/images/2022/NGUYEN_THI_NGOC_ANH.jpg</t>
+    <t>./data/images/2022/NGUYEN_THI_NGOC_ANH.webp</t>
   </si>
   <si>
     <t>Hồ Thị Châu Linh</t>
@@ -1528,7 +1531,7 @@
     <t>Cá thích chơi</t>
   </si>
   <si>
-    <t>./data/images/2022/HO_THI_CHAU_LINH.jpg</t>
+    <t>./data/images/2022/HO_THI_CHAU_LINH.webp</t>
   </si>
   <si>
     <t>Dương Thị Thu Huyền</t>
@@ -1540,7 +1543,7 @@
     <t>&lt;b&gt;𝘽𝙚 𝙮𝙤𝙪𝙧𝙨𝙚𝙡𝙛, 𝙙𝙤𝙣'𝙩 𝙗𝙚 𝙖𝙣𝙮𝙤𝙣𝙚 𝙚𝙡𝙨𝙚&lt;/b&gt;</t>
   </si>
   <si>
-    <t>./data/images/2022/DUONG_THI_THU_HUYEN.jpg</t>
+    <t>./data/images/2022/DUONG_THI_THU_HUYEN.webp</t>
   </si>
   <si>
     <t>Hoàng Hữu Tuấn Vũ (TVũ 4S)</t>
@@ -1555,7 +1558,7 @@
     <t>Sống chỉ đơn giản - lấy nụ cười làm căn bản</t>
   </si>
   <si>
-    <t>./data/images/2022/HOANG_HUU_TUAN_VU.jpg</t>
+    <t>./data/images/2022/HOANG_HUU_TUAN_VU.webp</t>
   </si>
   <si>
     <t>Trần Phương Nam (Nhuận Tường)</t>
@@ -1564,7 +1567,7 @@
     <t>Hiện tại mình đang sống ẩn</t>
   </si>
   <si>
-    <t>./data/images/2022/TRAN_PHUONG_NAM.jpg</t>
+    <t>./data/images/2022/TRAN_PHUONG_NAM.webp</t>
   </si>
   <si>
     <t>Võ Hồng Đức (Mai Cồ Phước Duyên)</t>
@@ -1573,7 +1576,7 @@
     <t>Hậu cần, Diễn kịch và Nước mía</t>
   </si>
   <si>
-    <t>./data/images/2022/VO_HONG_DUC.jpg</t>
+    <t>./data/images/2022/VO_HONG_DUC.webp</t>
   </si>
   <si>
     <t>Nguyễn Đức Nguyên Thông (Thúng)</t>
@@ -1588,7 +1591,7 @@
     <t>Thở là ra thơ</t>
   </si>
   <si>
-    <t>./data/images/2022/NGUYEN_DUC_NGUYEN_THONG.jpg</t>
+    <t>./data/images/2022/NGUYEN_DUC_NGUYEN_THONG.webp</t>
   </si>
   <si>
     <t>Đậu Đoàn Hoàn Mỹ (Mỵ Mỵ)</t>
@@ -1603,7 +1606,7 @@
     <t>Nhỏ mà có võ</t>
   </si>
   <si>
-    <t>./data/images/2022/DAU_DOAN_HOAN_MY.jpg</t>
+    <t>./data/images/2022/DAU_DOAN_HOAN_MY.webp</t>
   </si>
   <si>
     <t>Lê  Thị Ngọc</t>
@@ -1618,7 +1621,7 @@
     <t>Quảng Thuần</t>
   </si>
   <si>
-    <t>./data/images/2022/LE_THI_THANH_NHAN.jpg</t>
+    <t>./data/images/2022/LE_THI_THANH_NHAN.webp</t>
   </si>
   <si>
     <t>Nguyễn Văn Rin</t>
@@ -1630,13 +1633,13 @@
     <t>Nguyện Thành</t>
   </si>
   <si>
-    <t>./data/images/2022/NGUYEN_VAN_RIN.jpg</t>
+    <t>./data/images/2022/NGUYEN_VAN_RIN.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Mỹ Duyên</t>
   </si>
   <si>
-    <t>./data/images/2022/NGUYEN_THI_MY_DUYEN.jpg</t>
+    <t>./data/images/2022/NGUYEN_THI_MY_DUYEN.webp</t>
   </si>
   <si>
     <t>Châu Phước Nhật</t>
@@ -1648,7 +1651,7 @@
     <t>Nhuận Tuệ</t>
   </si>
   <si>
-    <t>./data/images/2022/CHAU_PHUOC_NHAT.jpg</t>
+    <t>./data/images/2022/CHAU_PHUOC_NHAT.webp</t>
   </si>
   <si>
     <t>Trần Như Nhã Kỳ</t>
@@ -1657,7 +1660,7 @@
     <t>Kỳ</t>
   </si>
   <si>
-    <t>./data/images/2022/TRAN_NHU_NHA_KY.jpg</t>
+    <t>./data/images/2022/TRAN_NHU_NHA_KY.webp</t>
   </si>
   <si>
     <t>Lê Thị Diễm My (Mymyno)</t>
@@ -1666,19 +1669,19 @@
     <t>Nhuận Hiền</t>
   </si>
   <si>
-    <t>./data/images/2022/LE_THI_DIEM_MY.jpg</t>
+    <t>./data/images/2022/LE_THI_DIEM_MY.webp</t>
   </si>
   <si>
     <t>Dương Thị Thanh Tâm</t>
   </si>
   <si>
-    <t>./data/images/2022/DUONG_THI_THANH_TAM.jpg</t>
+    <t>./data/images/2022/DUONG_THI_THANH_TAM.webp</t>
   </si>
   <si>
     <t>Hồ Thị Thảo Tiên</t>
   </si>
   <si>
-    <t>./data/images/2022/HO_THI_THAO_TIEN.jpg</t>
+    <t>./data/images/2022/HO_THI_THAO_TIEN.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Kim Tuyến</t>
@@ -1693,7 +1696,7 @@
     <t>Đào Thị Bích Thảo</t>
   </si>
   <si>
-    <t>./data/images/2022/DAO_THI_BICH_THAO.jpg</t>
+    <t>./data/images/2022/DAO_THI_BICH_THAO.webp</t>
   </si>
   <si>
     <t>Hồ Thị Thanh Hiền</t>
@@ -1702,7 +1705,7 @@
     <t>Nhuận Đức</t>
   </si>
   <si>
-    <t>./data/images/2022/HO_THI_THANH_HIEN.jpg</t>
+    <t>./data/images/2022/HO_THI_THANH_HIEN.webp</t>
   </si>
   <si>
     <t>Lê Thị Xuân Nhàn (Nhàn Lee)</t>
@@ -1711,7 +1714,7 @@
     <t>Mình đây tuy chẳng cao sang. Chỉ mong cố gắng, vững vàng mai sau</t>
   </si>
   <si>
-    <t>./data/images/2022/LE_THI_XUAN_NHAN.jpg</t>
+    <t>./data/images/2022/LE_THI_XUAN_NHAN.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Diệp Linh (Nhỏ)</t>
@@ -1720,7 +1723,7 @@
     <t>smile</t>
   </si>
   <si>
-    <t>./data/images/2022/NGUYEN_THI_DIEP_LINH.jpg</t>
+    <t>./data/images/2022/NGUYEN_THI_DIEP_LINH.webp</t>
   </si>
   <si>
     <t>Lê Thị Kim Ngân</t>
@@ -1729,7 +1732,7 @@
     <t>Photo girl</t>
   </si>
   <si>
-    <t>./data/images/2021/LE_THI_KIM_NGAN.jpg</t>
+    <t>./data/images/2021/LE_THI_KIM_NGAN.webp</t>
   </si>
   <si>
     <t>Bạch Thị Thu Thảo (Tabi)</t>
@@ -1741,7 +1744,7 @@
     <t>Thảo Tabi</t>
   </si>
   <si>
-    <t>./data/images/2021/BACH_THI_THU_THAO.jpg</t>
+    <t>./data/images/2021/BACH_THI_THU_THAO.webp</t>
   </si>
   <si>
     <t>Nguyễn Khánh Hà</t>
@@ -1750,7 +1753,7 @@
     <t>oyoui</t>
   </si>
   <si>
-    <t>./data/images/2021/NGUYEN_KHANH_HA.jpg</t>
+    <t>./data/images/2021/NGUYEN_KHANH_HA.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Nhật Trâm (Na)</t>
@@ -1759,7 +1762,7 @@
     <t>Nhat Tram</t>
   </si>
   <si>
-    <t>./data/images/2021/NGUYEN_THI_NHAT_TRAM.jpg</t>
+    <t>./data/images/2021/NGUYEN_THI_NHAT_TRAM.webp</t>
   </si>
   <si>
     <t>Trần Thị Quỳnh Phương</t>
@@ -1771,7 +1774,7 @@
     <t>Mãi yêu Chánh Tâm</t>
   </si>
   <si>
-    <t>./data/images/2021/TRAN_THI_QUYNH_PHUONG.jpg</t>
+    <t>./data/images/2021/TRAN_THI_QUYNH_PHUONG.webp</t>
   </si>
   <si>
     <t>Phan Thị Cẩm Nhi (Nhem cute)</t>
@@ -1783,7 +1786,7 @@
     <t>Nhuận Hỷ</t>
   </si>
   <si>
-    <t>./data/images/2021/PHAN_THI_CAM_NHI.jpg</t>
+    <t>./data/images/2021/PHAN_THI_CAM_NHI.webp</t>
   </si>
   <si>
     <t>Nguyễn Văn Hồng Ngọc (Right)</t>
@@ -1793,6 +1796,9 @@
   </si>
   <si>
     <t>Quảng Ân</t>
+  </si>
+  <si>
+    <t>./data/images/2021/NGUYEN_THI_DIEM_AI.webp</t>
   </si>
   <si>
     <t>Lê Thị Ngọc (Ngọtle)</t>
@@ -2636,7 +2642,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2662,9 +2668,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4046,10 +4049,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -4058,13 +4061,13 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="H2" s="1">
-        <v>5.0</v>
+        <v>668</v>
+      </c>
+      <c r="H2" s="2">
+        <v>6.0</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -4072,25 +4075,25 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="H3" s="1">
-        <v>3.0</v>
+        <v>673</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2.0</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -4098,10 +4101,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
@@ -4110,13 +4113,13 @@
         <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="H4" s="1">
-        <v>5.0</v>
+        <v>676</v>
+      </c>
+      <c r="H4" s="2">
+        <v>6.0</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -4124,22 +4127,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>144</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4150,25 +4153,25 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>280</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="H6" s="1">
-        <v>6.0</v>
+        <v>684</v>
+      </c>
+      <c r="H6" s="2">
+        <v>5.0</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -4176,10 +4179,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -4188,10 +4191,10 @@
         <v>52</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4202,25 +4205,25 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>139</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H8" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -4228,25 +4231,25 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>39</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="H9" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1"/>
@@ -5293,22 +5296,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6363,22 +6366,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6389,10 +6392,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -6401,10 +6404,10 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7458,22 +7461,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>52</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="H2" s="7">
         <v>5.0</v>
@@ -8528,22 +8531,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="H2" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -8551,22 +8554,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H3" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1"/>
@@ -9620,22 +9623,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>146</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -9646,25 +9649,25 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>267</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H3" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -9672,7 +9675,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -9684,13 +9687,13 @@
         <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="H4" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -9698,22 +9701,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>175</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -10767,22 +10770,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -10793,22 +10796,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -10819,22 +10822,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -10845,7 +10848,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>71</v>
@@ -10857,10 +10860,10 @@
         <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -10871,7 +10874,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>222</v>
@@ -10883,10 +10886,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -11909,7 +11912,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -15033,8 +15036,8 @@
     <col customWidth="1" min="1" max="1" width="8.56"/>
     <col customWidth="1" min="2" max="2" width="30.33"/>
     <col customWidth="1" min="3" max="3" width="8.56"/>
-    <col customWidth="1" min="4" max="4" width="21.44"/>
-    <col customWidth="1" min="5" max="5" width="41.89"/>
+    <col customWidth="1" min="4" max="4" width="8.89"/>
+    <col customWidth="1" min="5" max="5" width="13.89"/>
     <col customWidth="1" min="6" max="6" width="38.78"/>
     <col customWidth="1" min="7" max="7" width="39.0"/>
     <col customWidth="1" min="8" max="8" width="11.67"/>
@@ -15090,7 +15093,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -15116,7 +15119,7 @@
         <v>18</v>
       </c>
       <c r="H3" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -15142,7 +15145,7 @@
         <v>23</v>
       </c>
       <c r="H4" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -15168,7 +15171,7 @@
         <v>28</v>
       </c>
       <c r="H5" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -15194,7 +15197,7 @@
         <v>32</v>
       </c>
       <c r="H6" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -15220,7 +15223,7 @@
         <v>36</v>
       </c>
       <c r="H7" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -15246,7 +15249,7 @@
         <v>41</v>
       </c>
       <c r="H8" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -15272,7 +15275,7 @@
         <v>45</v>
       </c>
       <c r="H9" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -15298,7 +15301,7 @@
         <v>49</v>
       </c>
       <c r="H10" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -15324,7 +15327,7 @@
         <v>54</v>
       </c>
       <c r="H11" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -15347,7 +15350,7 @@
         <v>56</v>
       </c>
       <c r="H12" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -15373,7 +15376,7 @@
         <v>60</v>
       </c>
       <c r="H13" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -15399,7 +15402,7 @@
         <v>64</v>
       </c>
       <c r="H14" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1"/>
@@ -16438,25 +16441,25 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="H2" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="3">
@@ -16464,22 +16467,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H3" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="4">
@@ -16487,25 +16490,25 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>208</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="H4" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="5">
@@ -16513,22 +16516,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H5" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="6">
@@ -16536,22 +16539,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H6" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="7">
@@ -16559,22 +16562,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>192</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="H7" s="2">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="8">
@@ -16582,13 +16585,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>26</v>
@@ -16597,7 +16600,7 @@
         <v>123</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -16608,13 +16611,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>26</v>
@@ -16623,10 +16626,10 @@
         <v>123</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="H9" s="2">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="10">
@@ -16634,13 +16637,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>39</v>
@@ -16649,7 +16652,7 @@
         <v>123</v>
       </c>
       <c r="H10" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="11">
@@ -16657,7 +16660,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>159</v>
@@ -16666,13 +16669,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H11" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="12">
@@ -16680,7 +16683,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>208</v>
@@ -16689,13 +16692,13 @@
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H12" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="13">
@@ -16703,22 +16706,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H13" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="14">
@@ -16726,22 +16729,22 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H14" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="15">
@@ -16749,10 +16752,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -16761,10 +16764,10 @@
         <v>26</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="H15" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="16">
@@ -16772,22 +16775,22 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H16" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="17">
@@ -16795,22 +16798,22 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H17" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="18">
@@ -16818,7 +16821,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>75</v>
@@ -16827,13 +16830,13 @@
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H18" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="19">
@@ -16841,22 +16844,22 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H19" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="20">
@@ -16864,7 +16867,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>144</v>
@@ -16873,13 +16876,13 @@
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H20" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="21">
@@ -16887,7 +16890,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -16896,13 +16899,13 @@
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H21" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="22">
@@ -16910,7 +16913,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>263</v>
@@ -16919,13 +16922,13 @@
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H22" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="23">
@@ -16933,7 +16936,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>167</v>
@@ -16942,13 +16945,13 @@
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H23" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="24">
@@ -16956,7 +16959,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>94</v>
@@ -16965,13 +16968,13 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H24" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="25">
@@ -16979,22 +16982,22 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H25" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="26">
@@ -17002,7 +17005,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>79</v>
@@ -17011,13 +17014,13 @@
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H26" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="27">
@@ -17025,7 +17028,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>20</v>
@@ -17040,7 +17043,7 @@
         <v>123</v>
       </c>
       <c r="H27" s="2">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="28">
@@ -17048,7 +17051,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>267</v>
@@ -17063,7 +17066,7 @@
         <v>123</v>
       </c>
       <c r="H28" s="2">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="29">
@@ -17071,7 +17074,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>51</v>
@@ -17080,13 +17083,13 @@
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H29" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="30">
@@ -17094,7 +17097,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>180</v>
@@ -17103,13 +17106,13 @@
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H30" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="31">
@@ -17117,22 +17120,22 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H31" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="32">
@@ -17140,7 +17143,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>90</v>
@@ -17149,13 +17152,13 @@
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H32" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="33">
@@ -17163,7 +17166,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>175</v>
@@ -17172,13 +17175,13 @@
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H33" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="34">
@@ -17186,7 +17189,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>177</v>
@@ -17195,13 +17198,13 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H34" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="35">
@@ -17209,22 +17212,22 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H35" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="36">
@@ -17232,22 +17235,22 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H36" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="37">
@@ -17255,7 +17258,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>165</v>
@@ -17264,13 +17267,13 @@
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H37" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="38">
@@ -17278,22 +17281,22 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H38" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="39">
@@ -17301,7 +17304,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>20</v>
@@ -17310,13 +17313,13 @@
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H39" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="40">
@@ -17333,13 +17336,13 @@
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H40" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="41">
@@ -17347,7 +17350,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
@@ -17356,13 +17359,13 @@
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H41" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="42">
@@ -17370,22 +17373,22 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H42" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="43">
@@ -17393,22 +17396,22 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H43" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="44">
@@ -17416,7 +17419,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>148</v>
@@ -17425,13 +17428,13 @@
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H44" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="45">
@@ -17439,22 +17442,22 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H45" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="46">
@@ -17462,22 +17465,22 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H46" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="47">
@@ -17485,22 +17488,22 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H47" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="48">
@@ -17508,22 +17511,22 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H48" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="49">
@@ -17531,7 +17534,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>300</v>
@@ -17540,13 +17543,13 @@
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H49" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="50">
@@ -17554,7 +17557,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>278</v>
@@ -17569,7 +17572,7 @@
         <v>123</v>
       </c>
       <c r="H50" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="51">
@@ -17577,22 +17580,22 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H51" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="52">
@@ -17600,7 +17603,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>271</v>
@@ -17609,13 +17612,13 @@
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H52" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="53">
@@ -17623,22 +17626,22 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H53" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="54">
@@ -17646,22 +17649,22 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H54" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="55">
@@ -17669,22 +17672,22 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H55" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="56">
@@ -17692,7 +17695,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>90</v>
@@ -17701,13 +17704,13 @@
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H56" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="57">
@@ -17715,22 +17718,22 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H57" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="58">
@@ -17738,7 +17741,7 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>192</v>
@@ -17747,13 +17750,13 @@
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H58" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="59">
@@ -17761,7 +17764,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>15</v>
@@ -17770,13 +17773,13 @@
         <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H59" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="60">
@@ -17784,23 +17787,23 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>123</v>
       </c>
       <c r="G60" s="9"/>
-      <c r="H60" s="10">
-        <v>8.0</v>
+      <c r="H60" s="2">
+        <v>10.0</v>
       </c>
     </row>
     <row r="61">
@@ -17808,22 +17811,22 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H61" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="62">
@@ -17831,22 +17834,22 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H62" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="63">
@@ -17854,22 +17857,22 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H63" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="64">
@@ -17877,22 +17880,22 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H64" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="65">
@@ -17900,22 +17903,22 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H65" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="66">
@@ -17923,7 +17926,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>144</v>
@@ -17932,13 +17935,13 @@
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H66" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="67">
@@ -17946,7 +17949,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>15</v>
@@ -17955,13 +17958,13 @@
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H67" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="68">
@@ -17969,7 +17972,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>129</v>
@@ -17978,13 +17981,13 @@
         <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H68" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="69">
@@ -17992,7 +17995,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>75</v>
@@ -18004,10 +18007,10 @@
         <v>26</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H69" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="70">
@@ -18015,22 +18018,22 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H70" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="71">
@@ -18038,22 +18041,22 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H71" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="72">
@@ -18061,22 +18064,22 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H72" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="73">
@@ -18084,22 +18087,22 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H73" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="74">
@@ -18107,7 +18110,7 @@
         <v>73.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>208</v>
@@ -18116,13 +18119,13 @@
         <v>10</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H74" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="75">
@@ -18130,22 +18133,22 @@
         <v>74.0</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>123</v>
       </c>
       <c r="H75" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>
@@ -18454,8 +18457,8 @@
       <c r="G11" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="1">
-        <v>4.0</v>
+      <c r="H11" s="2">
+        <v>3.0</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -18533,7 +18536,7 @@
         <v>114</v>
       </c>
       <c r="H14" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -18608,7 +18611,7 @@
         <v>123</v>
       </c>
       <c r="H17" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
@@ -18657,7 +18660,7 @@
         <v>123</v>
       </c>
       <c r="H19" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -18680,7 +18683,7 @@
         <v>123</v>
       </c>
       <c r="H20" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -18703,7 +18706,7 @@
         <v>123</v>
       </c>
       <c r="H21" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -18729,7 +18732,7 @@
         <v>137</v>
       </c>
       <c r="H22" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -18778,7 +18781,7 @@
         <v>123</v>
       </c>
       <c r="H24" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -18801,7 +18804,7 @@
         <v>123</v>
       </c>
       <c r="H25" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -18824,7 +18827,7 @@
         <v>123</v>
       </c>
       <c r="H26" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -18847,7 +18850,7 @@
         <v>123</v>
       </c>
       <c r="H27" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -18873,7 +18876,7 @@
         <v>152</v>
       </c>
       <c r="H28" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -18896,7 +18899,7 @@
         <v>123</v>
       </c>
       <c r="H29" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -18919,7 +18922,7 @@
         <v>123</v>
       </c>
       <c r="H30" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -18942,7 +18945,7 @@
         <v>123</v>
       </c>
       <c r="H31" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -18965,7 +18968,7 @@
         <v>123</v>
       </c>
       <c r="H32" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -18991,7 +18994,7 @@
         <v>162</v>
       </c>
       <c r="H33" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
@@ -19014,7 +19017,7 @@
         <v>123</v>
       </c>
       <c r="H34" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -19037,7 +19040,7 @@
         <v>123</v>
       </c>
       <c r="H35" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
@@ -19063,7 +19066,7 @@
         <v>168</v>
       </c>
       <c r="H36" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -19086,7 +19089,7 @@
         <v>123</v>
       </c>
       <c r="H37" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -19109,7 +19112,7 @@
         <v>123</v>
       </c>
       <c r="H38" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -19132,7 +19135,7 @@
         <v>123</v>
       </c>
       <c r="H39" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -19155,7 +19158,7 @@
         <v>123</v>
       </c>
       <c r="H40" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -19178,7 +19181,7 @@
         <v>123</v>
       </c>
       <c r="H41" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -19201,7 +19204,7 @@
         <v>123</v>
       </c>
       <c r="H42" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -19224,7 +19227,7 @@
         <v>123</v>
       </c>
       <c r="H43" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -19247,7 +19250,7 @@
         <v>123</v>
       </c>
       <c r="H44" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
@@ -19270,7 +19273,7 @@
         <v>123</v>
       </c>
       <c r="H45" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
@@ -19293,7 +19296,7 @@
         <v>123</v>
       </c>
       <c r="H46" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -19319,7 +19322,7 @@
         <v>187</v>
       </c>
       <c r="H47" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
@@ -19345,7 +19348,7 @@
         <v>190</v>
       </c>
       <c r="H48" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
@@ -19397,7 +19400,7 @@
         <v>198</v>
       </c>
       <c r="H50" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
@@ -19423,7 +19426,7 @@
         <v>201</v>
       </c>
       <c r="H51" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
@@ -19449,7 +19452,7 @@
         <v>204</v>
       </c>
       <c r="H52" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
@@ -19472,7 +19475,7 @@
         <v>123</v>
       </c>
       <c r="H53" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
@@ -19495,7 +19498,7 @@
         <v>123</v>
       </c>
       <c r="H54" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
@@ -19518,7 +19521,7 @@
         <v>123</v>
       </c>
       <c r="H55" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
@@ -19544,7 +19547,7 @@
         <v>212</v>
       </c>
       <c r="H56" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
@@ -19567,7 +19570,7 @@
         <v>123</v>
       </c>
       <c r="H57" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
@@ -19593,7 +19596,7 @@
         <v>217</v>
       </c>
       <c r="H58" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
@@ -19619,7 +19622,7 @@
         <v>220</v>
       </c>
       <c r="H59" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
@@ -19645,7 +19648,7 @@
         <v>223</v>
       </c>
       <c r="H60" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
@@ -19671,7 +19674,7 @@
         <v>225</v>
       </c>
       <c r="H61" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
@@ -19697,7 +19700,7 @@
         <v>228</v>
       </c>
       <c r="H62" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -19723,7 +19726,7 @@
         <v>231</v>
       </c>
       <c r="H63" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
@@ -19749,7 +19752,7 @@
         <v>233</v>
       </c>
       <c r="H64" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
@@ -19775,7 +19778,7 @@
         <v>237</v>
       </c>
       <c r="H65" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
@@ -19801,7 +19804,7 @@
         <v>240</v>
       </c>
       <c r="H66" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
@@ -19827,7 +19830,7 @@
         <v>243</v>
       </c>
       <c r="H67" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
@@ -19853,7 +19856,7 @@
         <v>246</v>
       </c>
       <c r="H68" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
@@ -19879,7 +19882,7 @@
         <v>250</v>
       </c>
       <c r="H69" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -19931,7 +19934,7 @@
         <v>257</v>
       </c>
       <c r="H71" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
@@ -19957,7 +19960,7 @@
         <v>261</v>
       </c>
       <c r="H72" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
@@ -19983,7 +19986,7 @@
         <v>265</v>
       </c>
       <c r="H73" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
@@ -20006,7 +20009,7 @@
         <v>123</v>
       </c>
       <c r="H74" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
@@ -20029,7 +20032,7 @@
         <v>123</v>
       </c>
       <c r="H75" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
@@ -20055,7 +20058,7 @@
         <v>273</v>
       </c>
       <c r="H76" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
@@ -20078,7 +20081,7 @@
         <v>123</v>
       </c>
       <c r="H77" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
@@ -20101,7 +20104,7 @@
         <v>123</v>
       </c>
       <c r="H78" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
@@ -20124,7 +20127,7 @@
         <v>123</v>
       </c>
       <c r="H79" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
@@ -20150,7 +20153,7 @@
         <v>282</v>
       </c>
       <c r="H80" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
@@ -20176,7 +20179,7 @@
         <v>286</v>
       </c>
       <c r="H81" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
@@ -20202,7 +20205,7 @@
         <v>289</v>
       </c>
       <c r="H82" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
@@ -20228,7 +20231,7 @@
         <v>291</v>
       </c>
       <c r="H83" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
@@ -20280,7 +20283,7 @@
         <v>298</v>
       </c>
       <c r="H85" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
@@ -20306,7 +20309,7 @@
         <v>302</v>
       </c>
       <c r="H86" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
@@ -20332,7 +20335,7 @@
         <v>306</v>
       </c>
       <c r="H87" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
@@ -20358,7 +20361,7 @@
         <v>309</v>
       </c>
       <c r="H88" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
@@ -20384,7 +20387,7 @@
         <v>312</v>
       </c>
       <c r="H89" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
@@ -20410,7 +20413,7 @@
         <v>314</v>
       </c>
       <c r="H90" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
@@ -20433,7 +20436,7 @@
         <v>123</v>
       </c>
       <c r="H91" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1"/>
@@ -21370,9 +21373,10 @@
     <col customWidth="1" min="3" max="3" width="10.67"/>
     <col customWidth="1" min="4" max="4" width="21.44"/>
     <col customWidth="1" min="5" max="5" width="17.0"/>
-    <col customWidth="1" min="6" max="6" width="46.78"/>
-    <col customWidth="1" min="7" max="7" width="51.22"/>
-    <col customWidth="1" min="8" max="26" width="8.56"/>
+    <col customWidth="1" min="6" max="6" width="27.56"/>
+    <col customWidth="1" min="7" max="7" width="43.56"/>
+    <col customWidth="1" min="8" max="8" width="11.0"/>
+    <col customWidth="1" min="9" max="26" width="8.56"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -21411,20 +21415,20 @@
       <c r="C2" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>67</v>
+      <c r="D2" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="H2" s="1">
-        <v>4.0</v>
+        <v>320</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3.0</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -21432,10 +21436,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>67</v>
@@ -21444,10 +21448,10 @@
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -21458,10 +21462,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>67</v>
@@ -21470,10 +21474,10 @@
         <v>39</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -21484,10 +21488,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>67</v>
@@ -21496,10 +21500,10 @@
         <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -21510,7 +21514,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>180</v>
@@ -21522,10 +21526,10 @@
         <v>39</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -21536,7 +21540,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
@@ -21548,10 +21552,10 @@
         <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H7" s="2">
         <v>4.0</v>
@@ -21562,25 +21566,25 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="H8" s="1">
-        <v>5.0</v>
+        <v>343</v>
+      </c>
+      <c r="H8" s="2">
+        <v>7.0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -21588,25 +21592,25 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="H9" s="1">
-        <v>5.0</v>
+        <v>346</v>
+      </c>
+      <c r="H9" s="2">
+        <v>7.0</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -21614,22 +21618,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H10" s="1">
         <v>5.0</v>
@@ -21640,7 +21644,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>62</v>
@@ -21652,10 +21656,10 @@
         <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -21666,7 +21670,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>58</v>
@@ -21678,13 +21682,13 @@
         <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H12" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -21692,10 +21696,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -21704,10 +21708,10 @@
         <v>52</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -21718,10 +21722,10 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
@@ -21730,10 +21734,10 @@
         <v>39</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H14" s="2">
         <v>6.0</v>
@@ -21744,7 +21748,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>185</v>
@@ -21756,13 +21760,13 @@
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H15" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -21770,7 +21774,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>148</v>
@@ -21782,13 +21786,13 @@
         <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H16" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
@@ -21796,10 +21800,10 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
@@ -21808,10 +21812,10 @@
         <v>21</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H17" s="2">
         <v>6.0</v>
@@ -21822,7 +21826,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>146</v>
@@ -21834,13 +21838,13 @@
         <v>21</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H18" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
@@ -21848,10 +21852,10 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -21860,10 +21864,10 @@
         <v>39</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H19" s="1">
         <v>6.0</v>
@@ -21874,7 +21878,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>144</v>
@@ -21886,10 +21890,10 @@
         <v>52</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="H20" s="1">
-        <v>7.0</v>
+        <v>382</v>
+      </c>
+      <c r="H20" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -21897,10 +21901,10 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -21912,10 +21916,10 @@
         <v>56</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="H21" s="1">
-        <v>7.0</v>
+        <v>385</v>
+      </c>
+      <c r="H21" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -21923,10 +21927,10 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -21938,10 +21942,10 @@
         <v>56</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="H22" s="1">
-        <v>7.0</v>
+        <v>387</v>
+      </c>
+      <c r="H22" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -21949,10 +21953,10 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -21961,13 +21965,13 @@
         <v>26</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="H23" s="1">
-        <v>7.0</v>
+        <v>391</v>
+      </c>
+      <c r="H23" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -21975,10 +21979,10 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
@@ -21987,13 +21991,13 @@
         <v>39</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="H24" s="1">
-        <v>6.0</v>
+        <v>395</v>
+      </c>
+      <c r="H24" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -22001,7 +22005,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>175</v>
@@ -22013,13 +22017,13 @@
         <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="H25" s="1">
-        <v>7.0</v>
+        <v>398</v>
+      </c>
+      <c r="H25" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -22027,25 +22031,25 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="H26" s="1">
-        <v>4.0</v>
+        <v>402</v>
+      </c>
+      <c r="H26" s="2">
+        <v>3.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -22053,10 +22057,10 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
@@ -22065,13 +22069,13 @@
         <v>11</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="H27" s="1">
-        <v>7.0</v>
+        <v>406</v>
+      </c>
+      <c r="H27" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -22079,10 +22083,10 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
@@ -22094,10 +22098,10 @@
         <v>123</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="H28" s="1">
-        <v>6.0</v>
+        <v>409</v>
+      </c>
+      <c r="H28" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -22105,10 +22109,10 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
@@ -22117,13 +22121,13 @@
         <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H29" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -22131,7 +22135,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>71</v>
@@ -22146,10 +22150,10 @@
         <v>123</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H30" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -22157,10 +22161,10 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -22172,10 +22176,10 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H31" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -22183,10 +22187,10 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
@@ -22195,13 +22199,13 @@
         <v>16</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H32" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -22209,10 +22213,10 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
@@ -22221,13 +22225,13 @@
         <v>26</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H33" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
@@ -22235,7 +22239,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>165</v>
@@ -22247,13 +22251,13 @@
         <v>21</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H34" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -22261,7 +22265,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>208</v>
@@ -22273,13 +22277,13 @@
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H35" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
@@ -22287,10 +22291,10 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -22299,13 +22303,13 @@
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H36" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -22313,10 +22317,10 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
@@ -22325,13 +22329,13 @@
         <v>52</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H37" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -22339,10 +22343,10 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
@@ -22351,10 +22355,10 @@
         <v>52</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H38" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -22362,10 +22366,10 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
@@ -22374,13 +22378,13 @@
         <v>39</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H39" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -22388,7 +22392,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>71</v>
@@ -22400,13 +22404,13 @@
         <v>39</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H40" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -22414,10 +22418,10 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
@@ -22426,13 +22430,13 @@
         <v>26</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H41" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -22440,7 +22444,7 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>167</v>
@@ -22455,10 +22459,10 @@
         <v>123</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H42" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -22466,10 +22470,10 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
@@ -22481,10 +22485,10 @@
         <v>123</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H43" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -22492,7 +22496,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>43</v>
@@ -22507,7 +22511,7 @@
         <v>123</v>
       </c>
       <c r="H44" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
@@ -22515,7 +22519,7 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>43</v>
@@ -22527,7 +22531,7 @@
         <v>16</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H45" s="2">
         <v>6.0</v>
@@ -22538,7 +22542,7 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>62</v>
@@ -22553,7 +22557,7 @@
         <v>123</v>
       </c>
       <c r="H46" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -22561,7 +22565,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>15</v>
@@ -22573,7 +22577,7 @@
         <v>39</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H47" s="2">
         <v>6.0</v>
@@ -22584,7 +22588,7 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>90</v>
@@ -22599,10 +22603,10 @@
         <v>123</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H48" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
@@ -22610,10 +22614,10 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
@@ -22622,13 +22626,13 @@
         <v>21</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H49" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
@@ -22636,7 +22640,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>278</v>
@@ -22651,10 +22655,10 @@
         <v>123</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H50" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -23628,11 +23632,11 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="8.56"/>
     <col customWidth="1" min="2" max="2" width="35.0"/>
-    <col customWidth="1" min="3" max="3" width="13.33"/>
-    <col customWidth="1" min="4" max="4" width="22.22"/>
-    <col customWidth="1" min="5" max="5" width="30.0"/>
-    <col customWidth="1" min="6" max="6" width="37.22"/>
-    <col customWidth="1" min="7" max="7" width="51.22"/>
+    <col customWidth="1" min="3" max="3" width="7.33"/>
+    <col customWidth="1" min="4" max="4" width="13.67"/>
+    <col customWidth="1" min="5" max="5" width="15.11"/>
+    <col customWidth="1" min="6" max="6" width="17.67"/>
+    <col customWidth="1" min="7" max="7" width="29.44"/>
     <col customWidth="1" min="8" max="26" width="8.56"/>
   </cols>
   <sheetData>
@@ -23667,22 +23671,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -23693,10 +23697,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>67</v>
@@ -23705,10 +23709,10 @@
         <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -23719,7 +23723,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>90</v>
@@ -23731,10 +23735,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -23745,25 +23749,25 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="H5" s="1">
-        <v>4.0</v>
+        <v>487</v>
+      </c>
+      <c r="H5" s="2">
+        <v>5.0</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -23771,22 +23775,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -23797,22 +23801,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>167</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -23823,10 +23827,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>67</v>
@@ -23835,10 +23839,10 @@
         <v>16</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H8" s="2">
         <v>4.0</v>
@@ -23849,22 +23853,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -23875,7 +23879,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>259</v>
@@ -23887,13 +23891,13 @@
         <v>21</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H10" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -23901,7 +23905,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>271</v>
@@ -23913,10 +23917,10 @@
         <v>39</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -23927,25 +23931,25 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H12" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -23953,25 +23957,25 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="H13" s="1">
-        <v>4.0</v>
+        <v>520</v>
+      </c>
+      <c r="H13" s="2">
+        <v>3.0</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -23979,7 +23983,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>79</v>
@@ -24002,10 +24006,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -24014,13 +24018,13 @@
         <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="H15" s="1">
-        <v>7.0</v>
+        <v>525</v>
+      </c>
+      <c r="H15" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -24028,10 +24032,10 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -24040,13 +24044,13 @@
         <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="H16" s="1">
-        <v>7.0</v>
+        <v>529</v>
+      </c>
+      <c r="H16" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
@@ -24054,10 +24058,10 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
@@ -24069,10 +24073,10 @@
         <v>123</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="H17" s="1">
-        <v>8.0</v>
+        <v>531</v>
+      </c>
+      <c r="H17" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
@@ -24080,10 +24084,10 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
@@ -24092,13 +24096,13 @@
         <v>39</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H18" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
@@ -24106,10 +24110,10 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -24118,13 +24122,13 @@
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H19" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -24132,25 +24136,25 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H20" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -24158,10 +24162,10 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -24173,7 +24177,7 @@
         <v>123</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H21" s="2">
         <v>7.0</v>
@@ -24184,7 +24188,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>175</v>
@@ -24199,10 +24203,10 @@
         <v>123</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H22" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -24210,10 +24214,10 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -24222,10 +24226,10 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H23" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -24233,7 +24237,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>71</v>
@@ -24248,10 +24252,10 @@
         <v>123</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H24" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -24259,7 +24263,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>263</v>
@@ -24271,13 +24275,13 @@
         <v>26</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H25" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -24285,10 +24289,10 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -24297,13 +24301,13 @@
         <v>26</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H26" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -24311,7 +24315,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>167</v>
@@ -24323,13 +24327,13 @@
         <v>26</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H27" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
@@ -25327,10 +25331,10 @@
     <col customWidth="1" min="1" max="1" width="10.11"/>
     <col customWidth="1" min="2" max="2" width="23.33"/>
     <col customWidth="1" min="3" max="3" width="13.89"/>
-    <col customWidth="1" min="4" max="4" width="22.33"/>
-    <col customWidth="1" min="5" max="5" width="22.11"/>
-    <col customWidth="1" min="6" max="6" width="20.67"/>
-    <col customWidth="1" min="7" max="7" width="44.67"/>
+    <col customWidth="1" min="4" max="4" width="20.11"/>
+    <col customWidth="1" min="5" max="5" width="14.33"/>
+    <col customWidth="1" min="6" max="6" width="13.56"/>
+    <col customWidth="1" min="7" max="7" width="14.33"/>
     <col customWidth="1" min="8" max="26" width="8.56"/>
   </cols>
   <sheetData>
@@ -25365,10 +25369,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -25377,10 +25381,10 @@
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25391,25 +25395,25 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="H3" s="1">
-        <v>5.0</v>
+        <v>566</v>
+      </c>
+      <c r="H3" s="2">
+        <v>7.0</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -25417,25 +25421,25 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="H4" s="1">
-        <v>5.0</v>
+        <v>569</v>
+      </c>
+      <c r="H4" s="2">
+        <v>7.0</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -25443,7 +25447,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>185</v>
@@ -25455,10 +25459,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -25469,22 +25473,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>129</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -25495,22 +25499,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -25521,7 +25525,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>79</v>
@@ -25544,10 +25548,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
@@ -25556,10 +25560,13 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>584</v>
       </c>
       <c r="H9" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -25567,7 +25574,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>79</v>
@@ -26594,9 +26601,9 @@
     <col customWidth="1" min="2" max="2" width="22.11"/>
     <col customWidth="1" min="3" max="3" width="9.78"/>
     <col customWidth="1" min="4" max="4" width="22.0"/>
-    <col customWidth="1" min="5" max="5" width="29.67"/>
-    <col customWidth="1" min="6" max="6" width="29.22"/>
-    <col customWidth="1" min="7" max="7" width="40.67"/>
+    <col customWidth="1" min="5" max="5" width="18.22"/>
+    <col customWidth="1" min="6" max="6" width="16.89"/>
+    <col customWidth="1" min="7" max="7" width="19.33"/>
     <col customWidth="1" min="8" max="26" width="8.56"/>
   </cols>
   <sheetData>
@@ -26631,25 +26638,25 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="H2" s="1">
-        <v>3.0</v>
+        <v>590</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2.0</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -26657,22 +26664,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>167</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -26683,22 +26690,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -26709,22 +26716,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -26735,22 +26742,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>144</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -26761,10 +26768,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -26773,13 +26780,13 @@
         <v>16</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="H7" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -26787,10 +26794,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
@@ -26801,8 +26808,8 @@
       <c r="F8" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H8" s="1">
-        <v>7.0</v>
+      <c r="H8" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -26810,7 +26817,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>267</v>
@@ -26822,13 +26829,13 @@
         <v>52</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="H9" s="1">
-        <v>7.0</v>
+        <v>609</v>
+      </c>
+      <c r="H9" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -26836,7 +26843,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>267</v>
@@ -26850,8 +26857,8 @@
       <c r="F10" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H10" s="1">
-        <v>7.0</v>
+      <c r="H10" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -26859,7 +26866,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>62</v>
@@ -26871,13 +26878,13 @@
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="H11" s="1">
-        <v>7.0</v>
+        <v>613</v>
+      </c>
+      <c r="H11" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -26885,7 +26892,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>62</v>
@@ -26897,13 +26904,13 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H12" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -26911,10 +26918,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -26923,13 +26930,13 @@
         <v>26</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H13" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1"/>
@@ -27936,10 +27943,10 @@
     <col customWidth="1" min="1" max="1" width="8.56"/>
     <col customWidth="1" min="2" max="2" width="19.67"/>
     <col customWidth="1" min="3" max="3" width="8.56"/>
-    <col customWidth="1" min="4" max="4" width="27.33"/>
+    <col customWidth="1" min="4" max="4" width="16.78"/>
     <col customWidth="1" min="5" max="5" width="15.67"/>
-    <col customWidth="1" min="6" max="6" width="19.0"/>
-    <col customWidth="1" min="7" max="7" width="39.67"/>
+    <col customWidth="1" min="6" max="6" width="11.0"/>
+    <col customWidth="1" min="7" max="7" width="16.67"/>
     <col customWidth="1" min="8" max="26" width="8.56"/>
   </cols>
   <sheetData>
@@ -27974,25 +27981,25 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="H2" s="1">
-        <v>4.0</v>
+        <v>624</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3.0</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -28000,22 +28007,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -28026,22 +28033,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28052,10 +28059,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -28066,8 +28073,8 @@
       <c r="F5" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H5" s="1">
-        <v>7.0</v>
+      <c r="H5" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -28075,7 +28082,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>263</v>
@@ -28087,13 +28094,13 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="H6" s="1">
-        <v>7.0</v>
+        <v>637</v>
+      </c>
+      <c r="H6" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -28101,10 +28108,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -28113,10 +28120,10 @@
         <v>39</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28127,25 +28134,25 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H8" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1"/>
@@ -29161,7 +29168,7 @@
     <col customWidth="1" min="4" max="4" width="13.0"/>
     <col customWidth="1" min="5" max="5" width="12.67"/>
     <col customWidth="1" min="6" max="6" width="20.67"/>
-    <col customWidth="1" min="7" max="7" width="51.22"/>
+    <col customWidth="1" min="7" max="7" width="16.44"/>
     <col customWidth="1" min="8" max="26" width="8.56"/>
   </cols>
   <sheetData>
@@ -29196,10 +29203,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -29208,13 +29215,13 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="H2" s="1">
-        <v>6.0</v>
+        <v>649</v>
+      </c>
+      <c r="H2" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -29222,25 +29229,25 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="H3" s="1">
-        <v>6.0</v>
+        <v>653</v>
+      </c>
+      <c r="H3" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -29248,7 +29255,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>183</v>
@@ -29260,10 +29267,10 @@
         <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H4" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -29271,25 +29278,25 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="H5" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -29297,22 +29304,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29323,7 +29330,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>58</v>
@@ -29335,13 +29342,13 @@
         <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="H7" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1"/>

--- a/data/DATA.xlsx
+++ b/data/DATA.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="855">
   <si>
     <t>id</t>
   </si>
@@ -249,7 +249,7 @@
     <t>Nhà Thơ</t>
   </si>
   <si>
-    <t>./data/images/2024/TRAN_THI_XUAN_DIEU.jpg</t>
+    <t>./data/images/2024/TRAN_THI_XUAN_DIEU.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Dạ Thảo (Nai)</t>
@@ -261,7 +261,7 @@
     <t>Con Nai vàng ngơ ngác</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_THI_DA_THAO.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_DA_THAO.webp</t>
   </si>
   <si>
     <t>Nguyễn Phan Bảo Uyên</t>
@@ -273,7 +273,7 @@
     <t>🧶</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_PHAN_BAO_UYEN.jpg</t>
+    <t>./data/images/2024/NGUYEN_PHAN_BAO_UYEN.webp</t>
   </si>
   <si>
     <t>Tôn Nữ Yến Ngọc</t>
@@ -285,7 +285,7 @@
     <t>Sống cùng cảm xúc</t>
   </si>
   <si>
-    <t>./data/images/2024/TON_NU_YEN_NGOC.jpg</t>
+    <t>./data/images/2024/TON_NU_YEN_NGOC.webp</t>
   </si>
   <si>
     <t>Nguyễn Luýt (Nhất Tam)</t>
@@ -297,7 +297,7 @@
     <t>Nguyện người thường An 🍀</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_LUYT.jpg</t>
+    <t>./data/images/2024/NGUYEN_LUYT.webp</t>
   </si>
   <si>
     <t>Phạm Đức Định</t>
@@ -318,7 +318,7 @@
     <t>Em Ánh Nguyệt</t>
   </si>
   <si>
-    <t xml:space="preserve">./data/images/2024/TRAN_NGUYEN_ANH_NHI.jpg
+    <t xml:space="preserve">./data/images/2024/TRAN_NGUYEN_ANH_NHI.webp
 </t>
   </si>
   <si>
@@ -331,7 +331,7 @@
     <t>Hương Queen</t>
   </si>
   <si>
-    <t>./data/images/2024/TRAN_THI_THU_HUONG.jpg</t>
+    <t>./data/images/2024/TRAN_THI_THU_HUONG.webp</t>
   </si>
   <si>
     <t>Trần Nguyễn Ánh Nguyệt</t>
@@ -343,7 +343,7 @@
     <t>Chị Ánh Nhi</t>
   </si>
   <si>
-    <t xml:space="preserve">./data/images/2024/TRAN_NGUYEN_ANH_NGUYET.jpg
+    <t xml:space="preserve">./data/images/2024/TRAN_NGUYEN_ANH_NGUYET.webp
 </t>
   </si>
   <si>
@@ -356,7 +356,7 @@
     <t>bạn thân Minh Anh</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_THI_NHAT_ANH.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_NHAT_ANH.webp</t>
   </si>
   <si>
     <t>Phan Lê Xuân Hiếu (Híu)</t>
@@ -368,7 +368,7 @@
     <t>hihi</t>
   </si>
   <si>
-    <t>./data/images/2024/PHAN_LE_XUAN_HIEU.jpg</t>
+    <t>./data/images/2024/PHAN_LE_XUAN_HIEU.webp</t>
   </si>
   <si>
     <t>Lê Thị Huyền Trang (Suu)</t>
@@ -377,7 +377,7 @@
     <t>Người hay cười 😊</t>
   </si>
   <si>
-    <t>./data/images/2024/LE_THI_HUYEN_TRANG.jpg</t>
+    <t>./data/images/2024/LE_THI_HUYEN_TRANG.webp</t>
   </si>
   <si>
     <t>Nguyễn Ngọc Thanh Thảo (naaaa)</t>
@@ -386,7 +386,7 @@
     <t>na xinh vứi đôi má hồnggg</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_NGOC_THANH_THAO.jpg</t>
+    <t>./data/images/2024/NGUYEN_NGOC_THANH_THAO.webp</t>
   </si>
   <si>
     <t>Nguyễn Hoàng Minh Anh (Ma)</t>
@@ -395,7 +395,7 @@
     <t>bạn thân Nhật Anh</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_HOANG_MINH_ANH.jpg</t>
+    <t>./data/images/2024/NGUYEN_HOANG_MINH_ANH.webp</t>
   </si>
   <si>
     <t>Trương Văn Quý</t>
@@ -407,7 +407,7 @@
     <t>Nhuận Thiền Dũng</t>
   </si>
   <si>
-    <t>./data/images/2024/TRUONG_VAN_QUY.jpg</t>
+    <t>./data/images/2024/TRUONG_VAN_QUY.webp</t>
   </si>
   <si>
     <t>Nguyễn Hồ Minh Anh (Manh)</t>
@@ -425,7 +425,7 @@
     <t>Quỳnh Như hihi</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_HOANG_QUYNH_NHU.jpg</t>
+    <t>./data/images/2024/NGUYEN_HOANG_QUYNH_NHU.webp</t>
   </si>
   <si>
     <t>Nguyễn Văn Phương</t>
@@ -446,6 +446,12 @@
     <t>Thủy</t>
   </si>
   <si>
+    <t>Nhuận Diệu</t>
+  </si>
+  <si>
+    <t>./data/images/2024/TON_NU_THI_THUY.webp</t>
+  </si>
+  <si>
     <t>Dương Thị Ngọc Bích</t>
   </si>
   <si>
@@ -455,7 +461,7 @@
     <t>Cái gì không làm được thì mình vừa khóc vừa làm!</t>
   </si>
   <si>
-    <t>./data/images/2024/DUONG_THI_NGOC_BICH.jpg</t>
+    <t>./data/images/2024/DUONG_THI_NGOC_BICH.webp</t>
   </si>
   <si>
     <t>Nguyễn Phúc (Phúc Phúc)</t>
@@ -467,7 +473,7 @@
     <t>Người lái tàu</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_PHUC.jpg</t>
+    <t>./data/images/2024/NGUYEN_PHUC.webp</t>
   </si>
   <si>
     <t>Đào Gia Hiếu</t>
@@ -500,7 +506,7 @@
     <t>Nhuận Bảo Lộc</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_VAN_LOC.jpg</t>
+    <t>./data/images/2024/NGUYEN_VAN_LOC.webp</t>
   </si>
   <si>
     <t>Trương Thị Phương Loan</t>
@@ -530,7 +536,7 @@
     <t>dưa hấu không hạt</t>
   </si>
   <si>
-    <t>./data/images/2024/MAI_THI_THANH_THAO.jpg</t>
+    <t>./data/images/2024/MAI_THI_THANH_THAO.webp</t>
   </si>
   <si>
     <t>Lê Thị Bích Ngọc</t>
@@ -548,7 +554,7 @@
     <t>Linh</t>
   </si>
   <si>
-    <t>./data/images/2024/DANG_THI_KHANH_LINH.jpg</t>
+    <t>./data/images/2024/DANG_THI_KHANH_LINH.webp</t>
   </si>
   <si>
     <t>Lê Thị Băng Nhi</t>
@@ -605,7 +611,7 @@
     <t>Yêu múa ca</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_MAI_THUY_TRAM.jpg</t>
+    <t>./data/images/2024/NGUYEN_MAI_THUY_TRAM.webp</t>
   </si>
   <si>
     <t>Lê Thị Minh Ngọc</t>
@@ -614,7 +620,7 @@
     <t>Cá nọc</t>
   </si>
   <si>
-    <t>./data/images/2024/LE_THI_MINH_NGOC.jpg</t>
+    <t>./data/images/2024/LE_THI_MINH_NGOC.webp</t>
   </si>
   <si>
     <t>Nguyễn Anh Tài (Tài Cris)</t>
@@ -626,7 +632,7 @@
     <t>Siêu đầu bếp Chánh Tâm</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_ANH_TAI.jpg</t>
+    <t>./data/images/2024/NGUYEN_ANH_TAI.webp</t>
   </si>
   <si>
     <t>Nguyễn Mai Lan</t>
@@ -638,7 +644,7 @@
     <t>hướng nội ít nói</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_MAI_LAN.jpg</t>
+    <t>./data/images/2024/NGUYEN_MAI_LAN.webp</t>
   </si>
   <si>
     <t>Ngô Vũ Vân Châu (mani - mina)</t>
@@ -647,7 +653,7 @@
     <t>thích chị Nhật Uyên - thích BTT 📷</t>
   </si>
   <si>
-    <t>./data/images/2024/NGO_VU_VAN_CHAU.jpg</t>
+    <t>./data/images/2024/NGO_VU_VAN_CHAU.webp</t>
   </si>
   <si>
     <t>Lê Thị Kim Anh (Ka)</t>
@@ -656,7 +662,7 @@
     <t>Chị Ka</t>
   </si>
   <si>
-    <t>./data/images/2024/LE_THI_KIM_ANH.jpg</t>
+    <t>./data/images/2024/LE_THI_KIM_ANH.webp</t>
   </si>
   <si>
     <t>Nguyễn Trần Quang Khánh</t>
@@ -680,7 +686,7 @@
     <t>Nhuận Minh</t>
   </si>
   <si>
-    <t>./data/images/2024/DO_ANH_KIET.jpg</t>
+    <t>./data/images/2024/DO_ANH_KIET.webp</t>
   </si>
   <si>
     <t>Lê Thị Hồng Hạnh</t>
@@ -695,7 +701,7 @@
     <t>Nhuận Bảoo ✌️</t>
   </si>
   <si>
-    <t>./data/images/2024/TRAN_NGOC_MINH_CHAU.jpg</t>
+    <t>./data/images/2024/TRAN_NGOC_MINH_CHAU.webp</t>
   </si>
   <si>
     <t>Phan Uyên Phương (Bơ)</t>
@@ -704,7 +710,7 @@
     <t>hướng nội part time</t>
   </si>
   <si>
-    <t>./data/images/2024/PHAN_UYEN_PHUONG.jpg</t>
+    <t>./data/images/2024/PHAN_UYEN_PHUONG.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Thu Hồng</t>
@@ -713,13 +719,13 @@
     <t>Hồng</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_THI_THU_HONG.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_THU_HONG.webp</t>
   </si>
   <si>
     <t>Huỳnh Thị Thu Phương (Pủm)</t>
   </si>
   <si>
-    <t>./data/images/2024/HUYNH_THI_THU_PHUONG.jpg</t>
+    <t>./data/images/2024/HUYNH_THI_THU_PHUONG.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Uyên Thi</t>
@@ -728,7 +734,7 @@
     <t>Đang học ở Đài Loan</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_THI_UYEN_THI.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_UYEN_THI.webp</t>
   </si>
   <si>
     <t>Trần Phước Thanh Thanh</t>
@@ -737,13 +743,13 @@
     <t>Nhuận Phước</t>
   </si>
   <si>
-    <t>./data/images/2024/TRAN_PHUOC_THANH_THANH.jpg</t>
+    <t>./data/images/2024/TRAN_PHUOC_THANH_THANH.webp</t>
   </si>
   <si>
     <t>Võ Thị Hồng My</t>
   </si>
   <si>
-    <t>./data/images/2024/VO_THI_HONG_MY.jpg</t>
+    <t>./data/images/2024/VO_THI_HONG_MY.webp</t>
   </si>
   <si>
     <t>Huỳnh Thị Huê</t>
@@ -755,7 +761,7 @@
     <t>Hay cười 🌱</t>
   </si>
   <si>
-    <t xml:space="preserve">./data/images/2024/HUYNH_THI_HUE.jpg
+    <t xml:space="preserve">./data/images/2024/HUYNH_THI_HUE.webp
 </t>
   </si>
   <si>
@@ -765,7 +771,7 @@
     <t>Doanh</t>
   </si>
   <si>
-    <t>./data/images/2024/TRAN_THIEN_DOANH.jpg</t>
+    <t>./data/images/2024/TRAN_THIEN_DOANH.webp</t>
   </si>
   <si>
     <t>Nguyễn Tấn Nhật Huy</t>
@@ -774,7 +780,7 @@
     <t>Quảng Đức</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_TAN_NHAT_HUY.jpg</t>
+    <t>./data/images/2024/NGUYEN_TAN_NHAT_HUY.webp</t>
   </si>
   <si>
     <t>Châu Bảo Anh (May)</t>
@@ -783,7 +789,7 @@
     <t>Vạn Thông</t>
   </si>
   <si>
-    <t xml:space="preserve">./data/images/2024/CHAU_BAO_ANH.jpg
+    <t xml:space="preserve">./data/images/2024/CHAU_BAO_ANH.webp
 </t>
   </si>
   <si>
@@ -796,7 +802,7 @@
     <t>Biển Trần</t>
   </si>
   <si>
-    <t>./data/images/2024/TRAN_HOANG_THANH_HAI.jpg</t>
+    <t>./data/images/2024/TRAN_HOANG_THANH_HAI.webp</t>
   </si>
   <si>
     <t>Trương Ngọc Hiếu An (Đậu)</t>
@@ -805,7 +811,7 @@
     <t>Đậu Hũ</t>
   </si>
   <si>
-    <t>./data/images/2024/TRUONG_NGOC_HIEU_AN.jpg</t>
+    <t>./data/images/2024/TRUONG_NGOC_HIEU_AN.webp</t>
   </si>
   <si>
     <t>Trần Nguyễn Xuân Nghi</t>
@@ -817,7 +823,7 @@
     <t>ngại ngùng</t>
   </si>
   <si>
-    <t>./data/images/2024/TRAN_NGUYEN_XUAN_NGHI.jpg</t>
+    <t>./data/images/2024/TRAN_NGUYEN_XUAN_NGHI.webp</t>
   </si>
   <si>
     <t>Nguyễn Đình Nam</t>
@@ -829,7 +835,7 @@
     <t>Ồn nhất Tương Sinh</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_DINH_NAM.jpg</t>
+    <t>./data/images/2024/NGUYEN_DINH_NAM.webp</t>
   </si>
   <si>
     <t>Hồ Thị Thanh Hiền (Sam)</t>
@@ -841,7 +847,7 @@
     <t>Thanh Hiền</t>
   </si>
   <si>
-    <t>./data/images/2024/HO_THI_THANH_HIEN.jpg</t>
+    <t>./data/images/2024/HO_THI_THANH_HIEN.webp</t>
   </si>
   <si>
     <t>Nguyễn Bảo Hưng</t>
@@ -865,7 +871,7 @@
     <t>Nhuận Thường</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_HOANG_DUC.jpg</t>
+    <t>./data/images/2024/NGUYEN_HOANG_DUC.webp</t>
   </si>
   <si>
     <t>Nguyễn Quốc Việt</t>
@@ -892,7 +898,7 @@
     <t>Bông 🌸</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_THI_QUYNH_NHAN.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_QUYNH_NHAN.webp</t>
   </si>
   <si>
     <t>Phạm Văn Quốc Tấn</t>
@@ -904,7 +910,7 @@
     <t>Quảng Đạt</t>
   </si>
   <si>
-    <t>./data/images/2024/PHAM_VAN_QUOC_TAN.jpg</t>
+    <t>./data/images/2024/PHAM_VAN_QUOC_TAN.webp</t>
   </si>
   <si>
     <t>Phan Văn Đạt</t>
@@ -913,13 +919,13 @@
     <t>Đạt</t>
   </si>
   <si>
-    <t>./data/images/2024/PHAN_VAN_DAT.jpg</t>
+    <t>./data/images/2024/PHAN_VAN_DAT.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Thu Thảo</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_THI_THU_THAO.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_THU_THAO.webp</t>
   </si>
   <si>
     <t>Đặng Hoàng Hoài Thư</t>
@@ -928,7 +934,7 @@
     <t>Thực tập Ban chấp hành</t>
   </si>
   <si>
-    <t>./data/images/2024/DANG_HOANG_HOAI_THU.jpg</t>
+    <t>./data/images/2024/DANG_HOANG_HOAI_THU.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Ánh Tuyết (Út)</t>
@@ -940,7 +946,7 @@
     <t>Nguyên Lan</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_THI_ANH_TUYET.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_ANH_TUYET.webp</t>
   </si>
   <si>
     <t>Võ Thị Kiều Yến</t>
@@ -952,7 +958,7 @@
     <t>Quãng Ngọc</t>
   </si>
   <si>
-    <t>./data/images/2024/VO_THI_KIEU_YEN.jpg</t>
+    <t>./data/images/2024/VO_THI_KIEU_YEN.webp</t>
   </si>
   <si>
     <t>Lê Thị Thu Thuỷ</t>
@@ -964,7 +970,7 @@
     <t>Như Tiên</t>
   </si>
   <si>
-    <t>./data/images/2024/LE_THI_THU_THUY.jpg</t>
+    <t>./data/images/2024/LE_THI_THU_THUY.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Đăng Nhi</t>
@@ -973,7 +979,7 @@
     <t>Thể Tường</t>
   </si>
   <si>
-    <t>./data/images/2024/NGUYEN_THI_DANG_NHI.jpg</t>
+    <t>./data/images/2024/NGUYEN_THI_DANG_NHI.webp</t>
   </si>
   <si>
     <t>Đinh Thị Hiếu Thảo (Mắm)</t>
@@ -982,13 +988,13 @@
     <t>Thánh Nhiên</t>
   </si>
   <si>
-    <t>./data/images/2024/DINH_THI_HIEU_THAO.jpg</t>
+    <t>./data/images/2024/DINH_THI_HIEU_THAO.webp</t>
   </si>
   <si>
     <t>Huỳnh Thị Kim Ánh</t>
   </si>
   <si>
-    <t>./data/images/2024/HUYNH_THI_KIM_ANH.jpg</t>
+    <t>./data/images/2024/HUYNH_THI_KIM_ANH.webp</t>
   </si>
   <si>
     <t>Nguyễn Phan Phước Hải Anh</t>
@@ -4049,10 +4055,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -4061,10 +4067,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -4075,22 +4081,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="H3" s="2">
         <v>2.0</v>
@@ -4101,10 +4107,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
@@ -4113,10 +4119,10 @@
         <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="H4" s="2">
         <v>6.0</v>
@@ -4127,22 +4133,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4153,22 +4159,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -4179,10 +4185,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -4191,10 +4197,10 @@
         <v>52</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4205,22 +4211,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -4231,22 +4237,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>39</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -5296,22 +5302,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6366,22 +6372,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6392,10 +6398,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -6404,10 +6410,10 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7461,22 +7467,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>52</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H2" s="7">
         <v>5.0</v>
@@ -8531,19 +8537,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -8554,16 +8560,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>123</v>
@@ -9623,22 +9629,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -9649,22 +9655,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -9675,7 +9681,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -9687,10 +9693,10 @@
         <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="H4" s="2">
         <v>4.0</v>
@@ -9701,22 +9707,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -10770,22 +10776,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -10796,22 +10802,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -10822,22 +10828,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -10848,7 +10854,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>71</v>
@@ -10860,10 +10866,10 @@
         <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -10874,10 +10880,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
@@ -10886,10 +10892,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -11912,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -16441,22 +16447,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="H2" s="2">
         <v>8.0</v>
@@ -16467,16 +16473,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>123</v>
@@ -16490,22 +16496,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -16516,16 +16522,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>123</v>
@@ -16539,16 +16545,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>123</v>
@@ -16562,19 +16568,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="H7" s="2">
         <v>5.0</v>
@@ -16585,13 +16591,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>26</v>
@@ -16600,7 +16606,7 @@
         <v>123</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -16611,13 +16617,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>26</v>
@@ -16626,7 +16632,7 @@
         <v>123</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -16637,13 +16643,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>39</v>
@@ -16660,16 +16666,16 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>123</v>
@@ -16683,16 +16689,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>123</v>
@@ -16706,16 +16712,16 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>123</v>
@@ -16729,16 +16735,16 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>123</v>
@@ -16752,10 +16758,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -16764,7 +16770,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
@@ -16775,16 +16781,16 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>123</v>
@@ -16798,16 +16804,16 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>123</v>
@@ -16821,7 +16827,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>75</v>
@@ -16830,7 +16836,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>123</v>
@@ -16844,16 +16850,16 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>123</v>
@@ -16867,16 +16873,16 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>123</v>
@@ -16890,7 +16896,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -16899,7 +16905,7 @@
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>123</v>
@@ -16913,16 +16919,16 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>123</v>
@@ -16936,16 +16942,16 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>123</v>
@@ -16959,7 +16965,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>94</v>
@@ -16968,7 +16974,7 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>123</v>
@@ -16982,16 +16988,16 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>123</v>
@@ -17005,7 +17011,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>79</v>
@@ -17014,7 +17020,7 @@
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>123</v>
@@ -17028,7 +17034,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>20</v>
@@ -17051,10 +17057,10 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
@@ -17074,7 +17080,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>51</v>
@@ -17083,7 +17089,7 @@
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>123</v>
@@ -17097,16 +17103,16 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>123</v>
@@ -17120,16 +17126,16 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>123</v>
@@ -17143,7 +17149,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>90</v>
@@ -17152,7 +17158,7 @@
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>123</v>
@@ -17166,16 +17172,16 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>123</v>
@@ -17189,16 +17195,16 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>123</v>
@@ -17212,16 +17218,16 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>123</v>
@@ -17235,16 +17241,16 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>123</v>
@@ -17258,16 +17264,16 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>123</v>
@@ -17281,16 +17287,16 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>123</v>
@@ -17304,7 +17310,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>20</v>
@@ -17313,7 +17319,7 @@
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>123</v>
@@ -17327,7 +17333,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -17336,7 +17342,7 @@
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>123</v>
@@ -17350,7 +17356,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
@@ -17359,7 +17365,7 @@
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>123</v>
@@ -17373,16 +17379,16 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>123</v>
@@ -17396,16 +17402,16 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>123</v>
@@ -17419,16 +17425,16 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>123</v>
@@ -17442,16 +17448,16 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>123</v>
@@ -17465,16 +17471,16 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>123</v>
@@ -17488,16 +17494,16 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>123</v>
@@ -17511,16 +17517,16 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>123</v>
@@ -17534,16 +17540,16 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>123</v>
@@ -17557,10 +17563,10 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
@@ -17580,16 +17586,16 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>123</v>
@@ -17603,16 +17609,16 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>123</v>
@@ -17626,16 +17632,16 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>123</v>
@@ -17649,16 +17655,16 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>123</v>
@@ -17672,16 +17678,16 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>123</v>
@@ -17695,7 +17701,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>90</v>
@@ -17704,7 +17710,7 @@
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>123</v>
@@ -17718,16 +17724,16 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>123</v>
@@ -17741,16 +17747,16 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>123</v>
@@ -17764,7 +17770,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>15</v>
@@ -17773,7 +17779,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>123</v>
@@ -17787,16 +17793,16 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>123</v>
@@ -17811,16 +17817,16 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>123</v>
@@ -17834,16 +17840,16 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>123</v>
@@ -17857,16 +17863,16 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>123</v>
@@ -17880,16 +17886,16 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>123</v>
@@ -17903,16 +17909,16 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>123</v>
@@ -17926,16 +17932,16 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>123</v>
@@ -17949,7 +17955,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>15</v>
@@ -17958,7 +17964,7 @@
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>123</v>
@@ -17972,7 +17978,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>129</v>
@@ -17981,7 +17987,7 @@
         <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>123</v>
@@ -17995,7 +18001,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>75</v>
@@ -18007,7 +18013,7 @@
         <v>26</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
@@ -18018,16 +18024,16 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>123</v>
@@ -18041,16 +18047,16 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>123</v>
@@ -18064,16 +18070,16 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>123</v>
@@ -18087,16 +18093,16 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>123</v>
@@ -18110,16 +18116,16 @@
         <v>73.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>123</v>
@@ -18133,16 +18139,16 @@
         <v>74.0</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>123</v>
@@ -18702,8 +18708,11 @@
       <c r="E21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>123</v>
+      <c r="F21" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -18714,10 +18723,10 @@
         <v>19.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -18726,10 +18735,10 @@
         <v>52</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -18740,10 +18749,10 @@
         <v>20.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -18752,10 +18761,10 @@
         <v>52</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H23" s="2">
         <v>6.0</v>
@@ -18766,7 +18775,7 @@
         <v>21.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>106</v>
@@ -18789,10 +18798,10 @@
         <v>22.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
@@ -18812,10 +18821,10 @@
         <v>23.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>10</v>
@@ -18835,10 +18844,10 @@
         <v>24.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
@@ -18858,10 +18867,10 @@
         <v>25.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
@@ -18870,10 +18879,10 @@
         <v>52</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -18884,10 +18893,10 @@
         <v>26.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
@@ -18907,10 +18916,10 @@
         <v>27.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
@@ -18930,7 +18939,7 @@
         <v>28.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>62</v>
@@ -18953,10 +18962,10 @@
         <v>29.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>10</v>
@@ -18976,7 +18985,7 @@
         <v>30.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>71</v>
@@ -18988,10 +18997,10 @@
         <v>21</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -19002,7 +19011,7 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>79</v>
@@ -19025,10 +19034,10 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>10</v>
@@ -19048,10 +19057,10 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -19063,7 +19072,7 @@
         <v>123</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -19074,7 +19083,7 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>90</v>
@@ -19097,7 +19106,7 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>58</v>
@@ -19120,10 +19129,10 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
@@ -19143,7 +19152,7 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>71</v>
@@ -19166,10 +19175,10 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>10</v>
@@ -19189,10 +19198,10 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>10</v>
@@ -19212,10 +19221,10 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
@@ -19235,10 +19244,10 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
@@ -19258,7 +19267,7 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>75</v>
@@ -19281,10 +19290,10 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>10</v>
@@ -19304,10 +19313,10 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
@@ -19316,10 +19325,10 @@
         <v>16</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H47" s="2">
         <v>9.0</v>
@@ -19330,7 +19339,7 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>79</v>
@@ -19342,10 +19351,10 @@
         <v>16</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -19356,10 +19365,10 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>10</v>
@@ -19368,10 +19377,10 @@
         <v>16</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H49" s="2">
         <v>6.0</v>
@@ -19382,10 +19391,10 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>10</v>
@@ -19394,10 +19403,10 @@
         <v>16</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -19408,7 +19417,7 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>58</v>
@@ -19420,10 +19429,10 @@
         <v>16</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H51" s="2">
         <v>9.0</v>
@@ -19434,7 +19443,7 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>62</v>
@@ -19446,10 +19455,10 @@
         <v>16</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H52" s="2">
         <v>9.0</v>
@@ -19460,10 +19469,10 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
@@ -19483,10 +19492,10 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>10</v>
@@ -19506,10 +19515,10 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>10</v>
@@ -19529,10 +19538,10 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>10</v>
@@ -19541,10 +19550,10 @@
         <v>16</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H56" s="2">
         <v>9.0</v>
@@ -19555,10 +19564,10 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>10</v>
@@ -19578,7 +19587,7 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>58</v>
@@ -19590,10 +19599,10 @@
         <v>39</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H58" s="2">
         <v>9.0</v>
@@ -19604,7 +19613,7 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>129</v>
@@ -19616,10 +19625,10 @@
         <v>39</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H59" s="2">
         <v>9.0</v>
@@ -19630,10 +19639,10 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>10</v>
@@ -19645,7 +19654,7 @@
         <v>123</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H60" s="2">
         <v>9.0</v>
@@ -19656,7 +19665,7 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>129</v>
@@ -19671,7 +19680,7 @@
         <v>123</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H61" s="2">
         <v>9.0</v>
@@ -19682,10 +19691,10 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>10</v>
@@ -19694,10 +19703,10 @@
         <v>39</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H62" s="2">
         <v>9.0</v>
@@ -19708,7 +19717,7 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>25</v>
@@ -19720,10 +19729,10 @@
         <v>39</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H63" s="2">
         <v>9.0</v>
@@ -19734,7 +19743,7 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>30</v>
@@ -19749,7 +19758,7 @@
         <v>123</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H64" s="2">
         <v>9.0</v>
@@ -19760,10 +19769,10 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>10</v>
@@ -19772,10 +19781,10 @@
         <v>39</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H65" s="2">
         <v>9.0</v>
@@ -19786,10 +19795,10 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>10</v>
@@ -19801,7 +19810,7 @@
         <v>123</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H66" s="2">
         <v>9.0</v>
@@ -19812,10 +19821,10 @@
         <v>65.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
@@ -19824,10 +19833,10 @@
         <v>39</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H67" s="2">
         <v>9.0</v>
@@ -19838,7 +19847,7 @@
         <v>66.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>62</v>
@@ -19850,10 +19859,10 @@
         <v>39</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H68" s="2">
         <v>9.0</v>
@@ -19864,10 +19873,10 @@
         <v>67.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>10</v>
@@ -19876,10 +19885,10 @@
         <v>39</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H69" s="2">
         <v>9.0</v>
@@ -19890,7 +19899,7 @@
         <v>68.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>20</v>
@@ -19902,10 +19911,10 @@
         <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H70" s="2">
         <v>6.0</v>
@@ -19916,10 +19925,10 @@
         <v>69.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>10</v>
@@ -19928,10 +19937,10 @@
         <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H71" s="2">
         <v>6.0</v>
@@ -19942,10 +19951,10 @@
         <v>70.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
@@ -19954,10 +19963,10 @@
         <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H72" s="2">
         <v>9.0</v>
@@ -19968,10 +19977,10 @@
         <v>71.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
@@ -19980,10 +19989,10 @@
         <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H73" s="2">
         <v>9.0</v>
@@ -19994,10 +20003,10 @@
         <v>72.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>10</v>
@@ -20017,10 +20026,10 @@
         <v>73.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>10</v>
@@ -20040,10 +20049,10 @@
         <v>74.0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>10</v>
@@ -20052,10 +20061,10 @@
         <v>11</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H76" s="2">
         <v>6.0</v>
@@ -20066,10 +20075,10 @@
         <v>75.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>10</v>
@@ -20089,7 +20098,7 @@
         <v>76.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>34</v>
@@ -20112,10 +20121,10 @@
         <v>77.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
@@ -20135,10 +20144,10 @@
         <v>78.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>10</v>
@@ -20147,10 +20156,10 @@
         <v>21</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H80" s="2">
         <v>9.0</v>
@@ -20161,10 +20170,10 @@
         <v>79.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>10</v>
@@ -20173,10 +20182,10 @@
         <v>21</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H81" s="2">
         <v>9.0</v>
@@ -20187,10 +20196,10 @@
         <v>80.0</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>10</v>
@@ -20202,7 +20211,7 @@
         <v>123</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H82" s="2">
         <v>9.0</v>
@@ -20213,7 +20222,7 @@
         <v>81.0</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>71</v>
@@ -20228,7 +20237,7 @@
         <v>123</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H83" s="2">
         <v>9.0</v>
@@ -20239,13 +20248,13 @@
         <v>82.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>11</v>
@@ -20254,7 +20263,7 @@
         <v>123</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H84" s="2">
         <v>4.0</v>
@@ -20265,10 +20274,10 @@
         <v>83.0</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>10</v>
@@ -20277,10 +20286,10 @@
         <v>52</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H85" s="2">
         <v>9.0</v>
@@ -20291,10 +20300,10 @@
         <v>84.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>10</v>
@@ -20303,10 +20312,10 @@
         <v>52</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H86" s="2">
         <v>9.0</v>
@@ -20317,10 +20326,10 @@
         <v>85.0</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>10</v>
@@ -20329,10 +20338,10 @@
         <v>26</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H87" s="2">
         <v>9.0</v>
@@ -20343,7 +20352,7 @@
         <v>86.0</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>90</v>
@@ -20355,10 +20364,10 @@
         <v>21</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H88" s="2">
         <v>9.0</v>
@@ -20369,7 +20378,7 @@
         <v>87.0</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>71</v>
@@ -20381,10 +20390,10 @@
         <v>16</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H89" s="2">
         <v>9.0</v>
@@ -20395,7 +20404,7 @@
         <v>88.0</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>34</v>
@@ -20410,7 +20419,7 @@
         <v>123</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H90" s="2">
         <v>9.0</v>
@@ -20421,7 +20430,7 @@
         <v>89.0</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>62</v>
@@ -21410,22 +21419,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -21436,10 +21445,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>67</v>
@@ -21448,10 +21457,10 @@
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -21462,10 +21471,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>67</v>
@@ -21474,10 +21483,10 @@
         <v>39</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -21488,10 +21497,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>67</v>
@@ -21500,10 +21509,10 @@
         <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -21514,10 +21523,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>67</v>
@@ -21526,10 +21535,10 @@
         <v>39</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -21540,7 +21549,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
@@ -21552,10 +21561,10 @@
         <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H7" s="2">
         <v>4.0</v>
@@ -21566,22 +21575,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -21592,22 +21601,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -21618,22 +21627,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H10" s="1">
         <v>5.0</v>
@@ -21644,7 +21653,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>62</v>
@@ -21656,10 +21665,10 @@
         <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -21670,7 +21679,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>58</v>
@@ -21682,10 +21691,10 @@
         <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -21696,10 +21705,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -21708,10 +21717,10 @@
         <v>52</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -21722,10 +21731,10 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
@@ -21734,10 +21743,10 @@
         <v>39</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H14" s="2">
         <v>6.0</v>
@@ -21748,10 +21757,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -21760,10 +21769,10 @@
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -21774,10 +21783,10 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -21786,10 +21795,10 @@
         <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -21800,10 +21809,10 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
@@ -21812,10 +21821,10 @@
         <v>21</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H17" s="2">
         <v>6.0</v>
@@ -21826,10 +21835,10 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
@@ -21838,10 +21847,10 @@
         <v>21</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -21852,10 +21861,10 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -21864,10 +21873,10 @@
         <v>39</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H19" s="1">
         <v>6.0</v>
@@ -21878,10 +21887,10 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
@@ -21890,7 +21899,7 @@
         <v>52</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -21901,10 +21910,10 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -21916,7 +21925,7 @@
         <v>56</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -21927,10 +21936,10 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -21942,7 +21951,7 @@
         <v>56</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -21953,10 +21962,10 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -21965,10 +21974,10 @@
         <v>26</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -21979,10 +21988,10 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
@@ -21991,10 +22000,10 @@
         <v>39</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -22005,10 +22014,10 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
@@ -22017,10 +22026,10 @@
         <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -22031,22 +22040,22 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H26" s="2">
         <v>3.0</v>
@@ -22057,10 +22066,10 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
@@ -22069,10 +22078,10 @@
         <v>11</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -22083,10 +22092,10 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
@@ -22098,7 +22107,7 @@
         <v>123</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -22109,10 +22118,10 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
@@ -22121,10 +22130,10 @@
         <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H29" s="2">
         <v>9.0</v>
@@ -22135,7 +22144,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>71</v>
@@ -22150,7 +22159,7 @@
         <v>123</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H30" s="2">
         <v>9.0</v>
@@ -22161,10 +22170,10 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -22176,7 +22185,7 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H31" s="2">
         <v>9.0</v>
@@ -22187,10 +22196,10 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
@@ -22199,10 +22208,10 @@
         <v>16</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H32" s="2">
         <v>9.0</v>
@@ -22213,10 +22222,10 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
@@ -22225,10 +22234,10 @@
         <v>26</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -22239,10 +22248,10 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
@@ -22251,10 +22260,10 @@
         <v>21</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H34" s="2">
         <v>9.0</v>
@@ -22265,10 +22274,10 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
@@ -22277,10 +22286,10 @@
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H35" s="2">
         <v>9.0</v>
@@ -22291,10 +22300,10 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -22303,10 +22312,10 @@
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -22317,10 +22326,10 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
@@ -22329,10 +22338,10 @@
         <v>52</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H37" s="2">
         <v>9.0</v>
@@ -22343,10 +22352,10 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
@@ -22355,7 +22364,7 @@
         <v>52</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H38" s="2">
         <v>9.0</v>
@@ -22366,10 +22375,10 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
@@ -22378,10 +22387,10 @@
         <v>39</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H39" s="2">
         <v>9.0</v>
@@ -22392,7 +22401,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>71</v>
@@ -22404,10 +22413,10 @@
         <v>39</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H40" s="2">
         <v>9.0</v>
@@ -22418,10 +22427,10 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
@@ -22430,10 +22439,10 @@
         <v>26</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H41" s="2">
         <v>9.0</v>
@@ -22444,10 +22453,10 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
@@ -22459,7 +22468,7 @@
         <v>123</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H42" s="2">
         <v>9.0</v>
@@ -22470,10 +22479,10 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
@@ -22485,7 +22494,7 @@
         <v>123</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H43" s="2">
         <v>9.0</v>
@@ -22496,7 +22505,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>43</v>
@@ -22519,7 +22528,7 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>43</v>
@@ -22531,7 +22540,7 @@
         <v>16</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H45" s="2">
         <v>6.0</v>
@@ -22542,7 +22551,7 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>62</v>
@@ -22565,7 +22574,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>15</v>
@@ -22577,7 +22586,7 @@
         <v>39</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H47" s="2">
         <v>6.0</v>
@@ -22588,7 +22597,7 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>90</v>
@@ -22603,7 +22612,7 @@
         <v>123</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -22614,10 +22623,10 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
@@ -22626,10 +22635,10 @@
         <v>21</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H49" s="2">
         <v>9.0</v>
@@ -22640,10 +22649,10 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
@@ -22655,7 +22664,7 @@
         <v>123</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -23671,22 +23680,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -23697,10 +23706,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>67</v>
@@ -23709,10 +23718,10 @@
         <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -23723,7 +23732,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>90</v>
@@ -23735,10 +23744,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -23749,22 +23758,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -23775,22 +23784,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -23801,22 +23810,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -23827,10 +23836,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>67</v>
@@ -23839,10 +23848,10 @@
         <v>16</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H8" s="2">
         <v>4.0</v>
@@ -23853,22 +23862,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -23879,10 +23888,10 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
@@ -23891,10 +23900,10 @@
         <v>21</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -23905,10 +23914,10 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
@@ -23917,10 +23926,10 @@
         <v>39</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -23931,22 +23940,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H12" s="2">
         <v>5.0</v>
@@ -23957,22 +23966,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H13" s="2">
         <v>3.0</v>
@@ -23983,7 +23992,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>79</v>
@@ -24006,10 +24015,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -24018,10 +24027,10 @@
         <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -24032,10 +24041,10 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -24044,10 +24053,10 @@
         <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -24058,10 +24067,10 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
@@ -24073,7 +24082,7 @@
         <v>123</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="H17" s="2">
         <v>9.0</v>
@@ -24084,10 +24093,10 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
@@ -24096,10 +24105,10 @@
         <v>39</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -24110,10 +24119,10 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -24122,10 +24131,10 @@
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -24136,22 +24145,22 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H20" s="2">
         <v>7.0</v>
@@ -24162,10 +24171,10 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -24177,7 +24186,7 @@
         <v>123</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H21" s="2">
         <v>7.0</v>
@@ -24188,10 +24197,10 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -24203,7 +24212,7 @@
         <v>123</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -24214,10 +24223,10 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -24226,7 +24235,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -24237,7 +24246,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>71</v>
@@ -24252,7 +24261,7 @@
         <v>123</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -24263,10 +24272,10 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -24275,10 +24284,10 @@
         <v>26</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -24289,10 +24298,10 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -24301,10 +24310,10 @@
         <v>26</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H26" s="2">
         <v>9.0</v>
@@ -24315,10 +24324,10 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -24327,10 +24336,10 @@
         <v>26</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -25369,10 +25378,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -25381,10 +25390,10 @@
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25395,22 +25404,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -25421,22 +25430,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -25447,10 +25456,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>67</v>
@@ -25459,10 +25468,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -25473,22 +25482,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>129</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -25499,22 +25508,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -25525,7 +25534,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>79</v>
@@ -25548,10 +25557,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
@@ -25560,10 +25569,10 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -25574,7 +25583,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>79</v>
@@ -26638,22 +26647,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H2" s="2">
         <v>2.0</v>
@@ -26664,22 +26673,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -26690,22 +26699,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -26716,22 +26725,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -26742,22 +26751,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -26768,10 +26777,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -26780,10 +26789,10 @@
         <v>16</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>
@@ -26794,10 +26803,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
@@ -26817,10 +26826,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
@@ -26829,10 +26838,10 @@
         <v>52</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -26843,10 +26852,10 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
@@ -26866,7 +26875,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>62</v>
@@ -26878,10 +26887,10 @@
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -26892,7 +26901,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>62</v>
@@ -26904,10 +26913,10 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -26918,10 +26927,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -26930,10 +26939,10 @@
         <v>26</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H13" s="2">
         <v>9.0</v>
@@ -27981,22 +27990,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -28007,22 +28016,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -28033,22 +28042,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28059,10 +28068,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -28082,10 +28091,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
@@ -28094,10 +28103,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -28108,10 +28117,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -28120,10 +28129,10 @@
         <v>39</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28134,22 +28143,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H8" s="2">
         <v>5.0</v>
@@ -29203,10 +29212,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -29215,10 +29224,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -29229,22 +29238,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -29255,10 +29264,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
@@ -29267,7 +29276,7 @@
         <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -29278,22 +29287,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -29304,22 +29313,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29330,7 +29339,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>58</v>
@@ -29342,10 +29351,10 @@
         <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>

--- a/data/DATA.xlsx
+++ b/data/DATA.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="860">
   <si>
     <t>id</t>
   </si>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Vui vẻ, thích cười </t>
   </si>
   <si>
-    <t>./data/images/2025/LE_THI_THUY_TRANG.jpg</t>
+    <t>./data/images/2025/LE_THI_THUY_TRANG.webp</t>
   </si>
   <si>
     <t>Trần Văn Quang</t>
@@ -96,7 +96,7 @@
     <t>Trầm tính</t>
   </si>
   <si>
-    <t>./data/images/2025/TRAN_VAN_QUANG.jpg</t>
+    <t>./data/images/2025/TRAN_VAN_QUANG.webp</t>
   </si>
   <si>
     <t>Hoàng Ngọc Hoài An</t>
@@ -111,7 +111,7 @@
     <t>Mình là một người low pin nhưng high mood, nhạc là chân ái, deadline là động lực, chưa giỏi lắm nhưng vui là chính</t>
   </si>
   <si>
-    <t>./data/images/2025/HOANG_NGOC_HOAI_AN.jpg</t>
+    <t>./data/images/2025/HOANG_NGOC_HOAI_AN.webp</t>
   </si>
   <si>
     <t xml:space="preserve">Đặng Thị Thu Thanh </t>
@@ -126,7 +126,7 @@
     <t>Khi tâm an, đời sẽ nhẹ</t>
   </si>
   <si>
-    <t>./data/images/2025/DANG_THI_THU_THANH.jpg</t>
+    <t>./data/images/2025/DANG_THI_THU_THANH.webp</t>
   </si>
   <si>
     <t>Lê Nguyễn Phương My (Mắm)</t>
@@ -138,7 +138,7 @@
     <t>Mập nhất gia đình Chánh Tâm</t>
   </si>
   <si>
-    <t>./data/images/2025/LE_NGUYEN_PHUONG_MY.png</t>
+    <t>./data/images/2025/LE_NGUYEN_PHUONG_MY.webp</t>
   </si>
   <si>
     <t>Nguyễn Nhật Ánh (Tia)</t>
@@ -150,7 +150,7 @@
     <t>Tia Nắng</t>
   </si>
   <si>
-    <t>./data/images/2025/NGUYEN_NHAT_ANH.jpg</t>
+    <t>./data/images/2025/NGUYEN_NHAT_ANH.webp</t>
   </si>
   <si>
     <t>Phạm Thị Mỹ Nga (Sư sư)</t>
@@ -165,7 +165,7 @@
     <t>📸</t>
   </si>
   <si>
-    <t>./data/images/2025/PHAM_THI_MY_NGA.jpg</t>
+    <t>./data/images/2025/PHAM_THI_MY_NGA.webp</t>
   </si>
   <si>
     <t>Lê Bảo Trân (Su Zin)</t>
@@ -177,7 +177,7 @@
     <t>Thành viên mới👼🏻</t>
   </si>
   <si>
-    <t>./data/images/2025/LE_BAO_TRAN.jpg</t>
+    <t>./data/images/2025/LE_BAO_TRAN.webp</t>
   </si>
   <si>
     <t>Trần Thị Anh Thư</t>
@@ -189,7 +189,7 @@
     <t>Niệm vô thất</t>
   </si>
   <si>
-    <t>./data/images/2025/TRAN_THI_ANH_THU.jpg</t>
+    <t>./data/images/2025/TRAN_THI_ANH_THU.webp</t>
   </si>
   <si>
     <t>Châu Thị Mỹ Lệ</t>
@@ -204,7 +204,7 @@
     <t>Chân thật trong suy nghĩ tử tế trong hành động🥰</t>
   </si>
   <si>
-    <t>./data/images/2025/CHAU_THI_MY_LE.jpg</t>
+    <t>./data/images/2025/CHAU_THI_MY_LE.webp</t>
   </si>
   <si>
     <t>Lê Thị Trà My</t>
@@ -222,7 +222,7 @@
     <t>hối nượng</t>
   </si>
   <si>
-    <t>./data/images/2025/HO_THI_MINH_CHAU.jpg</t>
+    <t>./data/images/2025/HO_THI_MINH_CHAU.webp</t>
   </si>
   <si>
     <t>Nguyễn Minh Trâm Anh (Nai)</t>
@@ -234,7 +234,7 @@
     <t>Hướng nội fulltime</t>
   </si>
   <si>
-    <t>./data/images/2025/NGUYEN_MINH_TRAM_ANH.jpg</t>
+    <t>./data/images/2025/NGUYEN_MINH_TRAM_ANH.webp</t>
   </si>
   <si>
     <t>Trần Thị Xuân Diệu</t>
@@ -434,10 +434,22 @@
     <t>Phương</t>
   </si>
   <si>
+    <t>Phuongwg Nguyễn</t>
+  </si>
+  <si>
+    <t>./data/images/2024/NGUYEN_VAN_PHUONG.webp</t>
+  </si>
+  <si>
     <t>Nguyễn Quang Gia Khôi</t>
   </si>
   <si>
     <t>Khôi</t>
+  </si>
+  <si>
+    <t>Gia Khôi Quang</t>
+  </si>
+  <si>
+    <t>./data/images/2024/NGUYEN_QUANG_GIA_KHOI.webp</t>
   </si>
   <si>
     <t>Tôn Nữ Thị Thủy</t>
@@ -2309,7 +2321,7 @@
     <t>Mẹ Chánh Tâm</t>
   </si>
   <si>
-    <t>./data/images/NO/CHAU_LIEN_PHUONG.jpg</t>
+    <t>./data/images/NO/CHAU_LIEN_PHUONG.webp</t>
   </si>
   <si>
     <t>Hà Thị Thu</t>
@@ -2321,7 +2333,7 @@
     <t>Hoàng Thị Xuân Vân</t>
   </si>
   <si>
-    <t>./data/images/NO/HOANG_THI_XUAN_VAN.jpg</t>
+    <t>./data/images/NO/HOANG_THI_XUAN_VAN.webp</t>
   </si>
   <si>
     <t>Huỳnh Thị Kim Anh</t>
@@ -2333,13 +2345,16 @@
     <t>Nguyễn Xuân Tài</t>
   </si>
   <si>
-    <t>Rainbow</t>
+    <t>Salt and pepper</t>
+  </si>
+  <si>
+    <t>./data/images/NO/NGUYEN_XUAN_TAI.webp</t>
   </si>
   <si>
     <t>Lê Thị Huyền Ngân (Mắm)</t>
   </si>
   <si>
-    <t>./data/images/NO/LE_THI_HUYEN_NGAN.jpg</t>
+    <t>./data/images/NO/LE_THI_HUYEN_NGAN.webp</t>
   </si>
   <si>
     <t>Nguyễn Hữu Khánh Toàn</t>
@@ -2348,7 +2363,7 @@
     <t>Toàn</t>
   </si>
   <si>
-    <t>./data/images/NO/NGUYEN_HUU_KHANH_TOAN.jpg</t>
+    <t>./data/images/NO/NGUYEN_HUU_KHANH_TOAN.webp</t>
   </si>
   <si>
     <t>Nguyễn Thị Lan Anh</t>
@@ -4055,10 +4070,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -4067,10 +4082,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -4081,22 +4096,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="H3" s="2">
         <v>2.0</v>
@@ -4107,10 +4122,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
@@ -4119,10 +4134,10 @@
         <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="H4" s="2">
         <v>6.0</v>
@@ -4133,22 +4148,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4159,22 +4174,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -4185,10 +4200,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -4197,10 +4212,10 @@
         <v>52</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4211,22 +4226,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -4237,22 +4252,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>39</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -5302,22 +5317,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6372,22 +6387,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6398,10 +6413,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -6410,10 +6425,10 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7467,22 +7482,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>52</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="H2" s="7">
         <v>5.0</v>
@@ -8537,19 +8552,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -8560,16 +8575,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>123</v>
@@ -9629,22 +9644,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -9655,22 +9670,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -9681,7 +9696,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -9693,10 +9708,10 @@
         <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="H4" s="2">
         <v>4.0</v>
@@ -9707,22 +9722,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -10776,22 +10791,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -10802,22 +10817,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -10828,22 +10843,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -10854,7 +10869,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>71</v>
@@ -10866,10 +10881,10 @@
         <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -10880,10 +10895,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
@@ -10892,10 +10907,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -11918,7 +11933,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -16447,22 +16462,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="H2" s="2">
         <v>8.0</v>
@@ -16473,16 +16488,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>123</v>
@@ -16496,22 +16511,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -16522,16 +16537,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>123</v>
@@ -16545,16 +16560,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>123</v>
@@ -16568,19 +16583,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>767</v>
       </c>
       <c r="H7" s="2">
         <v>5.0</v>
@@ -16591,13 +16609,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>26</v>
@@ -16606,7 +16624,7 @@
         <v>123</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -16617,13 +16635,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>26</v>
@@ -16632,7 +16650,7 @@
         <v>123</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -16643,13 +16661,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>39</v>
@@ -16666,16 +16684,16 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>123</v>
@@ -16689,16 +16707,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>123</v>
@@ -16712,16 +16730,16 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>123</v>
@@ -16735,16 +16753,16 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>123</v>
@@ -16758,10 +16776,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -16770,7 +16788,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
@@ -16781,16 +16799,16 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>123</v>
@@ -16804,16 +16822,16 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>123</v>
@@ -16827,7 +16845,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>75</v>
@@ -16836,7 +16854,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>123</v>
@@ -16850,16 +16868,16 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>123</v>
@@ -16873,16 +16891,16 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>123</v>
@@ -16896,7 +16914,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -16905,7 +16923,7 @@
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>123</v>
@@ -16919,16 +16937,16 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>123</v>
@@ -16942,16 +16960,16 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>123</v>
@@ -16965,7 +16983,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>94</v>
@@ -16974,7 +16992,7 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>123</v>
@@ -16988,16 +17006,16 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>123</v>
@@ -17011,7 +17029,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>79</v>
@@ -17020,7 +17038,7 @@
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>123</v>
@@ -17034,7 +17052,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>20</v>
@@ -17057,10 +17075,10 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
@@ -17080,7 +17098,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>51</v>
@@ -17089,7 +17107,7 @@
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>123</v>
@@ -17103,16 +17121,16 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>123</v>
@@ -17126,16 +17144,16 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>123</v>
@@ -17149,7 +17167,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>90</v>
@@ -17158,7 +17176,7 @@
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>123</v>
@@ -17172,16 +17190,16 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>123</v>
@@ -17195,16 +17213,16 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>123</v>
@@ -17218,16 +17236,16 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>123</v>
@@ -17241,16 +17259,16 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>123</v>
@@ -17264,16 +17282,16 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>123</v>
@@ -17287,16 +17305,16 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>123</v>
@@ -17310,7 +17328,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>20</v>
@@ -17319,7 +17337,7 @@
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>123</v>
@@ -17333,7 +17351,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -17342,7 +17360,7 @@
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>123</v>
@@ -17356,7 +17374,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
@@ -17365,7 +17383,7 @@
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>123</v>
@@ -17379,16 +17397,16 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>123</v>
@@ -17402,16 +17420,16 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>123</v>
@@ -17425,16 +17443,16 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>123</v>
@@ -17448,16 +17466,16 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>123</v>
@@ -17471,16 +17489,16 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>123</v>
@@ -17494,16 +17512,16 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>123</v>
@@ -17517,16 +17535,16 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>123</v>
@@ -17540,16 +17558,16 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>123</v>
@@ -17563,10 +17581,10 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
@@ -17586,16 +17604,16 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>123</v>
@@ -17609,16 +17627,16 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>123</v>
@@ -17632,16 +17650,16 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>123</v>
@@ -17655,16 +17673,16 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>123</v>
@@ -17678,16 +17696,16 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>123</v>
@@ -17701,7 +17719,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>90</v>
@@ -17710,7 +17728,7 @@
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>123</v>
@@ -17724,16 +17742,16 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>123</v>
@@ -17747,16 +17765,16 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>123</v>
@@ -17770,7 +17788,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>15</v>
@@ -17779,7 +17797,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>123</v>
@@ -17793,16 +17811,16 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>123</v>
@@ -17817,16 +17835,16 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>123</v>
@@ -17840,16 +17858,16 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>123</v>
@@ -17863,16 +17881,16 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>123</v>
@@ -17886,16 +17904,16 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>123</v>
@@ -17909,16 +17927,16 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>123</v>
@@ -17932,16 +17950,16 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>123</v>
@@ -17955,7 +17973,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>15</v>
@@ -17964,7 +17982,7 @@
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>123</v>
@@ -17978,7 +17996,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>129</v>
@@ -17987,7 +18005,7 @@
         <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>123</v>
@@ -18001,7 +18019,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>75</v>
@@ -18013,7 +18031,7 @@
         <v>26</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
@@ -18024,16 +18042,16 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>123</v>
@@ -18047,16 +18065,16 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>123</v>
@@ -18070,16 +18088,16 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>123</v>
@@ -18093,16 +18111,16 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>123</v>
@@ -18116,16 +18134,16 @@
         <v>73.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>123</v>
@@ -18139,16 +18157,16 @@
         <v>74.0</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>123</v>
@@ -18662,8 +18680,11 @@
       <c r="E19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>123</v>
+      <c r="F19" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -18674,10 +18695,10 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
@@ -18685,8 +18706,11 @@
       <c r="E20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>123</v>
+      <c r="F20" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -18697,10 +18721,10 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -18709,10 +18733,10 @@
         <v>26</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -18723,10 +18747,10 @@
         <v>19.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -18735,10 +18759,10 @@
         <v>52</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -18749,10 +18773,10 @@
         <v>20.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -18761,10 +18785,10 @@
         <v>52</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H23" s="2">
         <v>6.0</v>
@@ -18775,7 +18799,7 @@
         <v>21.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>106</v>
@@ -18798,10 +18822,10 @@
         <v>22.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
@@ -18821,10 +18845,10 @@
         <v>23.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>10</v>
@@ -18844,10 +18868,10 @@
         <v>24.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
@@ -18867,10 +18891,10 @@
         <v>25.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
@@ -18879,10 +18903,10 @@
         <v>52</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -18893,10 +18917,10 @@
         <v>26.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
@@ -18916,10 +18940,10 @@
         <v>27.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
@@ -18939,7 +18963,7 @@
         <v>28.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>62</v>
@@ -18962,10 +18986,10 @@
         <v>29.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>10</v>
@@ -18985,7 +19009,7 @@
         <v>30.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>71</v>
@@ -18997,10 +19021,10 @@
         <v>21</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -19011,7 +19035,7 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>79</v>
@@ -19034,10 +19058,10 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>10</v>
@@ -19057,10 +19081,10 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -19072,7 +19096,7 @@
         <v>123</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -19083,7 +19107,7 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>90</v>
@@ -19106,7 +19130,7 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>58</v>
@@ -19129,10 +19153,10 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
@@ -19152,7 +19176,7 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>71</v>
@@ -19175,10 +19199,10 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>10</v>
@@ -19198,10 +19222,10 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>10</v>
@@ -19221,10 +19245,10 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
@@ -19244,10 +19268,10 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
@@ -19267,7 +19291,7 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>75</v>
@@ -19290,10 +19314,10 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>10</v>
@@ -19313,10 +19337,10 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
@@ -19325,10 +19349,10 @@
         <v>16</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H47" s="2">
         <v>9.0</v>
@@ -19339,7 +19363,7 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>79</v>
@@ -19351,10 +19375,10 @@
         <v>16</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -19365,10 +19389,10 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>10</v>
@@ -19377,10 +19401,10 @@
         <v>16</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H49" s="2">
         <v>6.0</v>
@@ -19391,10 +19415,10 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>10</v>
@@ -19403,10 +19427,10 @@
         <v>16</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -19417,7 +19441,7 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>58</v>
@@ -19429,10 +19453,10 @@
         <v>16</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H51" s="2">
         <v>9.0</v>
@@ -19443,7 +19467,7 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>62</v>
@@ -19455,10 +19479,10 @@
         <v>16</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H52" s="2">
         <v>9.0</v>
@@ -19469,10 +19493,10 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
@@ -19492,10 +19516,10 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>10</v>
@@ -19515,10 +19539,10 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>10</v>
@@ -19538,10 +19562,10 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>10</v>
@@ -19550,10 +19574,10 @@
         <v>16</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H56" s="2">
         <v>9.0</v>
@@ -19564,10 +19588,10 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>10</v>
@@ -19587,7 +19611,7 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>58</v>
@@ -19599,10 +19623,10 @@
         <v>39</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H58" s="2">
         <v>9.0</v>
@@ -19613,7 +19637,7 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>129</v>
@@ -19625,10 +19649,10 @@
         <v>39</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H59" s="2">
         <v>9.0</v>
@@ -19639,10 +19663,10 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>10</v>
@@ -19654,7 +19678,7 @@
         <v>123</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H60" s="2">
         <v>9.0</v>
@@ -19665,7 +19689,7 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>129</v>
@@ -19680,7 +19704,7 @@
         <v>123</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H61" s="2">
         <v>9.0</v>
@@ -19691,10 +19715,10 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>10</v>
@@ -19703,10 +19727,10 @@
         <v>39</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H62" s="2">
         <v>9.0</v>
@@ -19717,7 +19741,7 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>25</v>
@@ -19729,10 +19753,10 @@
         <v>39</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H63" s="2">
         <v>9.0</v>
@@ -19743,7 +19767,7 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>30</v>
@@ -19758,7 +19782,7 @@
         <v>123</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H64" s="2">
         <v>9.0</v>
@@ -19769,10 +19793,10 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>10</v>
@@ -19781,10 +19805,10 @@
         <v>39</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H65" s="2">
         <v>9.0</v>
@@ -19795,10 +19819,10 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>10</v>
@@ -19810,7 +19834,7 @@
         <v>123</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H66" s="2">
         <v>9.0</v>
@@ -19821,10 +19845,10 @@
         <v>65.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
@@ -19833,10 +19857,10 @@
         <v>39</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H67" s="2">
         <v>9.0</v>
@@ -19847,7 +19871,7 @@
         <v>66.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>62</v>
@@ -19859,10 +19883,10 @@
         <v>39</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H68" s="2">
         <v>9.0</v>
@@ -19873,10 +19897,10 @@
         <v>67.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>10</v>
@@ -19885,10 +19909,10 @@
         <v>39</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H69" s="2">
         <v>9.0</v>
@@ -19899,7 +19923,7 @@
         <v>68.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>20</v>
@@ -19911,10 +19935,10 @@
         <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="H70" s="2">
         <v>6.0</v>
@@ -19925,10 +19949,10 @@
         <v>69.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>10</v>
@@ -19937,10 +19961,10 @@
         <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H71" s="2">
         <v>6.0</v>
@@ -19951,10 +19975,10 @@
         <v>70.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
@@ -19963,10 +19987,10 @@
         <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H72" s="2">
         <v>9.0</v>
@@ -19977,10 +20001,10 @@
         <v>71.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
@@ -19989,10 +20013,10 @@
         <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H73" s="2">
         <v>9.0</v>
@@ -20003,10 +20027,10 @@
         <v>72.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>10</v>
@@ -20026,10 +20050,10 @@
         <v>73.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>10</v>
@@ -20049,10 +20073,10 @@
         <v>74.0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>10</v>
@@ -20061,10 +20085,10 @@
         <v>11</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H76" s="2">
         <v>6.0</v>
@@ -20075,10 +20099,10 @@
         <v>75.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>10</v>
@@ -20098,7 +20122,7 @@
         <v>76.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>34</v>
@@ -20121,10 +20145,10 @@
         <v>77.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
@@ -20144,10 +20168,10 @@
         <v>78.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>10</v>
@@ -20156,10 +20180,10 @@
         <v>21</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H80" s="2">
         <v>9.0</v>
@@ -20170,10 +20194,10 @@
         <v>79.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>10</v>
@@ -20182,10 +20206,10 @@
         <v>21</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H81" s="2">
         <v>9.0</v>
@@ -20196,10 +20220,10 @@
         <v>80.0</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>10</v>
@@ -20211,7 +20235,7 @@
         <v>123</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="H82" s="2">
         <v>9.0</v>
@@ -20222,7 +20246,7 @@
         <v>81.0</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>71</v>
@@ -20237,7 +20261,7 @@
         <v>123</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H83" s="2">
         <v>9.0</v>
@@ -20248,13 +20272,13 @@
         <v>82.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>11</v>
@@ -20263,7 +20287,7 @@
         <v>123</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H84" s="2">
         <v>4.0</v>
@@ -20274,10 +20298,10 @@
         <v>83.0</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>10</v>
@@ -20286,10 +20310,10 @@
         <v>52</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="H85" s="2">
         <v>9.0</v>
@@ -20300,10 +20324,10 @@
         <v>84.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>10</v>
@@ -20312,10 +20336,10 @@
         <v>52</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H86" s="2">
         <v>9.0</v>
@@ -20326,10 +20350,10 @@
         <v>85.0</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>10</v>
@@ -20338,10 +20362,10 @@
         <v>26</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="H87" s="2">
         <v>9.0</v>
@@ -20352,7 +20376,7 @@
         <v>86.0</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>90</v>
@@ -20364,10 +20388,10 @@
         <v>21</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H88" s="2">
         <v>9.0</v>
@@ -20378,7 +20402,7 @@
         <v>87.0</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>71</v>
@@ -20390,10 +20414,10 @@
         <v>16</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="H89" s="2">
         <v>9.0</v>
@@ -20404,7 +20428,7 @@
         <v>88.0</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>34</v>
@@ -20419,7 +20443,7 @@
         <v>123</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H90" s="2">
         <v>9.0</v>
@@ -20430,7 +20454,7 @@
         <v>89.0</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>62</v>
@@ -21419,22 +21443,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -21445,10 +21469,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>67</v>
@@ -21457,10 +21481,10 @@
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -21471,10 +21495,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>67</v>
@@ -21483,10 +21507,10 @@
         <v>39</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -21497,10 +21521,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>67</v>
@@ -21509,10 +21533,10 @@
         <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -21523,10 +21547,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>67</v>
@@ -21535,10 +21559,10 @@
         <v>39</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -21549,7 +21573,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
@@ -21561,10 +21585,10 @@
         <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H7" s="2">
         <v>4.0</v>
@@ -21575,22 +21599,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -21601,22 +21625,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -21627,22 +21651,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="H10" s="1">
         <v>5.0</v>
@@ -21653,7 +21677,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>62</v>
@@ -21665,10 +21689,10 @@
         <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -21679,7 +21703,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>58</v>
@@ -21691,10 +21715,10 @@
         <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -21705,10 +21729,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -21717,10 +21741,10 @@
         <v>52</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -21731,10 +21755,10 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
@@ -21743,10 +21767,10 @@
         <v>39</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H14" s="2">
         <v>6.0</v>
@@ -21757,10 +21781,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -21769,10 +21793,10 @@
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -21783,10 +21807,10 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -21795,10 +21819,10 @@
         <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -21809,10 +21833,10 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
@@ -21821,10 +21845,10 @@
         <v>21</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H17" s="2">
         <v>6.0</v>
@@ -21835,10 +21859,10 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
@@ -21847,10 +21871,10 @@
         <v>21</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -21861,10 +21885,10 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -21873,10 +21897,10 @@
         <v>39</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H19" s="1">
         <v>6.0</v>
@@ -21887,10 +21911,10 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
@@ -21899,7 +21923,7 @@
         <v>52</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -21910,10 +21934,10 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -21925,7 +21949,7 @@
         <v>56</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -21936,10 +21960,10 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -21951,7 +21975,7 @@
         <v>56</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -21962,10 +21986,10 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -21974,10 +21998,10 @@
         <v>26</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -21988,10 +22012,10 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
@@ -22000,10 +22024,10 @@
         <v>39</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -22014,10 +22038,10 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
@@ -22026,10 +22050,10 @@
         <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -22040,22 +22064,22 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H26" s="2">
         <v>3.0</v>
@@ -22066,10 +22090,10 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
@@ -22078,10 +22102,10 @@
         <v>11</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -22092,10 +22116,10 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
@@ -22107,7 +22131,7 @@
         <v>123</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -22118,10 +22142,10 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
@@ -22130,10 +22154,10 @@
         <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="H29" s="2">
         <v>9.0</v>
@@ -22144,7 +22168,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>71</v>
@@ -22159,7 +22183,7 @@
         <v>123</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H30" s="2">
         <v>9.0</v>
@@ -22170,10 +22194,10 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -22185,7 +22209,7 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="H31" s="2">
         <v>9.0</v>
@@ -22196,10 +22220,10 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
@@ -22208,10 +22232,10 @@
         <v>16</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="H32" s="2">
         <v>9.0</v>
@@ -22222,10 +22246,10 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
@@ -22234,10 +22258,10 @@
         <v>26</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -22248,10 +22272,10 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
@@ -22260,10 +22284,10 @@
         <v>21</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="H34" s="2">
         <v>9.0</v>
@@ -22274,10 +22298,10 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
@@ -22286,10 +22310,10 @@
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="H35" s="2">
         <v>9.0</v>
@@ -22300,10 +22324,10 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -22312,10 +22336,10 @@
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -22326,10 +22350,10 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
@@ -22338,10 +22362,10 @@
         <v>52</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="H37" s="2">
         <v>9.0</v>
@@ -22352,10 +22376,10 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
@@ -22364,7 +22388,7 @@
         <v>52</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H38" s="2">
         <v>9.0</v>
@@ -22375,10 +22399,10 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
@@ -22387,10 +22411,10 @@
         <v>39</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="H39" s="2">
         <v>9.0</v>
@@ -22401,7 +22425,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>71</v>
@@ -22413,10 +22437,10 @@
         <v>39</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="H40" s="2">
         <v>9.0</v>
@@ -22427,10 +22451,10 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
@@ -22439,10 +22463,10 @@
         <v>26</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="H41" s="2">
         <v>9.0</v>
@@ -22453,10 +22477,10 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
@@ -22468,7 +22492,7 @@
         <v>123</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H42" s="2">
         <v>9.0</v>
@@ -22479,10 +22503,10 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
@@ -22494,7 +22518,7 @@
         <v>123</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="H43" s="2">
         <v>9.0</v>
@@ -22505,7 +22529,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>43</v>
@@ -22528,7 +22552,7 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>43</v>
@@ -22540,7 +22564,7 @@
         <v>16</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H45" s="2">
         <v>6.0</v>
@@ -22551,7 +22575,7 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>62</v>
@@ -22574,7 +22598,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>15</v>
@@ -22586,7 +22610,7 @@
         <v>39</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H47" s="2">
         <v>6.0</v>
@@ -22597,7 +22621,7 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>90</v>
@@ -22612,7 +22636,7 @@
         <v>123</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -22623,10 +22647,10 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
@@ -22635,10 +22659,10 @@
         <v>21</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H49" s="2">
         <v>9.0</v>
@@ -22649,10 +22673,10 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
@@ -22664,7 +22688,7 @@
         <v>123</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -23680,22 +23704,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -23706,10 +23730,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>67</v>
@@ -23718,10 +23742,10 @@
         <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -23732,7 +23756,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>90</v>
@@ -23744,10 +23768,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -23758,22 +23782,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -23784,22 +23808,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -23810,22 +23834,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -23836,10 +23860,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>67</v>
@@ -23848,10 +23872,10 @@
         <v>16</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="H8" s="2">
         <v>4.0</v>
@@ -23862,22 +23886,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -23888,10 +23912,10 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
@@ -23900,10 +23924,10 @@
         <v>21</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -23914,10 +23938,10 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
@@ -23926,10 +23950,10 @@
         <v>39</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -23940,22 +23964,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="H12" s="2">
         <v>5.0</v>
@@ -23966,22 +23990,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="H13" s="2">
         <v>3.0</v>
@@ -23992,7 +24016,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>79</v>
@@ -24015,10 +24039,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -24027,10 +24051,10 @@
         <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -24041,10 +24065,10 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -24053,10 +24077,10 @@
         <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -24067,10 +24091,10 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
@@ -24082,7 +24106,7 @@
         <v>123</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="H17" s="2">
         <v>9.0</v>
@@ -24093,10 +24117,10 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
@@ -24105,10 +24129,10 @@
         <v>39</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -24119,10 +24143,10 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -24131,10 +24155,10 @@
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -24145,22 +24169,22 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="H20" s="2">
         <v>7.0</v>
@@ -24171,10 +24195,10 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -24186,7 +24210,7 @@
         <v>123</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="H21" s="2">
         <v>7.0</v>
@@ -24197,10 +24221,10 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -24212,7 +24236,7 @@
         <v>123</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -24223,10 +24247,10 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -24235,7 +24259,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -24246,7 +24270,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>71</v>
@@ -24261,7 +24285,7 @@
         <v>123</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -24272,10 +24296,10 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -24284,10 +24308,10 @@
         <v>26</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -24298,10 +24322,10 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -24310,10 +24334,10 @@
         <v>26</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="H26" s="2">
         <v>9.0</v>
@@ -24324,10 +24348,10 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -24336,10 +24360,10 @@
         <v>26</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -25378,10 +25402,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -25390,10 +25414,10 @@
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25404,22 +25428,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -25430,22 +25454,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -25456,10 +25480,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>67</v>
@@ -25468,10 +25492,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -25482,22 +25506,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>129</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -25508,22 +25532,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -25534,7 +25558,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>79</v>
@@ -25557,10 +25581,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
@@ -25569,10 +25593,10 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -25583,7 +25607,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>79</v>
@@ -26647,22 +26671,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="H2" s="2">
         <v>2.0</v>
@@ -26673,22 +26697,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -26699,22 +26723,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -26725,22 +26749,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -26751,22 +26775,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -26777,10 +26801,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -26789,10 +26813,10 @@
         <v>16</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>
@@ -26803,10 +26827,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
@@ -26826,10 +26850,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
@@ -26838,10 +26862,10 @@
         <v>52</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -26852,10 +26876,10 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
@@ -26875,7 +26899,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>62</v>
@@ -26887,10 +26911,10 @@
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -26901,7 +26925,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>62</v>
@@ -26913,10 +26937,10 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -26927,10 +26951,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -26939,10 +26963,10 @@
         <v>26</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="H13" s="2">
         <v>9.0</v>
@@ -27990,22 +28014,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -28016,22 +28040,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -28042,22 +28066,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28068,10 +28092,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -28091,10 +28115,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
@@ -28103,10 +28127,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -28117,10 +28141,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -28129,10 +28153,10 @@
         <v>39</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28143,22 +28167,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="H8" s="2">
         <v>5.0</v>
@@ -29212,10 +29236,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -29224,10 +29248,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -29238,22 +29262,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -29264,10 +29288,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
@@ -29276,7 +29300,7 @@
         <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -29287,22 +29311,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -29313,22 +29337,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29339,7 +29363,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>58</v>
@@ -29351,10 +29375,10 @@
         <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>
